--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9670C4E-6329-D345-B6B3-2D0DC192514C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D45F4D-14D1-1849-8E8A-6C7CC13C73E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="614">
   <si>
     <t>CARASE FB &amp; STORE  •  BẢNG CHỈ SỐ TỔNG HỢP  •  T1/2025 → T9/2026</t>
   </si>
@@ -2015,6 +2015,9 @@
   </si>
   <si>
     <t>3M</t>
+  </si>
+  <si>
+    <t>🏪  STORE</t>
   </si>
 </sst>
 </file>
@@ -2028,7 +2031,7 @@
     <numFmt numFmtId="167" formatCode="0.0\x"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="55" x14ac:knownFonts="1">
+  <fonts count="56" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -2433,6 +2436,11 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="54">
@@ -2887,7 +2895,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="49" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3304,26 +3312,15 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3331,6 +3328,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3345,12 +3355,6 @@
     <xf numFmtId="0" fontId="51" fillId="47" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3364,6 +3368,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3678,40 +3688,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="160" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="164" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="160" t="s">
+      <c r="A3" s="162" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="133" t="s">
@@ -3740,16 +3750,16 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="163" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="159"/>
-      <c r="C5" s="159"/>
-      <c r="D5" s="159"/>
-      <c r="E5" s="159"/>
-      <c r="F5" s="159"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="159"/>
+      <c r="B5" s="161"/>
+      <c r="C5" s="161"/>
+      <c r="D5" s="161"/>
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="161"/>
+      <c r="H5" s="161"/>
     </row>
     <row r="6" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="134" t="s">
@@ -3880,16 +3890,16 @@
       <c r="H10" s="136"/>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="161" t="s">
+      <c r="A11" s="163" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="159"/>
-      <c r="C11" s="159"/>
-      <c r="D11" s="159"/>
-      <c r="E11" s="159"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="159"/>
-      <c r="H11" s="159"/>
+      <c r="B11" s="161"/>
+      <c r="C11" s="161"/>
+      <c r="D11" s="161"/>
+      <c r="E11" s="161"/>
+      <c r="F11" s="161"/>
+      <c r="G11" s="161"/>
+      <c r="H11" s="161"/>
     </row>
     <row r="12" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="134" t="s">
@@ -4198,16 +4208,16 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="161" t="s">
+      <c r="A24" s="163" t="s">
         <v>207</v>
       </c>
-      <c r="B24" s="159"/>
-      <c r="C24" s="159"/>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="159"/>
-      <c r="G24" s="159"/>
-      <c r="H24" s="159"/>
+      <c r="B24" s="161"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="161"/>
+      <c r="H24" s="161"/>
     </row>
     <row r="25" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="134" t="s">
@@ -4352,16 +4362,16 @@
       <c r="H30" s="140"/>
     </row>
     <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="161" t="s">
+      <c r="A31" s="163" t="s">
         <v>237</v>
       </c>
-      <c r="B31" s="159"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="159"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="159"/>
-      <c r="G31" s="159"/>
-      <c r="H31" s="159"/>
+      <c r="B31" s="161"/>
+      <c r="C31" s="161"/>
+      <c r="D31" s="161"/>
+      <c r="E31" s="161"/>
+      <c r="F31" s="161"/>
+      <c r="G31" s="161"/>
+      <c r="H31" s="161"/>
     </row>
     <row r="32" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="134" t="s">
@@ -4646,16 +4656,16 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="161" t="s">
+      <c r="A44" s="163" t="s">
         <v>293</v>
       </c>
-      <c r="B44" s="159"/>
-      <c r="C44" s="159"/>
-      <c r="D44" s="159"/>
-      <c r="E44" s="159"/>
-      <c r="F44" s="159"/>
-      <c r="G44" s="159"/>
-      <c r="H44" s="159"/>
+      <c r="B44" s="161"/>
+      <c r="C44" s="161"/>
+      <c r="D44" s="161"/>
+      <c r="E44" s="161"/>
+      <c r="F44" s="161"/>
+      <c r="G44" s="161"/>
+      <c r="H44" s="161"/>
     </row>
     <row r="45" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="134" t="s">
@@ -4812,16 +4822,16 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="161" t="s">
+      <c r="A51" s="163" t="s">
         <v>331</v>
       </c>
-      <c r="B51" s="159"/>
-      <c r="C51" s="159"/>
-      <c r="D51" s="159"/>
-      <c r="E51" s="159"/>
-      <c r="F51" s="159"/>
-      <c r="G51" s="159"/>
-      <c r="H51" s="159"/>
+      <c r="B51" s="161"/>
+      <c r="C51" s="161"/>
+      <c r="D51" s="161"/>
+      <c r="E51" s="161"/>
+      <c r="F51" s="161"/>
+      <c r="G51" s="161"/>
+      <c r="H51" s="161"/>
     </row>
     <row r="52" spans="1:8" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="134" t="s">
@@ -5035,66 +5045,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -5104,11 +5114,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -5170,7 +5180,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -6933,66 +6943,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>414</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -7002,11 +7012,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -7068,7 +7078,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -8872,66 +8882,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>415</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -8941,11 +8951,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -9007,7 +9017,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1149763530</v>
       </c>
@@ -10785,36 +10795,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>416</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -11084,10 +11094,10 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>437</v>
       </c>
-      <c r="B23" s="147"/>
+      <c r="B23" s="149"/>
       <c r="C23" s="76">
         <v>1221140305</v>
       </c>
@@ -11107,37 +11117,37 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="172" t="s">
+      <c r="A25" s="174" t="s">
         <v>438</v>
       </c>
-      <c r="B25" s="147"/>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="147"/>
-      <c r="G25" s="147"/>
-      <c r="H25" s="147"/>
-      <c r="I25" s="147"/>
-      <c r="J25" s="147"/>
-      <c r="K25" s="147"/>
-      <c r="L25" s="147"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="149"/>
+      <c r="I25" s="149"/>
+      <c r="J25" s="149"/>
+      <c r="K25" s="149"/>
+      <c r="L25" s="149"/>
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="170" t="s">
+      <c r="A27" s="172" t="s">
         <v>439</v>
       </c>
-      <c r="B27" s="147"/>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="147"/>
-      <c r="F27" s="147"/>
-      <c r="G27" s="147"/>
-      <c r="H27" s="147"/>
-      <c r="I27" s="147"/>
-      <c r="J27" s="147"/>
-      <c r="K27" s="147"/>
-      <c r="L27" s="171"/>
+      <c r="B27" s="149"/>
+      <c r="C27" s="149"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
+      <c r="G27" s="149"/>
+      <c r="H27" s="149"/>
+      <c r="I27" s="149"/>
+      <c r="J27" s="149"/>
+      <c r="K27" s="149"/>
+      <c r="L27" s="173"/>
       <c r="M27" s="79"/>
       <c r="N27" s="79"/>
       <c r="O27" s="79"/>
@@ -11370,20 +11380,20 @@
       <c r="T34" s="84"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="170" t="s">
+      <c r="A35" s="172" t="s">
         <v>463</v>
       </c>
-      <c r="B35" s="147"/>
-      <c r="C35" s="147"/>
-      <c r="D35" s="147"/>
-      <c r="E35" s="147"/>
-      <c r="F35" s="147"/>
-      <c r="G35" s="147"/>
-      <c r="H35" s="147"/>
-      <c r="I35" s="147"/>
-      <c r="J35" s="147"/>
-      <c r="K35" s="147"/>
-      <c r="L35" s="171"/>
+      <c r="B35" s="149"/>
+      <c r="C35" s="149"/>
+      <c r="D35" s="149"/>
+      <c r="E35" s="149"/>
+      <c r="F35" s="149"/>
+      <c r="G35" s="149"/>
+      <c r="H35" s="149"/>
+      <c r="I35" s="149"/>
+      <c r="J35" s="149"/>
+      <c r="K35" s="149"/>
+      <c r="L35" s="173"/>
       <c r="M35" s="84"/>
       <c r="N35" s="84"/>
       <c r="O35" s="84"/>
@@ -11659,11 +11669,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11694,66 +11704,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>467</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -11763,11 +11773,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -11829,7 +11839,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1214990084</v>
       </c>
@@ -13660,36 +13670,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -14037,10 +14047,10 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>437</v>
       </c>
-      <c r="B23" s="147"/>
+      <c r="B23" s="149"/>
       <c r="C23" s="76">
         <v>1214990084</v>
       </c>
@@ -14060,20 +14070,20 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="172" t="s">
+      <c r="A25" s="174" t="s">
         <v>438</v>
       </c>
-      <c r="B25" s="147"/>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="147"/>
-      <c r="G25" s="147"/>
-      <c r="H25" s="147"/>
-      <c r="I25" s="147"/>
-      <c r="J25" s="147"/>
-      <c r="K25" s="147"/>
-      <c r="L25" s="147"/>
+      <c r="B25" s="149"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
+      <c r="G25" s="149"/>
+      <c r="H25" s="149"/>
+      <c r="I25" s="149"/>
+      <c r="J25" s="149"/>
+      <c r="K25" s="149"/>
+      <c r="L25" s="149"/>
     </row>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14286,66 +14296,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -14355,11 +14365,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -14421,7 +14431,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1221751028</v>
       </c>
@@ -14482,7 +14492,7 @@
         <v>92</v>
       </c>
       <c r="K6" s="49">
-        <v>559999</v>
+        <v>909999</v>
       </c>
       <c r="L6" s="50"/>
       <c r="M6" s="8">
@@ -15283,31 +15293,45 @@
       <c r="B22" s="48" t="s">
         <v>400</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
+      <c r="C22" s="49">
+        <v>37131550</v>
+      </c>
+      <c r="D22" s="49">
+        <v>70</v>
+      </c>
       <c r="E22" s="49"/>
       <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
+      <c r="G22" s="49">
+        <v>5196495</v>
+      </c>
+      <c r="H22" s="49">
+        <v>3660003</v>
+      </c>
+      <c r="I22" s="49">
+        <v>3904999</v>
+      </c>
+      <c r="J22" s="49">
+        <v>42</v>
+      </c>
+      <c r="K22" s="49">
+        <v>480000</v>
+      </c>
       <c r="L22" s="50"/>
-      <c r="M22" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N22" s="8" t="str">
+      <c r="M22" s="8">
+        <f t="shared" si="0"/>
+        <v>12761497</v>
+      </c>
+      <c r="N22" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O22" s="8" t="str">
+        <v>49893047</v>
+      </c>
+      <c r="O22" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P22" s="8" t="str">
+        <v>530450.71428571432</v>
+      </c>
+      <c r="P22" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>303845.16666666669</v>
       </c>
       <c r="Q22" s="21" t="str">
         <f t="shared" si="4"/>
@@ -15321,31 +15345,45 @@
       <c r="B23" s="48" t="s">
         <v>401</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
+      <c r="C23" s="49">
+        <v>41967298</v>
+      </c>
+      <c r="D23" s="49">
+        <v>86</v>
+      </c>
       <c r="E23" s="49"/>
       <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
+      <c r="G23" s="49">
+        <v>5696003</v>
+      </c>
+      <c r="H23" s="49">
+        <v>1689002</v>
+      </c>
+      <c r="I23" s="49">
+        <v>2518499</v>
+      </c>
+      <c r="J23" s="49">
+        <v>26</v>
+      </c>
+      <c r="K23" s="49">
+        <v>1828800</v>
+      </c>
       <c r="L23" s="50"/>
-      <c r="M23" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N23" s="8" t="str">
+      <c r="M23" s="8">
+        <f t="shared" si="0"/>
+        <v>9903504</v>
+      </c>
+      <c r="N23" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O23" s="8" t="str">
+        <v>51870802</v>
+      </c>
+      <c r="O23" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P23" s="8" t="str">
+        <v>487991.83720930235</v>
+      </c>
+      <c r="P23" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>380904</v>
       </c>
       <c r="Q23" s="21" t="str">
         <f t="shared" si="4"/>
@@ -15359,31 +15397,45 @@
       <c r="B24" s="48" t="s">
         <v>402</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
+      <c r="C24" s="49">
+        <v>39806062</v>
+      </c>
+      <c r="D24" s="49">
+        <v>88</v>
+      </c>
       <c r="E24" s="49"/>
       <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
+      <c r="G24" s="49">
+        <v>11530503</v>
+      </c>
+      <c r="H24" s="49">
+        <v>3214502</v>
+      </c>
+      <c r="I24" s="49">
+        <v>1877001</v>
+      </c>
+      <c r="J24" s="49">
+        <v>48</v>
+      </c>
+      <c r="K24" s="49">
+        <v>480000</v>
+      </c>
       <c r="L24" s="50"/>
-      <c r="M24" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N24" s="8" t="str">
+      <c r="M24" s="8">
+        <f t="shared" si="0"/>
+        <v>16622006</v>
+      </c>
+      <c r="N24" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O24" s="8" t="str">
+        <v>56428068</v>
+      </c>
+      <c r="O24" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P24" s="8" t="str">
+        <v>452341.61363636365</v>
+      </c>
+      <c r="P24" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>346291.79166666669</v>
       </c>
       <c r="Q24" s="21" t="str">
         <f t="shared" si="4"/>
@@ -15397,31 +15449,43 @@
       <c r="B25" s="48" t="s">
         <v>403</v>
       </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
+      <c r="C25" s="49">
+        <v>38745150</v>
+      </c>
+      <c r="D25" s="49">
+        <v>97</v>
+      </c>
       <c r="E25" s="49"/>
       <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
+      <c r="G25" s="49">
+        <v>4610000</v>
+      </c>
+      <c r="H25" s="49">
+        <v>1930004</v>
+      </c>
+      <c r="I25" s="49">
+        <v>2952000</v>
+      </c>
+      <c r="J25" s="49">
+        <v>30</v>
+      </c>
       <c r="K25" s="49"/>
       <c r="L25" s="50"/>
-      <c r="M25" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N25" s="8" t="str">
+      <c r="M25" s="8">
+        <f t="shared" si="0"/>
+        <v>9492004</v>
+      </c>
+      <c r="N25" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O25" s="8" t="str">
+        <v>48237154</v>
+      </c>
+      <c r="O25" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P25" s="8" t="str">
+        <v>399434.53608247422</v>
+      </c>
+      <c r="P25" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>316400.13333333336</v>
       </c>
       <c r="Q25" s="21" t="str">
         <f t="shared" si="4"/>
@@ -15435,31 +15499,45 @@
       <c r="B26" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
+      <c r="C26" s="49">
+        <v>28912295</v>
+      </c>
+      <c r="D26" s="49">
+        <v>68</v>
+      </c>
       <c r="E26" s="49"/>
       <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
+      <c r="G26" s="49">
+        <v>5468000</v>
+      </c>
+      <c r="H26" s="49">
+        <v>6046251</v>
+      </c>
+      <c r="I26" s="49">
+        <v>3174251</v>
+      </c>
+      <c r="J26" s="49">
+        <v>42</v>
+      </c>
+      <c r="K26" s="49">
+        <v>702400</v>
+      </c>
       <c r="L26" s="50"/>
-      <c r="M26" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N26" s="8" t="str">
+      <c r="M26" s="8">
+        <f t="shared" si="0"/>
+        <v>14688502</v>
+      </c>
+      <c r="N26" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O26" s="8" t="str">
+        <v>43600797</v>
+      </c>
+      <c r="O26" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P26" s="8" t="str">
+        <v>425180.8088235294</v>
+      </c>
+      <c r="P26" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>349726.23809523811</v>
       </c>
       <c r="Q26" s="21" t="str">
         <f t="shared" si="4"/>
@@ -15473,31 +15551,43 @@
       <c r="B27" s="52" t="s">
         <v>405</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
+      <c r="C27" s="49">
+        <v>33670286</v>
+      </c>
+      <c r="D27" s="49">
+        <v>78</v>
+      </c>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
+      <c r="G27" s="49">
+        <v>6381999</v>
+      </c>
+      <c r="H27" s="49">
+        <v>3534999</v>
+      </c>
+      <c r="I27" s="49">
+        <v>5284252</v>
+      </c>
+      <c r="J27" s="49">
+        <v>51</v>
+      </c>
       <c r="K27" s="49"/>
       <c r="L27" s="50"/>
-      <c r="M27" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N27" s="8" t="str">
+      <c r="M27" s="8">
+        <f t="shared" si="0"/>
+        <v>15201250</v>
+      </c>
+      <c r="N27" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O27" s="8" t="str">
+        <v>48871536</v>
+      </c>
+      <c r="O27" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P27" s="8" t="str">
+        <v>431670.33333333331</v>
+      </c>
+      <c r="P27" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>298063.72549019608</v>
       </c>
       <c r="Q27" s="21" t="str">
         <f t="shared" si="4"/>
@@ -15511,31 +15601,43 @@
       <c r="B28" s="52" t="s">
         <v>406</v>
       </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
+      <c r="C28" s="49">
+        <v>37574298</v>
+      </c>
+      <c r="D28" s="49">
+        <v>77</v>
+      </c>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
+      <c r="G28" s="49">
+        <v>13031998</v>
+      </c>
+      <c r="H28" s="49">
+        <v>1918501</v>
+      </c>
+      <c r="I28" s="49">
+        <v>2320498</v>
+      </c>
+      <c r="J28" s="49">
+        <v>47</v>
+      </c>
       <c r="K28" s="49"/>
       <c r="L28" s="50"/>
-      <c r="M28" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N28" s="8" t="str">
+      <c r="M28" s="8">
+        <f t="shared" si="0"/>
+        <v>17270997</v>
+      </c>
+      <c r="N28" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O28" s="8" t="str">
+        <v>54845295</v>
+      </c>
+      <c r="O28" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P28" s="8" t="str">
+        <v>487977.89610389608</v>
+      </c>
+      <c r="P28" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>367468.02127659577</v>
       </c>
       <c r="Q28" s="21" t="str">
         <f t="shared" si="4"/>
@@ -16048,36 +16150,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>476</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
     </row>
     <row r="3" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
@@ -16216,15 +16318,15 @@
       </c>
       <c r="C6" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!C20:C26),0)</f>
-        <v>67353633</v>
+        <v>253915988</v>
       </c>
       <c r="D6" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!D20:D26),0)</f>
-        <v>151</v>
+        <v>560</v>
       </c>
       <c r="E6" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!C20:C26)/SUM('📅 DAILY T8'!D20:D26),"")</f>
-        <v>446050.54966887418</v>
+        <v>453421.40714285715</v>
       </c>
       <c r="F6" s="56">
         <f>IFERROR(SUM('📅 DAILY T8'!F20:F26),0)</f>
@@ -16236,19 +16338,19 @@
       </c>
       <c r="H6" s="58">
         <f>IFERROR(SUM('📅 DAILY T8'!M20:M26),0)</f>
-        <v>33168522</v>
+        <v>96636035</v>
       </c>
       <c r="I6" s="59">
         <f>IFERROR(SUM('📅 DAILY T8'!N20:N26),0)</f>
-        <v>100522155</v>
+        <v>350552023</v>
       </c>
       <c r="J6" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C26)/1292244677,"")</f>
-        <v>0.45417330900717651</v>
+        <v>0.59854407587550074</v>
       </c>
       <c r="K6" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M26)/730208327,"")</f>
-        <v>0.35199724584899178</v>
+        <v>0.43891424015491953</v>
       </c>
       <c r="L6" s="61"/>
     </row>
@@ -16261,15 +16363,15 @@
       </c>
       <c r="C7" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!C27:C33),0)</f>
-        <v>0</v>
+        <v>71244584</v>
       </c>
       <c r="D7" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!D27:D33),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="55" t="str">
+        <v>155</v>
+      </c>
+      <c r="E7" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!C27:C33)/SUM('📅 DAILY T8'!D27:D33),"")</f>
-        <v/>
+        <v>459642.47741935484</v>
       </c>
       <c r="F7" s="56">
         <f>IFERROR(SUM('📅 DAILY T8'!F27:F33),0)</f>
@@ -16281,19 +16383,19 @@
       </c>
       <c r="H7" s="58">
         <f>IFERROR(SUM('📅 DAILY T8'!M27:M33),0)</f>
-        <v>0</v>
+        <v>32472247</v>
       </c>
       <c r="I7" s="59">
         <f>IFERROR(SUM('📅 DAILY T8'!N27:N33),0)</f>
-        <v>0</v>
+        <v>103716831</v>
       </c>
       <c r="J7" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C33)/1292244677,"")</f>
-        <v>0.45417330900717651</v>
+        <v>0.65367650185337156</v>
       </c>
       <c r="K7" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M33)/730208327,"")</f>
-        <v>0.35199724584899178</v>
+        <v>0.4833840795135167</v>
       </c>
       <c r="L7" s="61"/>
     </row>
@@ -16306,11 +16408,11 @@
       </c>
       <c r="C8" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!C28:C34),0)</f>
-        <v>0</v>
+        <v>37574298</v>
       </c>
       <c r="D8" s="55">
         <f>IFERROR(SUM('📅 DAILY T8'!D28:D34),0)</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="56">
@@ -16320,19 +16422,19 @@
       <c r="G8" s="57"/>
       <c r="H8" s="58">
         <f>IFERROR(SUM('📅 DAILY T8'!M28:M34),0)</f>
-        <v>0</v>
+        <v>17270997</v>
       </c>
       <c r="I8" s="59">
         <f>IFERROR(SUM('📅 DAILY T8'!N28:N34),0)</f>
-        <v>0</v>
+        <v>54845295</v>
       </c>
       <c r="J8" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!C7:C34)/1292244677,"")</f>
-        <v>0.42379783778362584</v>
+        <v>0.6233010306298209</v>
       </c>
       <c r="K8" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!M7:M34)/730208327,"")</f>
-        <v>0.3179244133708708</v>
+        <v>0.44931124703539571</v>
       </c>
       <c r="L8" s="61"/>
     </row>
@@ -16373,11 +16475,11 @@
       </c>
       <c r="J9" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36)/1292244677,"")</f>
-        <v>0.45417330900717651</v>
+        <v>0.65367650185337156</v>
       </c>
       <c r="K9" s="60">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M36)/730208327,"")</f>
-        <v>0.35199724584899178</v>
+        <v>0.4833840795135167</v>
       </c>
       <c r="L9" s="61"/>
     </row>
@@ -16426,15 +16528,15 @@
       </c>
       <c r="C22" s="73">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36),0)</f>
-        <v>586903041</v>
+        <v>844709980</v>
       </c>
       <c r="D22" s="73">
         <f>IFERROR(SUM('📅 DAILY T8'!D6:D36),0)</f>
-        <v>1392</v>
+        <v>1956</v>
       </c>
       <c r="E22" s="73">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36)/SUM('📅 DAILY T8'!D6:D36),"")</f>
-        <v>421625.74784482759</v>
+        <v>431855.81799591001</v>
       </c>
       <c r="F22" s="73">
         <f>IFERROR(SUM('📅 DAILY T8'!F6:F36),0)</f>
@@ -16446,28 +16548,28 @@
       </c>
       <c r="H22" s="73">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M36),0)</f>
-        <v>257031320</v>
+        <v>352971080</v>
       </c>
       <c r="I22" s="73">
         <f>IFERROR(SUM('📅 DAILY T8'!N6:N36),0)</f>
-        <v>843934361</v>
+        <v>1197681060</v>
       </c>
       <c r="J22" s="75">
         <f>IFERROR(SUM('📅 DAILY T8'!C6:C36)/1292244677,"")</f>
-        <v>0.45417330900717651</v>
+        <v>0.65367650185337156</v>
       </c>
       <c r="K22" s="75">
         <f>IFERROR(SUM('📅 DAILY T8'!M6:M36)/730208327,"")</f>
-        <v>0.35199724584899178</v>
+        <v>0.4833840795135167</v>
       </c>
       <c r="L22" s="70"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="173" t="s">
+      <c r="A24" s="175" t="s">
         <v>437</v>
       </c>
-      <c r="B24" s="147"/>
+      <c r="B24" s="149"/>
       <c r="C24" s="76">
         <v>1221751028</v>
       </c>
@@ -16487,20 +16589,20 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="172" t="s">
+      <c r="A26" s="174" t="s">
         <v>438</v>
       </c>
-      <c r="B26" s="147"/>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="147"/>
-      <c r="G26" s="147"/>
-      <c r="H26" s="147"/>
-      <c r="I26" s="147"/>
-      <c r="J26" s="147"/>
-      <c r="K26" s="147"/>
-      <c r="L26" s="147"/>
+      <c r="B26" s="149"/>
+      <c r="C26" s="149"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="149"/>
+      <c r="H26" s="149"/>
+      <c r="I26" s="149"/>
+      <c r="J26" s="149"/>
+      <c r="K26" s="149"/>
+      <c r="L26" s="149"/>
     </row>
     <row r="27" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -16713,66 +16815,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>484</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -16782,11 +16884,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -16848,7 +16950,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1009097583</v>
       </c>
@@ -18223,40 +18325,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>485</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="176" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -18583,60 +18685,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="158" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
-      <c r="R1" s="147"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
-      <c r="W1" s="147"/>
-      <c r="X1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
     </row>
     <row r="2" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="147"/>
-      <c r="S2" s="147"/>
-      <c r="T2" s="147"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
+      <c r="R2" s="149"/>
+      <c r="S2" s="149"/>
+      <c r="T2" s="149"/>
+      <c r="U2" s="149"/>
+      <c r="V2" s="149"/>
+      <c r="W2" s="149"/>
+      <c r="X2" s="149"/>
     </row>
     <row r="3" spans="1:24" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -18713,60 +18815,60 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
-      <c r="O4" s="147"/>
-      <c r="P4" s="147"/>
-      <c r="Q4" s="147"/>
-      <c r="R4" s="147"/>
-      <c r="S4" s="147"/>
-      <c r="T4" s="147"/>
-      <c r="U4" s="147"/>
-      <c r="V4" s="147"/>
-      <c r="W4" s="147"/>
-      <c r="X4" s="147"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="149"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="149"/>
+      <c r="R4" s="149"/>
+      <c r="S4" s="149"/>
+      <c r="T4" s="149"/>
+      <c r="U4" s="149"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="149"/>
+      <c r="X4" s="149"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="147"/>
-      <c r="Q5" s="147"/>
-      <c r="R5" s="147"/>
-      <c r="S5" s="147"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="147"/>
-      <c r="V5" s="147"/>
-      <c r="W5" s="147"/>
-      <c r="X5" s="147"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="149"/>
+      <c r="N5" s="149"/>
+      <c r="O5" s="149"/>
+      <c r="P5" s="149"/>
+      <c r="Q5" s="149"/>
+      <c r="R5" s="149"/>
+      <c r="S5" s="149"/>
+      <c r="T5" s="149"/>
+      <c r="U5" s="149"/>
+      <c r="V5" s="149"/>
+      <c r="W5" s="149"/>
+      <c r="X5" s="149"/>
     </row>
     <row r="6" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
@@ -18834,7 +18936,7 @@
         <v>1192707123</v>
       </c>
       <c r="W6" s="8">
-        <v>586903041</v>
+        <v>844709980</v>
       </c>
       <c r="X6" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35),0)</f>
@@ -18907,7 +19009,7 @@
         <v>2823</v>
       </c>
       <c r="W7" s="8">
-        <v>1392</v>
+        <v>1956</v>
       </c>
       <c r="X7" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!D$6:D$35),0)</f>
@@ -18980,7 +19082,7 @@
         <v>422496</v>
       </c>
       <c r="W8" s="8">
-        <v>421626</v>
+        <v>431855</v>
       </c>
       <c r="X8" s="8" t="str">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)/SUM('📅 DAILY T9'!D$6:D$35),"")</f>
@@ -19053,7 +19155,7 @@
         <v>5129</v>
       </c>
       <c r="W9" s="11">
-        <v>2474</v>
+        <v>3792</v>
       </c>
       <c r="X9" s="11"/>
     </row>
@@ -19171,7 +19273,7 @@
       </c>
       <c r="W11" s="12">
         <f t="shared" si="0"/>
-        <v>0.56265157639450281</v>
+        <v>0.51582278481012656</v>
       </c>
       <c r="X11" s="13"/>
     </row>
@@ -19204,60 +19306,60 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="148" t="s">
+      <c r="A13" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="147"/>
-      <c r="C13" s="147"/>
-      <c r="D13" s="147"/>
-      <c r="E13" s="147"/>
-      <c r="F13" s="147"/>
-      <c r="G13" s="147"/>
-      <c r="H13" s="147"/>
-      <c r="I13" s="147"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="147"/>
-      <c r="T13" s="147"/>
-      <c r="U13" s="147"/>
-      <c r="V13" s="147"/>
-      <c r="W13" s="147"/>
-      <c r="X13" s="147"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="149"/>
+      <c r="G13" s="149"/>
+      <c r="H13" s="149"/>
+      <c r="I13" s="149"/>
+      <c r="J13" s="149"/>
+      <c r="K13" s="149"/>
+      <c r="L13" s="149"/>
+      <c r="M13" s="149"/>
+      <c r="N13" s="149"/>
+      <c r="O13" s="149"/>
+      <c r="P13" s="149"/>
+      <c r="Q13" s="149"/>
+      <c r="R13" s="149"/>
+      <c r="S13" s="149"/>
+      <c r="T13" s="149"/>
+      <c r="U13" s="149"/>
+      <c r="V13" s="149"/>
+      <c r="W13" s="149"/>
+      <c r="X13" s="149"/>
     </row>
     <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="149" t="s">
+      <c r="A14" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="147"/>
-      <c r="C14" s="147"/>
-      <c r="D14" s="147"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="147"/>
-      <c r="G14" s="147"/>
-      <c r="H14" s="147"/>
-      <c r="I14" s="147"/>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="147"/>
-      <c r="N14" s="147"/>
-      <c r="O14" s="147"/>
-      <c r="P14" s="147"/>
-      <c r="Q14" s="147"/>
-      <c r="R14" s="147"/>
-      <c r="S14" s="147"/>
-      <c r="T14" s="147"/>
-      <c r="U14" s="147"/>
-      <c r="V14" s="147"/>
-      <c r="W14" s="147"/>
-      <c r="X14" s="147"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="149"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="149"/>
+      <c r="I14" s="149"/>
+      <c r="J14" s="149"/>
+      <c r="K14" s="149"/>
+      <c r="L14" s="149"/>
+      <c r="M14" s="149"/>
+      <c r="N14" s="149"/>
+      <c r="O14" s="149"/>
+      <c r="P14" s="149"/>
+      <c r="Q14" s="149"/>
+      <c r="R14" s="149"/>
+      <c r="S14" s="149"/>
+      <c r="T14" s="149"/>
+      <c r="U14" s="149"/>
+      <c r="V14" s="149"/>
+      <c r="W14" s="149"/>
+      <c r="X14" s="149"/>
     </row>
     <row r="15" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
@@ -19325,7 +19427,7 @@
         <v>824</v>
       </c>
       <c r="W15" s="11">
-        <v>403</v>
+        <v>553</v>
       </c>
       <c r="X15" s="11"/>
     </row>
@@ -19395,7 +19497,7 @@
         <v>393944</v>
       </c>
       <c r="W16" s="11">
-        <v>430758</v>
+        <v>435521</v>
       </c>
       <c r="X16" s="11"/>
     </row>
@@ -19405,7 +19507,7 @@
         <v>44</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D17" s="143">
         <v>525</v>
@@ -19465,7 +19567,7 @@
         <v>135</v>
       </c>
       <c r="W17" s="144">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="X17" s="13"/>
     </row>
@@ -19475,7 +19577,7 @@
         <v>45</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D18" s="143">
         <v>118</v>
@@ -19535,37 +19637,37 @@
         <v>69</v>
       </c>
       <c r="W18" s="144">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="X18" s="13"/>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="149" t="s">
+      <c r="A19" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="147"/>
-      <c r="C19" s="147"/>
-      <c r="D19" s="147"/>
-      <c r="E19" s="147"/>
-      <c r="F19" s="147"/>
-      <c r="G19" s="147"/>
-      <c r="H19" s="147"/>
-      <c r="I19" s="147"/>
-      <c r="J19" s="147"/>
-      <c r="K19" s="147"/>
-      <c r="L19" s="147"/>
-      <c r="M19" s="147"/>
-      <c r="N19" s="147"/>
-      <c r="O19" s="147"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="147"/>
-      <c r="T19" s="147"/>
-      <c r="U19" s="147"/>
-      <c r="V19" s="147"/>
-      <c r="W19" s="147"/>
-      <c r="X19" s="147"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="149"/>
+      <c r="G19" s="149"/>
+      <c r="H19" s="149"/>
+      <c r="I19" s="149"/>
+      <c r="J19" s="149"/>
+      <c r="K19" s="149"/>
+      <c r="L19" s="149"/>
+      <c r="M19" s="149"/>
+      <c r="N19" s="149"/>
+      <c r="O19" s="149"/>
+      <c r="P19" s="149"/>
+      <c r="Q19" s="149"/>
+      <c r="R19" s="149"/>
+      <c r="S19" s="149"/>
+      <c r="T19" s="149"/>
+      <c r="U19" s="149"/>
+      <c r="V19" s="149"/>
+      <c r="W19" s="149"/>
+      <c r="X19" s="149"/>
     </row>
     <row r="20" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
@@ -19633,7 +19735,7 @@
         <v>1739</v>
       </c>
       <c r="W20" s="11">
-        <v>916</v>
+        <v>1265</v>
       </c>
       <c r="X20" s="11"/>
     </row>
@@ -19703,7 +19805,7 @@
         <v>457245</v>
       </c>
       <c r="W21" s="11">
-        <v>454269</v>
+        <v>480004</v>
       </c>
       <c r="X21" s="11"/>
     </row>
@@ -19773,7 +19875,7 @@
         <v>0.67849999999999999</v>
       </c>
       <c r="W22" s="13">
-        <v>0.69450000000000001</v>
+        <v>0.69579999999999997</v>
       </c>
       <c r="X22" s="13"/>
     </row>
@@ -19843,7 +19945,7 @@
         <v>458</v>
       </c>
       <c r="W23" s="11">
-        <v>273</v>
+        <v>382</v>
       </c>
       <c r="X23" s="11"/>
     </row>
@@ -19913,7 +20015,7 @@
         <v>410866</v>
       </c>
       <c r="W24" s="11">
-        <v>417935</v>
+        <v>448219</v>
       </c>
       <c r="X24" s="11"/>
     </row>
@@ -19983,7 +20085,7 @@
         <v>520</v>
       </c>
       <c r="W25" s="11">
-        <v>266</v>
+        <v>366</v>
       </c>
       <c r="X25" s="11"/>
     </row>
@@ -20053,7 +20155,7 @@
         <v>472067</v>
       </c>
       <c r="W26" s="11">
-        <v>486224</v>
+        <v>512299</v>
       </c>
       <c r="X26" s="11"/>
     </row>
@@ -20123,7 +20225,7 @@
         <v>761</v>
       </c>
       <c r="W27" s="11">
-        <v>377</v>
+        <v>517</v>
       </c>
       <c r="X27" s="11"/>
     </row>
@@ -20193,37 +20295,37 @@
         <v>476924</v>
       </c>
       <c r="W28" s="11">
-        <v>458033</v>
+        <v>480626</v>
       </c>
       <c r="X28" s="11"/>
     </row>
     <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="149" t="s">
+      <c r="A29" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="147"/>
-      <c r="C29" s="147"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="147"/>
-      <c r="G29" s="147"/>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="147"/>
-      <c r="K29" s="147"/>
-      <c r="L29" s="147"/>
-      <c r="M29" s="147"/>
-      <c r="N29" s="147"/>
-      <c r="O29" s="147"/>
-      <c r="P29" s="147"/>
-      <c r="Q29" s="147"/>
-      <c r="R29" s="147"/>
-      <c r="S29" s="147"/>
-      <c r="T29" s="147"/>
-      <c r="U29" s="147"/>
-      <c r="V29" s="147"/>
-      <c r="W29" s="147"/>
-      <c r="X29" s="147"/>
+      <c r="B29" s="149"/>
+      <c r="C29" s="149"/>
+      <c r="D29" s="149"/>
+      <c r="E29" s="149"/>
+      <c r="F29" s="149"/>
+      <c r="G29" s="149"/>
+      <c r="H29" s="149"/>
+      <c r="I29" s="149"/>
+      <c r="J29" s="149"/>
+      <c r="K29" s="149"/>
+      <c r="L29" s="149"/>
+      <c r="M29" s="149"/>
+      <c r="N29" s="149"/>
+      <c r="O29" s="149"/>
+      <c r="P29" s="149"/>
+      <c r="Q29" s="149"/>
+      <c r="R29" s="149"/>
+      <c r="S29" s="149"/>
+      <c r="T29" s="149"/>
+      <c r="U29" s="149"/>
+      <c r="V29" s="149"/>
+      <c r="W29" s="149"/>
+      <c r="X29" s="149"/>
     </row>
     <row r="30" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
@@ -20291,7 +20393,7 @@
         <v>1788</v>
       </c>
       <c r="W30" s="11">
-        <v>743</v>
+        <v>1031</v>
       </c>
       <c r="X30" s="11"/>
     </row>
@@ -20361,7 +20463,7 @@
         <v>452381</v>
       </c>
       <c r="W31" s="11">
-        <v>477771</v>
+        <v>505837</v>
       </c>
       <c r="X31" s="11"/>
     </row>
@@ -20431,65 +20533,65 @@
         <v>1589471</v>
       </c>
       <c r="W32" s="11">
-        <v>1579126</v>
+        <v>1668585</v>
       </c>
       <c r="X32" s="11"/>
     </row>
     <row r="33" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="153" t="s">
+      <c r="A33" s="157" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="147"/>
-      <c r="C33" s="147"/>
-      <c r="D33" s="147"/>
-      <c r="E33" s="147"/>
-      <c r="F33" s="147"/>
-      <c r="G33" s="147"/>
-      <c r="H33" s="147"/>
-      <c r="I33" s="147"/>
-      <c r="J33" s="147"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="147"/>
-      <c r="M33" s="147"/>
-      <c r="N33" s="147"/>
-      <c r="O33" s="147"/>
-      <c r="P33" s="147"/>
-      <c r="Q33" s="147"/>
-      <c r="R33" s="147"/>
-      <c r="S33" s="147"/>
-      <c r="T33" s="147"/>
-      <c r="U33" s="147"/>
-      <c r="V33" s="147"/>
-      <c r="W33" s="147"/>
-      <c r="X33" s="147"/>
+      <c r="B33" s="149"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="149"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="149"/>
+      <c r="G33" s="149"/>
+      <c r="H33" s="149"/>
+      <c r="I33" s="149"/>
+      <c r="J33" s="149"/>
+      <c r="K33" s="149"/>
+      <c r="L33" s="149"/>
+      <c r="M33" s="149"/>
+      <c r="N33" s="149"/>
+      <c r="O33" s="149"/>
+      <c r="P33" s="149"/>
+      <c r="Q33" s="149"/>
+      <c r="R33" s="149"/>
+      <c r="S33" s="149"/>
+      <c r="T33" s="149"/>
+      <c r="U33" s="149"/>
+      <c r="V33" s="149"/>
+      <c r="W33" s="149"/>
+      <c r="X33" s="149"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="155" t="s">
+      <c r="A34" s="148" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="147"/>
-      <c r="C34" s="147"/>
-      <c r="D34" s="147"/>
-      <c r="E34" s="147"/>
-      <c r="F34" s="147"/>
-      <c r="G34" s="147"/>
-      <c r="H34" s="147"/>
-      <c r="I34" s="147"/>
-      <c r="J34" s="147"/>
-      <c r="K34" s="147"/>
-      <c r="L34" s="147"/>
-      <c r="M34" s="147"/>
-      <c r="N34" s="147"/>
-      <c r="O34" s="147"/>
-      <c r="P34" s="147"/>
-      <c r="Q34" s="147"/>
-      <c r="R34" s="147"/>
-      <c r="S34" s="147"/>
-      <c r="T34" s="147"/>
-      <c r="U34" s="147"/>
-      <c r="V34" s="147"/>
-      <c r="W34" s="147"/>
-      <c r="X34" s="147"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="149"/>
+      <c r="E34" s="149"/>
+      <c r="F34" s="149"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="149"/>
+      <c r="I34" s="149"/>
+      <c r="J34" s="149"/>
+      <c r="K34" s="149"/>
+      <c r="L34" s="149"/>
+      <c r="M34" s="149"/>
+      <c r="N34" s="149"/>
+      <c r="O34" s="149"/>
+      <c r="P34" s="149"/>
+      <c r="Q34" s="149"/>
+      <c r="R34" s="149"/>
+      <c r="S34" s="149"/>
+      <c r="T34" s="149"/>
+      <c r="U34" s="149"/>
+      <c r="V34" s="149"/>
+      <c r="W34" s="149"/>
+      <c r="X34" s="149"/>
     </row>
     <row r="35" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="20"/>
@@ -20557,7 +20659,7 @@
         <v>530083436</v>
       </c>
       <c r="W35" s="8">
-        <v>257031320</v>
+        <v>352971080</v>
       </c>
       <c r="X35" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!G$6:I$35),0)</f>
@@ -20630,7 +20732,7 @@
         <v>272494091</v>
       </c>
       <c r="W36" s="8">
-        <v>123880693</v>
+        <v>175795691</v>
       </c>
       <c r="X36" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!G$6:G$35),0)</f>
@@ -20703,7 +20805,7 @@
         <v>129188093</v>
       </c>
       <c r="W37" s="8">
-        <v>69200862</v>
+        <v>91194124</v>
       </c>
       <c r="X37" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!H$6:H$35),0)</f>
@@ -20776,7 +20878,7 @@
         <v>128401252</v>
       </c>
       <c r="W38" s="8">
-        <v>63949765</v>
+        <v>85981265</v>
       </c>
       <c r="X38" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!I$6:I$35),0)</f>
@@ -20849,7 +20951,7 @@
         <v>1717</v>
       </c>
       <c r="W39" s="8">
-        <v>848</v>
+        <v>1134</v>
       </c>
       <c r="X39" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!J$6:J$35),0)</f>
@@ -20922,7 +21024,7 @@
         <v>308727</v>
       </c>
       <c r="W40" s="8">
-        <v>303103</v>
+        <v>311260</v>
       </c>
       <c r="X40" s="8" t="str">
         <f>IFERROR(SUM('📅 DAILY T9'!M$6:M$35)/SUM('📅 DAILY T9'!J$6:J$35),"")</f>
@@ -20930,56 +21032,56 @@
       </c>
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="151"/>
-      <c r="B41" s="147"/>
-      <c r="C41" s="147"/>
-      <c r="D41" s="147"/>
-      <c r="E41" s="147"/>
-      <c r="F41" s="147"/>
-      <c r="G41" s="147"/>
-      <c r="H41" s="147"/>
-      <c r="I41" s="147"/>
-      <c r="J41" s="147"/>
-      <c r="K41" s="147"/>
-      <c r="L41" s="147"/>
-      <c r="M41" s="147"/>
-      <c r="N41" s="147"/>
-      <c r="O41" s="147"/>
-      <c r="P41" s="147"/>
-      <c r="Q41" s="147"/>
-      <c r="R41" s="147"/>
-      <c r="S41" s="147"/>
-      <c r="T41" s="147"/>
-      <c r="U41" s="147"/>
-      <c r="V41" s="147"/>
-      <c r="W41" s="147"/>
-      <c r="X41" s="152"/>
+      <c r="A41" s="156"/>
+      <c r="B41" s="149"/>
+      <c r="C41" s="149"/>
+      <c r="D41" s="149"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="149"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="149"/>
+      <c r="I41" s="149"/>
+      <c r="J41" s="149"/>
+      <c r="K41" s="149"/>
+      <c r="L41" s="149"/>
+      <c r="M41" s="149"/>
+      <c r="N41" s="149"/>
+      <c r="O41" s="149"/>
+      <c r="P41" s="149"/>
+      <c r="Q41" s="149"/>
+      <c r="R41" s="149"/>
+      <c r="S41" s="149"/>
+      <c r="T41" s="149"/>
+      <c r="U41" s="149"/>
+      <c r="V41" s="149"/>
+      <c r="W41" s="149"/>
+      <c r="X41" s="151"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="151"/>
-      <c r="B42" s="147"/>
-      <c r="C42" s="147"/>
-      <c r="D42" s="147"/>
-      <c r="E42" s="147"/>
-      <c r="F42" s="147"/>
-      <c r="G42" s="147"/>
-      <c r="H42" s="147"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="147"/>
-      <c r="K42" s="147"/>
-      <c r="L42" s="147"/>
-      <c r="M42" s="147"/>
-      <c r="N42" s="147"/>
-      <c r="O42" s="147"/>
-      <c r="P42" s="147"/>
-      <c r="Q42" s="147"/>
-      <c r="R42" s="147"/>
-      <c r="S42" s="147"/>
-      <c r="T42" s="147"/>
-      <c r="U42" s="147"/>
-      <c r="V42" s="147"/>
-      <c r="W42" s="147"/>
-      <c r="X42" s="152"/>
+      <c r="A42" s="156"/>
+      <c r="B42" s="149"/>
+      <c r="C42" s="149"/>
+      <c r="D42" s="149"/>
+      <c r="E42" s="149"/>
+      <c r="F42" s="149"/>
+      <c r="G42" s="149"/>
+      <c r="H42" s="149"/>
+      <c r="I42" s="149"/>
+      <c r="J42" s="149"/>
+      <c r="K42" s="149"/>
+      <c r="L42" s="149"/>
+      <c r="M42" s="149"/>
+      <c r="N42" s="149"/>
+      <c r="O42" s="149"/>
+      <c r="P42" s="149"/>
+      <c r="Q42" s="149"/>
+      <c r="R42" s="149"/>
+      <c r="S42" s="149"/>
+      <c r="T42" s="149"/>
+      <c r="U42" s="149"/>
+      <c r="V42" s="149"/>
+      <c r="W42" s="149"/>
+      <c r="X42" s="151"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -21047,7 +21149,7 @@
         <v>613</v>
       </c>
       <c r="W43" s="11">
-        <v>275</v>
+        <v>373</v>
       </c>
       <c r="X43" s="11"/>
     </row>
@@ -21117,7 +21219,7 @@
         <v>301500</v>
       </c>
       <c r="W44" s="11">
-        <v>343147</v>
+        <v>346270</v>
       </c>
       <c r="X44" s="11"/>
     </row>
@@ -21127,7 +21229,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D45" s="145">
         <v>167</v>
@@ -21187,7 +21289,7 @@
         <v>130</v>
       </c>
       <c r="W45" s="49">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="X45" s="13"/>
     </row>
@@ -21197,7 +21299,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D46" s="145">
         <v>72</v>
@@ -21257,37 +21359,37 @@
         <v>35</v>
       </c>
       <c r="W46" s="49">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="X46" s="13"/>
     </row>
     <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="149" t="s">
+      <c r="A47" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="147"/>
-      <c r="C47" s="147"/>
-      <c r="D47" s="147"/>
-      <c r="E47" s="147"/>
-      <c r="F47" s="147"/>
-      <c r="G47" s="147"/>
-      <c r="H47" s="147"/>
-      <c r="I47" s="147"/>
-      <c r="J47" s="147"/>
-      <c r="K47" s="147"/>
-      <c r="L47" s="147"/>
-      <c r="M47" s="147"/>
-      <c r="N47" s="147"/>
-      <c r="O47" s="147"/>
-      <c r="P47" s="147"/>
-      <c r="Q47" s="147"/>
-      <c r="R47" s="147"/>
-      <c r="S47" s="147"/>
-      <c r="T47" s="147"/>
-      <c r="U47" s="147"/>
-      <c r="V47" s="147"/>
-      <c r="W47" s="147"/>
-      <c r="X47" s="147"/>
+      <c r="B47" s="149"/>
+      <c r="C47" s="149"/>
+      <c r="D47" s="149"/>
+      <c r="E47" s="149"/>
+      <c r="F47" s="149"/>
+      <c r="G47" s="149"/>
+      <c r="H47" s="149"/>
+      <c r="I47" s="149"/>
+      <c r="J47" s="149"/>
+      <c r="K47" s="149"/>
+      <c r="L47" s="149"/>
+      <c r="M47" s="149"/>
+      <c r="N47" s="149"/>
+      <c r="O47" s="149"/>
+      <c r="P47" s="149"/>
+      <c r="Q47" s="149"/>
+      <c r="R47" s="149"/>
+      <c r="S47" s="149"/>
+      <c r="T47" s="149"/>
+      <c r="U47" s="149"/>
+      <c r="V47" s="149"/>
+      <c r="W47" s="149"/>
+      <c r="X47" s="149"/>
     </row>
     <row r="48" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="20"/>
@@ -21355,7 +21457,7 @@
         <v>801</v>
       </c>
       <c r="W48" s="11">
-        <v>474</v>
+        <v>613</v>
       </c>
       <c r="X48" s="11"/>
     </row>
@@ -21425,7 +21527,7 @@
         <v>337816</v>
       </c>
       <c r="W49" s="11">
-        <v>343177</v>
+        <v>367130</v>
       </c>
       <c r="X49" s="11"/>
     </row>
@@ -21495,7 +21597,7 @@
         <v>0.5665</v>
       </c>
       <c r="W50" s="13">
-        <v>0.63280000000000003</v>
+        <v>0.62170000000000003</v>
       </c>
       <c r="X50" s="13"/>
     </row>
@@ -21565,7 +21667,7 @@
         <v>181</v>
       </c>
       <c r="W51" s="11">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="X51" s="11"/>
     </row>
@@ -21635,7 +21737,7 @@
         <v>314399</v>
       </c>
       <c r="W52" s="11">
-        <v>381782</v>
+        <v>465910</v>
       </c>
       <c r="X52" s="11"/>
     </row>
@@ -21705,7 +21807,7 @@
         <v>229</v>
       </c>
       <c r="W53" s="11">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="X53" s="11"/>
     </row>
@@ -21775,7 +21877,7 @@
         <v>330301</v>
       </c>
       <c r="W54" s="11">
-        <v>350200</v>
+        <v>359365</v>
       </c>
       <c r="X54" s="11"/>
     </row>
@@ -21845,7 +21947,7 @@
         <v>391</v>
       </c>
       <c r="W55" s="11">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="X55" s="11"/>
     </row>
@@ -21915,37 +22017,37 @@
         <v>354566</v>
       </c>
       <c r="W56" s="11">
-        <v>321981</v>
+        <v>327039</v>
       </c>
       <c r="X56" s="11"/>
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="149" t="s">
+      <c r="A57" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="B57" s="147"/>
-      <c r="C57" s="147"/>
-      <c r="D57" s="147"/>
-      <c r="E57" s="147"/>
-      <c r="F57" s="147"/>
-      <c r="G57" s="147"/>
-      <c r="H57" s="147"/>
-      <c r="I57" s="147"/>
-      <c r="J57" s="147"/>
-      <c r="K57" s="147"/>
-      <c r="L57" s="147"/>
-      <c r="M57" s="147"/>
-      <c r="N57" s="147"/>
-      <c r="O57" s="147"/>
-      <c r="P57" s="147"/>
-      <c r="Q57" s="147"/>
-      <c r="R57" s="147"/>
-      <c r="S57" s="147"/>
-      <c r="T57" s="147"/>
-      <c r="U57" s="147"/>
-      <c r="V57" s="147"/>
-      <c r="W57" s="147"/>
-      <c r="X57" s="147"/>
+      <c r="B57" s="149"/>
+      <c r="C57" s="149"/>
+      <c r="D57" s="149"/>
+      <c r="E57" s="149"/>
+      <c r="F57" s="149"/>
+      <c r="G57" s="149"/>
+      <c r="H57" s="149"/>
+      <c r="I57" s="149"/>
+      <c r="J57" s="149"/>
+      <c r="K57" s="149"/>
+      <c r="L57" s="149"/>
+      <c r="M57" s="149"/>
+      <c r="N57" s="149"/>
+      <c r="O57" s="149"/>
+      <c r="P57" s="149"/>
+      <c r="Q57" s="149"/>
+      <c r="R57" s="149"/>
+      <c r="S57" s="149"/>
+      <c r="T57" s="149"/>
+      <c r="U57" s="149"/>
+      <c r="V57" s="149"/>
+      <c r="W57" s="149"/>
+      <c r="X57" s="149"/>
     </row>
     <row r="58" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="20"/>
@@ -22013,7 +22115,7 @@
         <v>832</v>
       </c>
       <c r="W58" s="11">
-        <v>338</v>
+        <v>447</v>
       </c>
       <c r="X58" s="11"/>
     </row>
@@ -22083,7 +22185,7 @@
         <v>320520</v>
       </c>
       <c r="W59" s="11">
-        <v>363938</v>
+        <v>392773</v>
       </c>
       <c r="X59" s="11"/>
     </row>
@@ -22153,7 +22255,7 @@
         <v>1233028</v>
       </c>
       <c r="W60" s="11">
-        <v>1252596</v>
+        <v>1340024</v>
       </c>
       <c r="X60" s="11"/>
     </row>
@@ -22233,7 +22335,7 @@
         <v>40164072</v>
       </c>
       <c r="W63" s="8">
-        <v>12386427</v>
+        <v>16227627</v>
       </c>
       <c r="X63" s="8"/>
     </row>
@@ -22303,7 +22405,7 @@
         <v>2.3313380602290611E-2</v>
       </c>
       <c r="W64" s="132">
-        <v>1.468E-2</v>
+        <v>1.3549E-2</v>
       </c>
       <c r="X64" s="8"/>
     </row>
@@ -22430,7 +22532,7 @@
         <v>1722790559</v>
       </c>
       <c r="W68" s="8">
-        <v>843934361</v>
+        <v>1197681060</v>
       </c>
       <c r="X68" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)+SUM('📅 DAILY T9'!G$6:I$35),0)</f>
@@ -22438,30 +22540,30 @@
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="154"/>
-      <c r="B69" s="147"/>
-      <c r="C69" s="147"/>
-      <c r="D69" s="147"/>
-      <c r="E69" s="147"/>
-      <c r="F69" s="147"/>
-      <c r="G69" s="147"/>
-      <c r="H69" s="147"/>
-      <c r="I69" s="147"/>
-      <c r="J69" s="147"/>
-      <c r="K69" s="147"/>
-      <c r="L69" s="147"/>
-      <c r="M69" s="147"/>
-      <c r="N69" s="147"/>
-      <c r="O69" s="147"/>
-      <c r="P69" s="147"/>
-      <c r="Q69" s="147"/>
-      <c r="R69" s="147"/>
-      <c r="S69" s="147"/>
-      <c r="T69" s="147"/>
-      <c r="U69" s="147"/>
-      <c r="V69" s="147"/>
-      <c r="W69" s="147"/>
-      <c r="X69" s="152"/>
+      <c r="A69" s="150"/>
+      <c r="B69" s="149"/>
+      <c r="C69" s="149"/>
+      <c r="D69" s="149"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="149"/>
+      <c r="H69" s="149"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="149"/>
+      <c r="K69" s="149"/>
+      <c r="L69" s="149"/>
+      <c r="M69" s="149"/>
+      <c r="N69" s="149"/>
+      <c r="O69" s="149"/>
+      <c r="P69" s="149"/>
+      <c r="Q69" s="149"/>
+      <c r="R69" s="149"/>
+      <c r="S69" s="149"/>
+      <c r="T69" s="149"/>
+      <c r="U69" s="149"/>
+      <c r="V69" s="149"/>
+      <c r="W69" s="149"/>
+      <c r="X69" s="151"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="25"/>
@@ -22529,7 +22631,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="W70" s="14">
-        <v>1.0900000000000001</v>
+        <v>1.1180000000000001</v>
       </c>
       <c r="X70" s="14"/>
     </row>
@@ -22599,7 +22701,7 @@
         <v>19927</v>
       </c>
       <c r="W71" s="11">
-        <v>19442</v>
+        <v>19923</v>
       </c>
       <c r="X71" s="11"/>
     </row>
@@ -22669,7 +22771,7 @@
         <v>1493</v>
       </c>
       <c r="W72" s="11">
-        <v>715</v>
+        <v>1024</v>
       </c>
       <c r="X72" s="11"/>
     </row>
@@ -22739,7 +22841,7 @@
         <v>97</v>
       </c>
       <c r="W73" s="28">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="X73" s="28">
         <v>98</v>
@@ -22875,7 +22977,7 @@
         <v>99</v>
       </c>
       <c r="W75">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="X75">
         <v>100</v>
@@ -22975,7 +23077,7 @@
         <v>1296094</v>
       </c>
       <c r="W77" s="11">
-        <v>1287658</v>
+        <v>605581</v>
       </c>
       <c r="X77" s="11"/>
     </row>
@@ -23045,7 +23147,7 @@
         <v>811265</v>
       </c>
       <c r="W78" s="11">
-        <v>824140</v>
+        <v>370238</v>
       </c>
       <c r="X78" s="11"/>
     </row>
@@ -23115,7 +23217,7 @@
         <v>1589471</v>
       </c>
       <c r="W79" s="11">
-        <v>1579126</v>
+        <v>1668585</v>
       </c>
       <c r="X79" s="11"/>
     </row>
@@ -23185,37 +23287,37 @@
         <v>1233028</v>
       </c>
       <c r="W80" s="11">
-        <v>1252596</v>
+        <v>1340024</v>
       </c>
       <c r="X80" s="11"/>
     </row>
     <row r="81" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="157" t="s">
+      <c r="A81" s="154" t="s">
         <v>93</v>
       </c>
-      <c r="B81" s="147"/>
-      <c r="C81" s="147"/>
-      <c r="D81" s="147"/>
-      <c r="E81" s="147"/>
-      <c r="F81" s="147"/>
-      <c r="G81" s="147"/>
-      <c r="H81" s="147"/>
-      <c r="I81" s="147"/>
-      <c r="J81" s="147"/>
-      <c r="K81" s="147"/>
-      <c r="L81" s="147"/>
-      <c r="M81" s="147"/>
-      <c r="N81" s="147"/>
-      <c r="O81" s="147"/>
-      <c r="P81" s="147"/>
-      <c r="Q81" s="147"/>
-      <c r="R81" s="147"/>
-      <c r="S81" s="147"/>
-      <c r="T81" s="147"/>
-      <c r="U81" s="147"/>
-      <c r="V81" s="147"/>
-      <c r="W81" s="147"/>
-      <c r="X81" s="147"/>
+      <c r="B81" s="149"/>
+      <c r="C81" s="149"/>
+      <c r="D81" s="149"/>
+      <c r="E81" s="149"/>
+      <c r="F81" s="149"/>
+      <c r="G81" s="149"/>
+      <c r="H81" s="149"/>
+      <c r="I81" s="149"/>
+      <c r="J81" s="149"/>
+      <c r="K81" s="149"/>
+      <c r="L81" s="149"/>
+      <c r="M81" s="149"/>
+      <c r="N81" s="149"/>
+      <c r="O81" s="149"/>
+      <c r="P81" s="149"/>
+      <c r="Q81" s="149"/>
+      <c r="R81" s="149"/>
+      <c r="S81" s="149"/>
+      <c r="T81" s="149"/>
+      <c r="U81" s="149"/>
+      <c r="V81" s="149"/>
+      <c r="W81" s="149"/>
+      <c r="X81" s="149"/>
     </row>
     <row r="82" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="29"/>
@@ -23515,14 +23617,8 @@
     <row r="200" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A69:X69"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A29:X29"/>
-    <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A81:X81"/>
-    <mergeCell ref="A57:X57"/>
-    <mergeCell ref="A47:X47"/>
     <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A5:X5"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A14:X14"/>
     <mergeCell ref="A2:X2"/>
@@ -23530,7 +23626,13 @@
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
-    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="A69:X69"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A4:X4"/>
+    <mergeCell ref="A81:X81"/>
+    <mergeCell ref="A57:X57"/>
+    <mergeCell ref="A47:X47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23561,66 +23663,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>495</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -23630,11 +23732,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -23696,7 +23798,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1258798314</v>
       </c>
@@ -25098,40 +25200,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>496</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="176" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -25465,66 +25567,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>502</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -25534,11 +25636,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -25600,7 +25702,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1625138977</v>
       </c>
@@ -26975,40 +27077,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>503</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="176" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -27393,66 +27495,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>510</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -27462,11 +27564,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -27528,7 +27630,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41">
         <v>1965067740</v>
       </c>
@@ -28930,40 +29032,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>511</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="174" t="s">
+      <c r="A2" s="176" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="116" t="s">
@@ -29288,19 +29390,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>517</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
     </row>
     <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="178" t="s">
+      <c r="A3" s="180" t="s">
         <v>518</v>
       </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
     </row>
     <row r="4" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
@@ -29358,11 +29460,11 @@
     </row>
     <row r="10" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="176" t="s">
+      <c r="A11" s="178" t="s">
         <v>531</v>
       </c>
-      <c r="B11" s="147"/>
-      <c r="C11" s="147"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="149"/>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="90"/>
@@ -29402,11 +29504,11 @@
     </row>
     <row r="16" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="177" t="s">
+      <c r="A17" s="179" t="s">
         <v>540</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="149"/>
     </row>
     <row r="18" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="93"/>
@@ -29455,11 +29557,11 @@
     </row>
     <row r="23" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="179" t="s">
+      <c r="A24" s="181" t="s">
         <v>551</v>
       </c>
-      <c r="B24" s="147"/>
-      <c r="C24" s="147"/>
+      <c r="B24" s="149"/>
+      <c r="C24" s="149"/>
     </row>
     <row r="25" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="96"/>
@@ -29732,7 +29834,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -29747,40 +29849,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="159"/>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-      <c r="L1" s="159"/>
-      <c r="M1" s="159"/>
-      <c r="N1" s="159"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
+      <c r="K1" s="161"/>
+      <c r="L1" s="161"/>
+      <c r="M1" s="161"/>
+      <c r="N1" s="161"/>
     </row>
     <row r="2" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="183" t="s">
         <v>573</v>
       </c>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="99" t="s">
@@ -29827,22 +29929,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="182" t="s">
         <v>588</v>
       </c>
-      <c r="B4" s="159"/>
-      <c r="C4" s="159"/>
-      <c r="D4" s="159"/>
-      <c r="E4" s="159"/>
-      <c r="F4" s="159"/>
-      <c r="G4" s="159"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="159"/>
-      <c r="J4" s="159"/>
-      <c r="K4" s="159"/>
-      <c r="L4" s="159"/>
-      <c r="M4" s="159"/>
-      <c r="N4" s="159"/>
+      <c r="B4" s="161"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="100" t="s">
@@ -32648,40 +32750,40 @@
         <v>610</v>
       </c>
       <c r="C80" s="108">
-        <v>438</v>
+        <v>596</v>
       </c>
       <c r="D80" s="108">
-        <v>176</v>
+        <v>229</v>
       </c>
       <c r="E80" s="108">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F80" s="108">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="G80" s="108">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H80" s="108">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="I80" s="108">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J80" s="108">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K80" s="108">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L80" s="108">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="M80" s="108">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N80" s="108">
-        <v>198</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -32692,40 +32794,40 @@
         <v>611</v>
       </c>
       <c r="C81">
-        <v>605</v>
+        <v>838</v>
       </c>
       <c r="D81">
-        <v>442</v>
+        <v>623</v>
       </c>
       <c r="E81">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F81">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G81">
+        <v>7</v>
+      </c>
+      <c r="H81">
+        <v>17</v>
+      </c>
+      <c r="I81">
         <v>4</v>
-      </c>
-      <c r="H81">
-        <v>11</v>
-      </c>
-      <c r="I81">
-        <v>3</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L81">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="M81">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="N81">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -32736,22 +32838,22 @@
         <v>612</v>
       </c>
       <c r="C82" s="102">
-        <v>322</v>
+        <v>446</v>
       </c>
       <c r="D82" s="103">
-        <v>269</v>
+        <v>365</v>
       </c>
       <c r="E82" s="103">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F82" s="103">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G82" s="103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82" s="103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I82" s="103">
         <v>0</v>
@@ -32760,16 +32862,16 @@
         <v>0</v>
       </c>
       <c r="K82" s="105">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="L82" s="105">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="M82" s="105">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="N82" s="105">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -35529,43 +35631,43 @@
         <v>24</v>
       </c>
       <c r="B157" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="C157">
-        <v>382</v>
+        <v>596</v>
       </c>
       <c r="D157">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="E157">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F157">
+        <v>135</v>
+      </c>
+      <c r="G157">
+        <v>18</v>
+      </c>
+      <c r="H157">
+        <v>67</v>
+      </c>
+      <c r="I157">
+        <v>44</v>
+      </c>
+      <c r="J157">
+        <v>29</v>
+      </c>
+      <c r="K157">
+        <v>15</v>
+      </c>
+      <c r="L157">
+        <v>107</v>
+      </c>
+      <c r="M157">
+        <v>7</v>
+      </c>
+      <c r="N157">
         <v>72</v>
-      </c>
-      <c r="G157">
-        <v>13</v>
-      </c>
-      <c r="H157">
-        <v>32</v>
-      </c>
-      <c r="I157">
-        <v>10</v>
-      </c>
-      <c r="J157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <v>16</v>
-      </c>
-      <c r="L157">
-        <v>93</v>
-      </c>
-      <c r="M157">
-        <v>15</v>
-      </c>
-      <c r="N157">
-        <v>156</v>
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
@@ -35573,43 +35675,43 @@
         <v>24</v>
       </c>
       <c r="B158" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="C158">
-        <v>306</v>
+        <v>834</v>
       </c>
       <c r="D158">
-        <v>273</v>
+        <v>620</v>
       </c>
       <c r="E158">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="F158">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I158">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
       <c r="K158">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="L158">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="M158">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="N158">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
@@ -35617,25 +35719,25 @@
         <v>24</v>
       </c>
       <c r="B159" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="C159">
-        <v>150</v>
+        <v>443</v>
       </c>
       <c r="D159">
-        <v>139</v>
+        <v>362</v>
       </c>
       <c r="E159">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I159">
         <v>0</v>
@@ -35644,16 +35746,197 @@
         <v>0</v>
       </c>
       <c r="K159">
+        <v>92</v>
+      </c>
+      <c r="L159">
         <v>36</v>
       </c>
-      <c r="L159">
-        <v>12</v>
-      </c>
       <c r="M159">
+        <v>58</v>
+      </c>
+      <c r="N159">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A161" s="146" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A162" s="147" t="s">
+        <v>574</v>
+      </c>
+      <c r="B162" s="147" t="s">
+        <v>575</v>
+      </c>
+      <c r="C162" s="147" t="s">
+        <v>576</v>
+      </c>
+      <c r="D162" s="147" t="s">
+        <v>577</v>
+      </c>
+      <c r="E162" s="147" t="s">
+        <v>578</v>
+      </c>
+      <c r="F162" s="147" t="s">
+        <v>579</v>
+      </c>
+      <c r="G162" s="147" t="s">
+        <v>580</v>
+      </c>
+      <c r="H162" s="147" t="s">
+        <v>581</v>
+      </c>
+      <c r="I162" s="147" t="s">
+        <v>582</v>
+      </c>
+      <c r="J162" s="147" t="s">
+        <v>583</v>
+      </c>
+      <c r="K162" s="147" t="s">
+        <v>584</v>
+      </c>
+      <c r="L162" s="147" t="s">
+        <v>585</v>
+      </c>
+      <c r="M162" s="147" t="s">
+        <v>586</v>
+      </c>
+      <c r="N162" s="147" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
         <v>24</v>
       </c>
-      <c r="N159">
+      <c r="B163" t="s">
+        <v>590</v>
+      </c>
+      <c r="C163">
+        <v>234</v>
+      </c>
+      <c r="D163">
+        <v>222</v>
+      </c>
+      <c r="E163">
+        <v>8</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>2</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
         <v>24</v>
+      </c>
+      <c r="B164" t="s">
+        <v>591</v>
+      </c>
+      <c r="C164">
+        <v>39</v>
+      </c>
+      <c r="D164">
+        <v>38</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>24</v>
+      </c>
+      <c r="B165" t="s">
+        <v>592</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -35691,66 +35974,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>372</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -35760,11 +36043,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -35826,7 +36109,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -37581,66 +37864,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -37650,11 +37933,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -37716,7 +37999,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -39539,66 +39822,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>408</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -39608,11 +39891,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -39674,7 +39957,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -41455,66 +41738,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>409</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -41524,11 +41807,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -41590,7 +41873,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -43419,66 +43702,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>410</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -43488,11 +43771,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -43554,7 +43837,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -45371,66 +45654,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -45440,11 +45723,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -45506,7 +45789,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
@@ -47159,66 +47442,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="170" t="s">
         <v>412</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
+      <c r="B1" s="149"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="150" t="s">
+      <c r="A2" s="155" t="s">
         <v>373</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="149"/>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="169" t="s">
         <v>374</v>
       </c>
-      <c r="B3" s="147"/>
+      <c r="B3" s="149"/>
       <c r="C3" s="168" t="s">
         <v>375</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="164" t="s">
+      <c r="D3" s="149"/>
+      <c r="E3" s="171" t="s">
         <v>376</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="166" t="s">
         <v>377</v>
       </c>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="147"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="149"/>
+      <c r="J3" s="149"/>
       <c r="K3" s="31" t="s">
         <v>378</v>
       </c>
@@ -47228,11 +47511,11 @@
       <c r="M3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="N3" s="147"/>
+      <c r="N3" s="149"/>
       <c r="O3" s="165" t="s">
         <v>380</v>
       </c>
-      <c r="P3" s="147"/>
+      <c r="P3" s="149"/>
       <c r="Q3" s="33" t="s">
         <v>381</v>
       </c>
@@ -47294,7 +47577,7 @@
       <c r="A5" s="167" t="s">
         <v>399</v>
       </c>
-      <c r="B5" s="147"/>
+      <c r="B5" s="149"/>
       <c r="C5" s="41"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAA581D-6D08-B744-8ED7-CF787940771B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07C4ECF5-8558-BF4C-AA5F-8C145FD1F42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29480" yWindow="600" windowWidth="38320" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📖 ĐỊNH NGHĨA CHỈ SỐ" sheetId="1" r:id="rId1"/>
@@ -3451,13 +3451,26 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3465,19 +3478,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3491,6 +3491,12 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="47" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3507,22 +3513,16 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5238,7 +5238,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>449</v>
       </c>
       <c r="B1" s="149"/>
@@ -5259,7 +5259,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -5280,19 +5280,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -5304,11 +5304,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -5370,7 +5370,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -7136,7 +7136,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>450</v>
       </c>
       <c r="B1" s="149"/>
@@ -7157,7 +7157,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -7178,19 +7178,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -7202,11 +7202,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -7268,7 +7268,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -9075,7 +9075,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>451</v>
       </c>
       <c r="B1" s="149"/>
@@ -9096,7 +9096,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -9117,19 +9117,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -9141,11 +9141,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -9207,7 +9207,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -10988,7 +10988,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>452</v>
       </c>
       <c r="B1" s="149"/>
@@ -11004,7 +11004,7 @@
       <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>453</v>
       </c>
       <c r="B2" s="149"/>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>473</v>
       </c>
       <c r="B23" s="149"/>
@@ -11310,7 +11310,7 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="172" t="s">
+      <c r="A25" s="174" t="s">
         <v>474</v>
       </c>
       <c r="B25" s="149"/>
@@ -11327,7 +11327,7 @@
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="174" t="s">
+      <c r="A27" s="172" t="s">
         <v>475</v>
       </c>
       <c r="B27" s="149"/>
@@ -11340,7 +11340,7 @@
       <c r="I27" s="149"/>
       <c r="J27" s="149"/>
       <c r="K27" s="149"/>
-      <c r="L27" s="175"/>
+      <c r="L27" s="173"/>
       <c r="M27" s="79"/>
       <c r="N27" s="79"/>
       <c r="O27" s="79"/>
@@ -11573,7 +11573,7 @@
       <c r="T34" s="84"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="174" t="s">
+      <c r="A35" s="172" t="s">
         <v>499</v>
       </c>
       <c r="B35" s="149"/>
@@ -11586,7 +11586,7 @@
       <c r="I35" s="149"/>
       <c r="J35" s="149"/>
       <c r="K35" s="149"/>
-      <c r="L35" s="175"/>
+      <c r="L35" s="173"/>
       <c r="M35" s="84"/>
       <c r="N35" s="84"/>
       <c r="O35" s="84"/>
@@ -11862,11 +11862,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11897,7 +11897,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>503</v>
       </c>
       <c r="B1" s="149"/>
@@ -11918,7 +11918,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -11939,19 +11939,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -11963,11 +11963,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -12029,7 +12029,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -13863,7 +13863,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>504</v>
       </c>
       <c r="B1" s="149"/>
@@ -13879,7 +13879,7 @@
       <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>453</v>
       </c>
       <c r="B2" s="149"/>
@@ -14240,7 +14240,7 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>473</v>
       </c>
       <c r="B23" s="149"/>
@@ -14263,7 +14263,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="172" t="s">
+      <c r="A25" s="174" t="s">
         <v>474</v>
       </c>
       <c r="B25" s="149"/>
@@ -14489,7 +14489,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>511</v>
       </c>
       <c r="B1" s="149"/>
@@ -14510,7 +14510,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -14531,19 +14531,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -14555,11 +14555,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -14621,7 +14621,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -16451,7 +16451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>512</v>
       </c>
       <c r="B1" s="149"/>
@@ -16467,7 +16467,7 @@
       <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>453</v>
       </c>
       <c r="B2" s="149"/>
@@ -16867,7 +16867,7 @@
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="173" t="s">
+      <c r="A24" s="175" t="s">
         <v>473</v>
       </c>
       <c r="B24" s="149"/>
@@ -16890,7 +16890,7 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="172" t="s">
+      <c r="A26" s="174" t="s">
         <v>474</v>
       </c>
       <c r="B26" s="149"/>
@@ -17116,7 +17116,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>520</v>
       </c>
       <c r="B1" s="149"/>
@@ -17137,7 +17137,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -17158,19 +17158,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -17182,11 +17182,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -17248,7 +17248,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -17396,7 +17396,7 @@
         <v>439</v>
       </c>
       <c r="C8" s="49">
-        <v>27959291</v>
+        <v>28089291</v>
       </c>
       <c r="D8" s="49">
         <v>70</v>
@@ -17423,11 +17423,11 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" si="1"/>
-        <v>44392539</v>
+        <v>44522539</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="2"/>
-        <v>399418.44285714283</v>
+        <v>401275.58571428573</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="3"/>
@@ -17599,31 +17599,45 @@
       <c r="B12" s="48" t="s">
         <v>436</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
+      <c r="C12" s="49">
+        <v>35421885</v>
+      </c>
+      <c r="D12" s="49">
+        <v>83</v>
+      </c>
       <c r="E12" s="49"/>
       <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
+      <c r="G12" s="49">
+        <v>6254004</v>
+      </c>
+      <c r="H12" s="49">
+        <v>3830501</v>
+      </c>
+      <c r="I12" s="49">
+        <v>3769255</v>
+      </c>
+      <c r="J12" s="49">
+        <v>35</v>
+      </c>
+      <c r="K12" s="49">
+        <v>1028800</v>
+      </c>
       <c r="L12" s="50"/>
-      <c r="M12" s="8" t="str">
+      <c r="M12" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N12" s="8" t="str">
+        <v>13853760</v>
+      </c>
+      <c r="N12" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O12" s="8" t="str">
+        <v>49275645</v>
+      </c>
+      <c r="O12" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P12" s="8" t="str">
+        <v>426769.69879518071</v>
+      </c>
+      <c r="P12" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>395821.71428571426</v>
       </c>
       <c r="Q12" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17637,31 +17651,45 @@
       <c r="B13" s="48" t="s">
         <v>437</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
+      <c r="C13" s="49">
+        <v>36832306</v>
+      </c>
+      <c r="D13" s="49">
+        <v>85</v>
+      </c>
       <c r="E13" s="49"/>
       <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
+      <c r="G13" s="49">
+        <v>8823251</v>
+      </c>
+      <c r="H13" s="49">
+        <v>3697004</v>
+      </c>
+      <c r="I13" s="49">
+        <v>2528498</v>
+      </c>
+      <c r="J13" s="49">
+        <v>48</v>
+      </c>
+      <c r="K13" s="49">
+        <v>449999</v>
+      </c>
       <c r="L13" s="50"/>
-      <c r="M13" s="8" t="str">
+      <c r="M13" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N13" s="8" t="str">
+        <v>15048753</v>
+      </c>
+      <c r="N13" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O13" s="8" t="str">
+        <v>51881059</v>
+      </c>
+      <c r="O13" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P13" s="8" t="str">
+        <v>433321.24705882353</v>
+      </c>
+      <c r="P13" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>313515.6875</v>
       </c>
       <c r="Q13" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17675,31 +17703,43 @@
       <c r="B14" s="48" t="s">
         <v>438</v>
       </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
+      <c r="C14" s="49">
+        <v>43407044</v>
+      </c>
+      <c r="D14" s="49">
+        <v>75</v>
+      </c>
       <c r="E14" s="49"/>
       <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
+      <c r="G14" s="49">
+        <v>4526000</v>
+      </c>
+      <c r="H14" s="49">
+        <v>3158503</v>
+      </c>
+      <c r="I14" s="49">
+        <v>2158001</v>
+      </c>
+      <c r="J14" s="49">
+        <v>35</v>
+      </c>
       <c r="K14" s="49"/>
       <c r="L14" s="50"/>
-      <c r="M14" s="8" t="str">
+      <c r="M14" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N14" s="8" t="str">
+        <v>9842504</v>
+      </c>
+      <c r="N14" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O14" s="8" t="str">
+        <v>53249548</v>
+      </c>
+      <c r="O14" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P14" s="8" t="str">
+        <v>578760.58666666667</v>
+      </c>
+      <c r="P14" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>281214.40000000002</v>
       </c>
       <c r="Q14" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17713,31 +17753,45 @@
       <c r="B15" s="48" t="s">
         <v>439</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
+      <c r="C15" s="49">
+        <v>27762575</v>
+      </c>
+      <c r="D15" s="49">
+        <v>71</v>
+      </c>
       <c r="E15" s="49"/>
       <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
+      <c r="G15" s="49">
+        <v>2183500</v>
+      </c>
+      <c r="H15" s="49">
+        <v>5738502</v>
+      </c>
+      <c r="I15" s="49">
+        <v>2332749</v>
+      </c>
+      <c r="J15" s="49">
+        <v>35</v>
+      </c>
+      <c r="K15" s="49">
+        <v>1727207</v>
+      </c>
       <c r="L15" s="50"/>
-      <c r="M15" s="8" t="str">
+      <c r="M15" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N15" s="8" t="str">
+        <v>10254751</v>
+      </c>
+      <c r="N15" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O15" s="8" t="str">
+        <v>38017326</v>
+      </c>
+      <c r="O15" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P15" s="8" t="str">
+        <v>391022.18309859157</v>
+      </c>
+      <c r="P15" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>292992.88571428572</v>
       </c>
       <c r="Q15" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17751,31 +17805,45 @@
       <c r="B16" s="48" t="s">
         <v>440</v>
       </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
+      <c r="C16" s="49">
+        <v>39021786</v>
+      </c>
+      <c r="D16" s="49">
+        <v>89</v>
+      </c>
       <c r="E16" s="49"/>
       <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
+      <c r="G16" s="49">
+        <v>10870752</v>
+      </c>
+      <c r="H16" s="49">
+        <v>3791499</v>
+      </c>
+      <c r="I16" s="49">
+        <v>5493702</v>
+      </c>
+      <c r="J16" s="49">
+        <v>59</v>
+      </c>
+      <c r="K16" s="49">
+        <v>364700</v>
+      </c>
       <c r="L16" s="50"/>
-      <c r="M16" s="8" t="str">
+      <c r="M16" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N16" s="8" t="str">
+        <v>20155953</v>
+      </c>
+      <c r="N16" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O16" s="8" t="str">
+        <v>59177739</v>
+      </c>
+      <c r="O16" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P16" s="8" t="str">
+        <v>438447.03370786516</v>
+      </c>
+      <c r="P16" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>341626.32203389832</v>
       </c>
       <c r="Q16" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17789,31 +17857,43 @@
       <c r="B17" s="52" t="s">
         <v>441</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
+      <c r="C17" s="49">
+        <v>38341033</v>
+      </c>
+      <c r="D17" s="49">
+        <v>89</v>
+      </c>
       <c r="E17" s="49"/>
       <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
+      <c r="G17" s="49">
+        <v>9599257</v>
+      </c>
+      <c r="H17" s="49">
+        <v>3314753</v>
+      </c>
+      <c r="I17" s="49">
+        <v>4445351</v>
+      </c>
+      <c r="J17" s="49">
+        <v>62</v>
+      </c>
       <c r="K17" s="49"/>
       <c r="L17" s="50"/>
-      <c r="M17" s="8" t="str">
+      <c r="M17" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N17" s="8" t="str">
+        <v>17359361</v>
+      </c>
+      <c r="N17" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O17" s="8" t="str">
+        <v>55700394</v>
+      </c>
+      <c r="O17" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P17" s="8" t="str">
+        <v>430798.1235955056</v>
+      </c>
+      <c r="P17" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>279989.69354838709</v>
       </c>
       <c r="Q17" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17827,31 +17907,45 @@
       <c r="B18" s="52" t="s">
         <v>442</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
+      <c r="C18" s="49">
+        <v>26083276</v>
+      </c>
+      <c r="D18" s="49">
+        <v>66</v>
+      </c>
       <c r="E18" s="49"/>
       <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
+      <c r="G18" s="49">
+        <v>10090499</v>
+      </c>
+      <c r="H18" s="49">
+        <v>4896999</v>
+      </c>
+      <c r="I18" s="49">
+        <v>4483500</v>
+      </c>
+      <c r="J18" s="49">
+        <v>60</v>
+      </c>
+      <c r="K18" s="49">
+        <v>1188800</v>
+      </c>
       <c r="L18" s="50"/>
-      <c r="M18" s="8" t="str">
+      <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N18" s="8" t="str">
+        <v>19470998</v>
+      </c>
+      <c r="N18" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O18" s="8" t="str">
+        <v>45554274</v>
+      </c>
+      <c r="O18" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P18" s="8" t="str">
+        <v>395201.15151515149</v>
+      </c>
+      <c r="P18" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>324516.63333333336</v>
       </c>
       <c r="Q18" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18793,20 +18887,20 @@
         <v>526</v>
       </c>
       <c r="C4" s="124">
-        <v>180051187</v>
+        <v>180181187</v>
       </c>
       <c r="D4" s="125">
         <v>201819517</v>
       </c>
       <c r="E4" s="126">
         <f>IFERROR(IF(D4&gt;0,C4/D4,""),"")</f>
-        <v>0.89213961898442162</v>
+        <v>0.89278375886708716</v>
       </c>
       <c r="F4" s="124">
         <v>433</v>
       </c>
       <c r="G4" s="124">
-        <v>415823</v>
+        <v>416123</v>
       </c>
       <c r="H4" s="127">
         <f>IFERROR(SUM('📅 DAILY T9'!F6:F11),0)</f>
@@ -18827,7 +18921,7 @@
         <v>0.98901425974827706</v>
       </c>
       <c r="M4" s="130">
-        <v>287200983</v>
+        <v>287330983</v>
       </c>
       <c r="N4" s="131"/>
     </row>
@@ -18839,20 +18933,20 @@
         <v>527</v>
       </c>
       <c r="C5" s="124">
-        <v>0</v>
+        <v>246869905</v>
       </c>
       <c r="D5" s="125">
         <v>235456103</v>
       </c>
       <c r="E5" s="126">
         <f>IFERROR(IF(D5&gt;0,C5/D5,""),"")</f>
-        <v>0</v>
+        <v>1.0484752862829807</v>
       </c>
       <c r="F5" s="124">
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="G5" s="124">
-        <v>0</v>
+        <v>442419</v>
       </c>
       <c r="H5" s="127">
         <f>IFERROR(SUM('📅 DAILY T9'!F12:F18),0)</f>
@@ -18863,17 +18957,17 @@
         <v/>
       </c>
       <c r="J5" s="129">
-        <v>0</v>
+        <v>105986080</v>
       </c>
       <c r="K5" s="125">
         <v>126396657</v>
       </c>
       <c r="L5" s="126">
         <f>IFERROR(IF(K5&gt;0,J5/K5,""),"")</f>
-        <v>0</v>
+        <v>0.83851964534156942</v>
       </c>
       <c r="M5" s="130">
-        <v>0</v>
+        <v>352855985</v>
       </c>
       <c r="N5" s="131"/>
     </row>
@@ -19041,7 +19135,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="148" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="149"/>
@@ -19069,7 +19163,7 @@
       <c r="X1" s="149"/>
     </row>
     <row r="2" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="149"/>
@@ -19171,7 +19265,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="153" t="s">
+      <c r="A4" s="158" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="149"/>
@@ -19199,7 +19293,7 @@
       <c r="X4" s="149"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="150" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="149"/>
@@ -19296,7 +19390,7 @@
       </c>
       <c r="X6" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35),0)</f>
-        <v>180051187</v>
+        <v>427051092</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19369,7 +19463,7 @@
       </c>
       <c r="X7" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!D$6:D$35),0)</f>
-        <v>433</v>
+        <v>991</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19442,7 +19536,7 @@
       </c>
       <c r="X8" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)/SUM('📅 DAILY T9'!D$6:D$35),"")</f>
-        <v>415822.60277136258</v>
+        <v>430929.45711402624</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19514,7 +19608,7 @@
         <v>4841</v>
       </c>
       <c r="X9" s="11">
-        <v>949</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19635,7 +19729,7 @@
       </c>
       <c r="X11" s="12">
         <f t="shared" si="0"/>
-        <v>0.45626975763962063</v>
+        <v>0.40088996763754048</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19667,7 +19761,7 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="158" t="s">
+      <c r="A13" s="150" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="149"/>
@@ -19695,7 +19789,7 @@
       <c r="X13" s="149"/>
     </row>
     <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="151" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="149"/>
@@ -19791,7 +19885,7 @@
         <v>747</v>
       </c>
       <c r="X15" s="11">
-        <v>134</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19863,7 +19957,7 @@
         <v>433990</v>
       </c>
       <c r="X16" s="11">
-        <v>359788</v>
+        <v>385103</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19935,7 +20029,7 @@
         <v>115</v>
       </c>
       <c r="X17" s="13">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20007,11 +20101,11 @@
         <v>74</v>
       </c>
       <c r="X18" s="13">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="152" t="s">
+      <c r="A19" s="151" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="149"/>
@@ -20107,7 +20201,7 @@
         <v>1655</v>
       </c>
       <c r="X20" s="11">
-        <v>289</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20179,7 +20273,7 @@
         <v>500556</v>
       </c>
       <c r="X21" s="11">
-        <v>457777</v>
+        <v>481095</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20251,7 +20345,7 @@
         <v>0.68899999999999995</v>
       </c>
       <c r="X22" s="13">
-        <v>0.68320000000000003</v>
+        <v>0.70299999999999996</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20323,7 +20417,7 @@
         <v>490</v>
       </c>
       <c r="X23" s="11">
-        <v>73</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20395,7 +20489,7 @@
         <v>473743</v>
       </c>
       <c r="X24" s="11">
-        <v>341600</v>
+        <v>371329</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20467,7 +20561,7 @@
         <v>483</v>
       </c>
       <c r="X25" s="11">
-        <v>91</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20539,7 +20633,7 @@
         <v>524029</v>
       </c>
       <c r="X26" s="11">
-        <v>450825</v>
+        <v>484623</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20611,7 +20705,7 @@
         <v>682</v>
       </c>
       <c r="X27" s="11">
-        <v>125</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20683,11 +20777,11 @@
         <v>503197</v>
       </c>
       <c r="X28" s="11">
-        <v>530686</v>
+        <v>550314</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="152" t="s">
+      <c r="A29" s="151" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="149"/>
@@ -20783,7 +20877,7 @@
         <v>1348</v>
       </c>
       <c r="X30" s="11">
-        <v>226</v>
+        <v>538</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20855,7 +20949,7 @@
         <v>517786</v>
       </c>
       <c r="X31" s="11">
-        <v>477845</v>
+        <v>506563</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20927,11 +21021,11 @@
         <v>1740028</v>
       </c>
       <c r="X32" s="11">
-        <v>1591320</v>
+        <v>1672378</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="157" t="s">
+      <c r="A33" s="155" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="149"/>
@@ -20959,7 +21053,7 @@
       <c r="X33" s="149"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="157" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="149"/>
@@ -21055,8 +21149,7 @@
         <v>478057804</v>
       </c>
       <c r="X35" s="8">
-        <f>IFERROR(SUM('📅 DAILY T9'!G$6:I$35),0)</f>
-        <v>107149796</v>
+        <v>213135876</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21128,8 +21221,7 @@
         <v>241642155</v>
       </c>
       <c r="X36" s="8">
-        <f>IFERROR(SUM('📅 DAILY T9'!G$6:G$35),0)</f>
-        <v>55950787</v>
+        <v>108298050</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21201,8 +21293,7 @@
         <v>124655638</v>
       </c>
       <c r="X37" s="8">
-        <f>IFERROR(SUM('📅 DAILY T9'!H$6:H$35),0)</f>
-        <v>32963502</v>
+        <v>61391263</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21274,8 +21365,7 @@
         <v>111760011</v>
       </c>
       <c r="X38" s="8">
-        <f>IFERROR(SUM('📅 DAILY T9'!I$6:I$35),0)</f>
-        <v>18235507</v>
+        <v>43446563</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21347,8 +21437,7 @@
         <v>1536</v>
       </c>
       <c r="X39" s="8">
-        <f>IFERROR(SUM('📅 DAILY T9'!J$6:J$35),0)</f>
-        <v>307</v>
+        <v>641</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21421,11 +21510,11 @@
       </c>
       <c r="X40" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!M$6:M$35)/SUM('📅 DAILY T9'!J$6:J$35),"")</f>
-        <v>349022.13680781762</v>
+        <v>332505.26677067083</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="156"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="149"/>
       <c r="C41" s="149"/>
       <c r="D41" s="149"/>
@@ -21448,10 +21537,10 @@
       <c r="U41" s="149"/>
       <c r="V41" s="149"/>
       <c r="W41" s="149"/>
-      <c r="X41" s="151"/>
+      <c r="X41" s="154"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="156"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="149"/>
       <c r="C42" s="149"/>
       <c r="D42" s="149"/>
@@ -21474,7 +21563,7 @@
       <c r="U42" s="149"/>
       <c r="V42" s="149"/>
       <c r="W42" s="149"/>
-      <c r="X42" s="151"/>
+      <c r="X42" s="154"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -21545,7 +21634,7 @@
         <v>527</v>
       </c>
       <c r="X43" s="11">
-        <v>107</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21617,7 +21706,7 @@
         <v>338511</v>
       </c>
       <c r="X44" s="11">
-        <v>406636</v>
+        <v>384295</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21689,7 +21778,7 @@
         <v>60</v>
       </c>
       <c r="X45" s="13">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21761,11 +21850,11 @@
         <v>34</v>
       </c>
       <c r="X46" s="13">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="152" t="s">
+      <c r="A47" s="151" t="s">
         <v>46</v>
       </c>
       <c r="B47" s="149"/>
@@ -21861,7 +21950,7 @@
         <v>791</v>
       </c>
       <c r="X48" s="11">
-        <v>159</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21933,7 +22022,7 @@
         <v>380772</v>
       </c>
       <c r="X49" s="11">
-        <v>400250</v>
+        <v>389171</v>
       </c>
     </row>
     <row r="50" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22005,7 +22094,7 @@
         <v>0.60019999999999996</v>
       </c>
       <c r="X50" s="13">
-        <v>0.59770000000000001</v>
+        <v>0.59709999999999996</v>
       </c>
     </row>
     <row r="51" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22077,7 +22166,7 @@
         <v>174</v>
       </c>
       <c r="X51" s="11">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22149,7 +22238,7 @@
         <v>500388</v>
       </c>
       <c r="X52" s="11">
-        <v>493690</v>
+        <v>476202</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22221,7 +22310,7 @@
         <v>223</v>
       </c>
       <c r="X53" s="11">
-        <v>46</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22293,7 +22382,7 @@
         <v>369027</v>
       </c>
       <c r="X54" s="11">
-        <v>344658</v>
+        <v>328995</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22365,7 +22454,7 @@
         <v>394</v>
       </c>
       <c r="X55" s="11">
-        <v>84</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22437,11 +22526,11 @@
         <v>334595</v>
       </c>
       <c r="X56" s="11">
-        <v>398435</v>
+        <v>387257</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="152" t="s">
+      <c r="A57" s="151" t="s">
         <v>54</v>
       </c>
       <c r="B57" s="149"/>
@@ -22537,7 +22626,7 @@
         <v>585</v>
       </c>
       <c r="X58" s="11">
-        <v>113</v>
+        <v>250</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22609,7 +22698,7 @@
         <v>406621</v>
       </c>
       <c r="X59" s="11">
-        <v>441856</v>
+        <v>418496</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22681,7 +22770,7 @@
         <v>1389818</v>
       </c>
       <c r="X60" s="11">
-        <v>1460912</v>
+        <v>1420474</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -22763,7 +22852,7 @@
         <v>30530917</v>
       </c>
       <c r="X63" s="8">
-        <v>4890500</v>
+        <v>9650006</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22835,7 +22924,7 @@
         <v>1.8781108525479821E-2</v>
       </c>
       <c r="X64" s="132">
-        <v>1.7028145060353089E-2</v>
+        <v>1.507373077297631E-2</v>
       </c>
     </row>
     <row r="65" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -22965,11 +23054,11 @@
       </c>
       <c r="X68" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)+SUM('📅 DAILY T9'!G$6:I$35),0)</f>
-        <v>287200983</v>
+        <v>640186968</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="150"/>
+      <c r="A69" s="156"/>
       <c r="B69" s="149"/>
       <c r="C69" s="149"/>
       <c r="D69" s="149"/>
@@ -22992,7 +23081,7 @@
       <c r="U69" s="149"/>
       <c r="V69" s="149"/>
       <c r="W69" s="149"/>
-      <c r="X69" s="151"/>
+      <c r="X69" s="154"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="25"/>
@@ -23063,7 +23152,7 @@
         <v>1.135</v>
       </c>
       <c r="X70" s="14">
-        <v>1.091</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23135,7 +23224,7 @@
         <v>20501</v>
       </c>
       <c r="X71" s="11">
-        <v>19399</v>
+        <v>19907</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23207,7 +23296,7 @@
         <v>1449</v>
       </c>
       <c r="X72" s="11">
-        <v>203</v>
+        <v>497</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23515,7 +23604,7 @@
         <v>1418862</v>
       </c>
       <c r="X77" s="11">
-        <v>1297602</v>
+        <v>1363698</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23587,7 +23676,7 @@
         <v>914424</v>
       </c>
       <c r="X78" s="11">
-        <v>961200</v>
+        <v>1004940</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23659,7 +23748,7 @@
         <v>1740028</v>
       </c>
       <c r="X79" s="11">
-        <v>1591320</v>
+        <v>1672378</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23731,11 +23820,11 @@
         <v>1389818</v>
       </c>
       <c r="X80" s="11">
-        <v>1460912</v>
+        <v>1420474</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="154" t="s">
+      <c r="A81" s="159" t="s">
         <v>93</v>
       </c>
       <c r="B81" s="149"/>
@@ -24060,22 +24149,22 @@
     <row r="200" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A13:X13"/>
-    <mergeCell ref="A14:X14"/>
-    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A81:X81"/>
+    <mergeCell ref="A57:X57"/>
+    <mergeCell ref="A47:X47"/>
     <mergeCell ref="A42:X42"/>
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
+    <mergeCell ref="A69:X69"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A1:X1"/>
     <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A69:X69"/>
-    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="A13:X13"/>
+    <mergeCell ref="A14:X14"/>
+    <mergeCell ref="A2:X2"/>
     <mergeCell ref="A4:X4"/>
-    <mergeCell ref="A81:X81"/>
-    <mergeCell ref="A57:X57"/>
-    <mergeCell ref="A47:X47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -24106,7 +24195,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>531</v>
       </c>
       <c r="B1" s="149"/>
@@ -24127,7 +24216,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -24148,19 +24237,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -24172,11 +24261,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -24238,7 +24327,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -26010,7 +26099,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>538</v>
       </c>
       <c r="B1" s="149"/>
@@ -26031,7 +26120,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -26052,19 +26141,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -26076,11 +26165,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -26142,7 +26231,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -27938,7 +28027,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>546</v>
       </c>
       <c r="B1" s="149"/>
@@ -27959,7 +28048,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -27980,19 +28069,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -28004,11 +28093,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -28070,7 +28159,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -29833,7 +29922,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>553</v>
       </c>
       <c r="B1" s="149"/>
@@ -33325,40 +33414,40 @@
         <v>626</v>
       </c>
       <c r="C83">
-        <v>125</v>
+        <v>301</v>
       </c>
       <c r="D83">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="E83">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F83">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G83">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H83">
+        <v>33</v>
+      </c>
+      <c r="I83">
         <v>14</v>
       </c>
-      <c r="I83">
-        <v>3</v>
-      </c>
       <c r="J83">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="M83">
         <v>0</v>
       </c>
       <c r="N83">
-        <v>48</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33369,22 +33458,22 @@
         <v>627</v>
       </c>
       <c r="C84">
-        <v>190</v>
+        <v>431</v>
       </c>
       <c r="D84">
-        <v>139</v>
+        <v>309</v>
       </c>
       <c r="E84">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="F84">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G84">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H84">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I84">
         <v>3</v>
@@ -33396,13 +33485,13 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="M84">
         <v>0</v>
       </c>
       <c r="N84">
-        <v>30</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33413,19 +33502,19 @@
         <v>628</v>
       </c>
       <c r="C85">
-        <v>91</v>
+        <v>215</v>
       </c>
       <c r="D85">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="E85">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -33440,13 +33529,13 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M85">
         <v>0</v>
       </c>
       <c r="N85">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -36341,13 +36430,13 @@
         <v>626</v>
       </c>
       <c r="C163">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="D163">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -36359,7 +36448,7 @@
         <v>2</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -36385,10 +36474,10 @@
         <v>627</v>
       </c>
       <c r="C164">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D164">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -36429,10 +36518,10 @@
         <v>628</v>
       </c>
       <c r="C165" s="147">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D165" s="147">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E165" s="147">
         <v>0</v>
@@ -36605,13 +36694,13 @@
         <v>626</v>
       </c>
       <c r="C172">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="D172">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -36623,7 +36712,7 @@
         <v>2</v>
       </c>
       <c r="I172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -36649,10 +36738,10 @@
         <v>627</v>
       </c>
       <c r="C173">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D173">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -36693,10 +36782,10 @@
         <v>628</v>
       </c>
       <c r="C174">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D174">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -36764,7 +36853,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>408</v>
       </c>
       <c r="B1" s="149"/>
@@ -36785,7 +36874,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -36806,19 +36895,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -36830,11 +36919,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -36896,7 +36985,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -38654,7 +38743,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>443</v>
       </c>
       <c r="B1" s="149"/>
@@ -38675,7 +38764,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -38696,19 +38785,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -38720,11 +38809,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -38786,7 +38875,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -40612,7 +40701,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>444</v>
       </c>
       <c r="B1" s="149"/>
@@ -40633,7 +40722,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -40654,19 +40743,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -40678,11 +40767,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -40744,7 +40833,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -42528,7 +42617,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>445</v>
       </c>
       <c r="B1" s="149"/>
@@ -42549,7 +42638,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -42570,19 +42659,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -42594,11 +42683,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -42660,7 +42749,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -44492,7 +44581,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>446</v>
       </c>
       <c r="B1" s="149"/>
@@ -44513,7 +44602,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -44534,19 +44623,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -44558,11 +44647,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -44624,7 +44713,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -46444,7 +46533,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>447</v>
       </c>
       <c r="B1" s="149"/>
@@ -46465,7 +46554,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -46486,19 +46575,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -46510,11 +46599,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -46576,7 +46665,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -48232,7 +48321,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>448</v>
       </c>
       <c r="B1" s="149"/>
@@ -48253,7 +48342,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="152" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -48274,19 +48363,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="171" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="168" t="s">
+      <c r="C3" s="170" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="166" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="166" t="s">
+      <c r="G3" s="168" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -48298,11 +48387,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="165" t="s">
+      <c r="M3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="165" t="s">
+      <c r="O3" s="167" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -48364,7 +48453,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="169" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07C4ECF5-8558-BF4C-AA5F-8C145FD1F42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82C3DAC-4D63-DE45-86D7-6DB0BB7231E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3451,26 +3451,13 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3478,6 +3465,19 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3491,12 +3491,6 @@
     </xf>
     <xf numFmtId="0" fontId="51" fillId="47" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3513,16 +3507,22 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5238,7 +5238,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>449</v>
       </c>
       <c r="B1" s="149"/>
@@ -5259,7 +5259,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -5280,19 +5280,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -5304,11 +5304,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -5370,7 +5370,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -7136,7 +7136,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>450</v>
       </c>
       <c r="B1" s="149"/>
@@ -7157,7 +7157,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -7178,19 +7178,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -7202,11 +7202,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -7268,7 +7268,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -9075,7 +9075,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>451</v>
       </c>
       <c r="B1" s="149"/>
@@ -9096,7 +9096,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -9117,19 +9117,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -9141,11 +9141,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -9207,7 +9207,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -10988,7 +10988,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>452</v>
       </c>
       <c r="B1" s="149"/>
@@ -11004,7 +11004,7 @@
       <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>453</v>
       </c>
       <c r="B2" s="149"/>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="175" t="s">
+      <c r="A23" s="173" t="s">
         <v>473</v>
       </c>
       <c r="B23" s="149"/>
@@ -11310,7 +11310,7 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="174" t="s">
+      <c r="A25" s="172" t="s">
         <v>474</v>
       </c>
       <c r="B25" s="149"/>
@@ -11327,7 +11327,7 @@
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="172" t="s">
+      <c r="A27" s="174" t="s">
         <v>475</v>
       </c>
       <c r="B27" s="149"/>
@@ -11340,7 +11340,7 @@
       <c r="I27" s="149"/>
       <c r="J27" s="149"/>
       <c r="K27" s="149"/>
-      <c r="L27" s="173"/>
+      <c r="L27" s="175"/>
       <c r="M27" s="79"/>
       <c r="N27" s="79"/>
       <c r="O27" s="79"/>
@@ -11573,7 +11573,7 @@
       <c r="T34" s="84"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="172" t="s">
+      <c r="A35" s="174" t="s">
         <v>499</v>
       </c>
       <c r="B35" s="149"/>
@@ -11586,7 +11586,7 @@
       <c r="I35" s="149"/>
       <c r="J35" s="149"/>
       <c r="K35" s="149"/>
-      <c r="L35" s="173"/>
+      <c r="L35" s="175"/>
       <c r="M35" s="84"/>
       <c r="N35" s="84"/>
       <c r="O35" s="84"/>
@@ -11862,11 +11862,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11897,7 +11897,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>503</v>
       </c>
       <c r="B1" s="149"/>
@@ -11918,7 +11918,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -11939,19 +11939,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -11963,11 +11963,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -12029,7 +12029,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -13863,7 +13863,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>504</v>
       </c>
       <c r="B1" s="149"/>
@@ -13879,7 +13879,7 @@
       <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>453</v>
       </c>
       <c r="B2" s="149"/>
@@ -14240,7 +14240,7 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="175" t="s">
+      <c r="A23" s="173" t="s">
         <v>473</v>
       </c>
       <c r="B23" s="149"/>
@@ -14263,7 +14263,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="174" t="s">
+      <c r="A25" s="172" t="s">
         <v>474</v>
       </c>
       <c r="B25" s="149"/>
@@ -14489,7 +14489,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>511</v>
       </c>
       <c r="B1" s="149"/>
@@ -14510,7 +14510,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -14531,19 +14531,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -14555,11 +14555,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -14621,7 +14621,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -16451,7 +16451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>512</v>
       </c>
       <c r="B1" s="149"/>
@@ -16467,7 +16467,7 @@
       <c r="L1" s="149"/>
     </row>
     <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>453</v>
       </c>
       <c r="B2" s="149"/>
@@ -16867,7 +16867,7 @@
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="175" t="s">
+      <c r="A24" s="173" t="s">
         <v>473</v>
       </c>
       <c r="B24" s="149"/>
@@ -16890,7 +16890,7 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="174" t="s">
+      <c r="A26" s="172" t="s">
         <v>474</v>
       </c>
       <c r="B26" s="149"/>
@@ -17116,7 +17116,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>520</v>
       </c>
       <c r="B1" s="149"/>
@@ -17137,7 +17137,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -17158,19 +17158,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -17182,11 +17182,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -17248,7 +17248,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -17446,7 +17446,7 @@
         <v>440</v>
       </c>
       <c r="C9" s="49">
-        <v>53539297</v>
+        <v>53997297</v>
       </c>
       <c r="D9" s="49">
         <v>100</v>
@@ -17475,11 +17475,11 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" si="1"/>
-        <v>78467318</v>
+        <v>78925318</v>
       </c>
       <c r="O9" s="8">
         <f t="shared" si="2"/>
-        <v>535392.97</v>
+        <v>539972.97</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="3"/>
@@ -17704,7 +17704,7 @@
         <v>438</v>
       </c>
       <c r="C14" s="49">
-        <v>43407044</v>
+        <v>43825044</v>
       </c>
       <c r="D14" s="49">
         <v>75</v>
@@ -17731,11 +17731,11 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" si="1"/>
-        <v>53249548</v>
+        <v>53667548</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="2"/>
-        <v>578760.58666666667</v>
+        <v>584333.92000000004</v>
       </c>
       <c r="P14" s="8">
         <f t="shared" si="3"/>
@@ -17858,7 +17858,7 @@
         <v>441</v>
       </c>
       <c r="C17" s="49">
-        <v>38341033</v>
+        <v>38556033</v>
       </c>
       <c r="D17" s="49">
         <v>89</v>
@@ -17885,11 +17885,11 @@
       </c>
       <c r="N17" s="8">
         <f t="shared" si="1"/>
-        <v>55700394</v>
+        <v>55915394</v>
       </c>
       <c r="O17" s="8">
         <f t="shared" si="2"/>
-        <v>430798.1235955056</v>
+        <v>433213.85393258429</v>
       </c>
       <c r="P17" s="8">
         <f t="shared" si="3"/>
@@ -17908,10 +17908,10 @@
         <v>442</v>
       </c>
       <c r="C18" s="49">
-        <v>26083276</v>
+        <v>26490027</v>
       </c>
       <c r="D18" s="49">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="49"/>
       <c r="F18" s="49"/>
@@ -17937,11 +17937,11 @@
       </c>
       <c r="N18" s="8">
         <f t="shared" si="1"/>
-        <v>45554274</v>
+        <v>45961025</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="2"/>
-        <v>395201.15151515149</v>
+        <v>395373.53731343284</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="3"/>
@@ -17959,31 +17959,43 @@
       <c r="B19" s="48" t="s">
         <v>436</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
+      <c r="C19" s="49">
+        <v>31189531</v>
+      </c>
+      <c r="D19" s="49">
+        <v>72</v>
+      </c>
       <c r="E19" s="49"/>
       <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
+      <c r="G19" s="49">
+        <v>12817011</v>
+      </c>
+      <c r="H19" s="49">
+        <v>3634005</v>
+      </c>
+      <c r="I19" s="49">
+        <v>5753493</v>
+      </c>
+      <c r="J19" s="49">
+        <v>63</v>
+      </c>
       <c r="K19" s="49"/>
       <c r="L19" s="50"/>
-      <c r="M19" s="8" t="str">
+      <c r="M19" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N19" s="8" t="str">
+        <v>22204509</v>
+      </c>
+      <c r="N19" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O19" s="8" t="str">
+        <v>53394040</v>
+      </c>
+      <c r="O19" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P19" s="8" t="str">
+        <v>433187.93055555556</v>
+      </c>
+      <c r="P19" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>352452.52380952379</v>
       </c>
       <c r="Q19" s="21" t="str">
         <f t="shared" si="4"/>
@@ -17997,31 +18009,43 @@
       <c r="B20" s="48" t="s">
         <v>437</v>
       </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
+      <c r="C20" s="49">
+        <v>30568282</v>
+      </c>
+      <c r="D20" s="49">
+        <v>75</v>
+      </c>
       <c r="E20" s="49"/>
       <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
+      <c r="G20" s="49">
+        <v>5637999</v>
+      </c>
+      <c r="H20" s="49">
+        <v>2679502</v>
+      </c>
+      <c r="I20" s="49">
+        <v>935000</v>
+      </c>
+      <c r="J20" s="49">
+        <v>27</v>
+      </c>
       <c r="K20" s="49"/>
       <c r="L20" s="50"/>
-      <c r="M20" s="8" t="str">
+      <c r="M20" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N20" s="8" t="str">
+        <v>9252501</v>
+      </c>
+      <c r="N20" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O20" s="8" t="str">
+        <v>39820783</v>
+      </c>
+      <c r="O20" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P20" s="8" t="str">
+        <v>407577.09333333332</v>
+      </c>
+      <c r="P20" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>342685.22222222225</v>
       </c>
       <c r="Q20" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18035,31 +18059,45 @@
       <c r="B21" s="48" t="s">
         <v>438</v>
       </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
+      <c r="C21" s="49">
+        <v>50475789</v>
+      </c>
+      <c r="D21" s="49">
+        <v>86</v>
+      </c>
       <c r="E21" s="49"/>
       <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
+      <c r="G21" s="49">
+        <v>5925850</v>
+      </c>
+      <c r="H21" s="49">
+        <v>2915000</v>
+      </c>
+      <c r="I21" s="49">
+        <v>2107499</v>
+      </c>
+      <c r="J21" s="49">
+        <v>38</v>
+      </c>
+      <c r="K21" s="49">
+        <v>1820000</v>
+      </c>
       <c r="L21" s="50"/>
-      <c r="M21" s="8" t="str">
+      <c r="M21" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N21" s="8" t="str">
+        <v>10948349</v>
+      </c>
+      <c r="N21" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O21" s="8" t="str">
+        <v>61424138</v>
+      </c>
+      <c r="O21" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P21" s="8" t="str">
+        <v>586927.77906976745</v>
+      </c>
+      <c r="P21" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>288114.44736842107</v>
       </c>
       <c r="Q21" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18073,31 +18111,45 @@
       <c r="B22" s="48" t="s">
         <v>439</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
+      <c r="C22" s="49">
+        <v>34573226</v>
+      </c>
+      <c r="D22" s="49">
+        <v>82</v>
+      </c>
       <c r="E22" s="49"/>
       <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
+      <c r="G22" s="49">
+        <v>8734253</v>
+      </c>
+      <c r="H22" s="49">
+        <v>3045001</v>
+      </c>
+      <c r="I22" s="49">
+        <v>3692004</v>
+      </c>
+      <c r="J22" s="49">
+        <v>54</v>
+      </c>
+      <c r="K22" s="49">
+        <v>231481</v>
+      </c>
       <c r="L22" s="50"/>
-      <c r="M22" s="8" t="str">
+      <c r="M22" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N22" s="8" t="str">
+        <v>15471258</v>
+      </c>
+      <c r="N22" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O22" s="8" t="str">
+        <v>50044484</v>
+      </c>
+      <c r="O22" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P22" s="8" t="str">
+        <v>421624.70731707319</v>
+      </c>
+      <c r="P22" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>286504.77777777775</v>
       </c>
       <c r="Q22" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18111,31 +18163,45 @@
       <c r="B23" s="48" t="s">
         <v>440</v>
       </c>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
+      <c r="C23" s="49">
+        <v>38179278</v>
+      </c>
+      <c r="D23" s="49">
+        <v>93</v>
+      </c>
       <c r="E23" s="49"/>
       <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
+      <c r="G23" s="49">
+        <v>8010006</v>
+      </c>
+      <c r="H23" s="49">
+        <v>6313252</v>
+      </c>
+      <c r="I23" s="49">
+        <v>2536847</v>
+      </c>
+      <c r="J23" s="49">
+        <v>57</v>
+      </c>
+      <c r="K23" s="49">
+        <v>280000</v>
+      </c>
       <c r="L23" s="50"/>
-      <c r="M23" s="8" t="str">
+      <c r="M23" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N23" s="8" t="str">
+        <v>16860105</v>
+      </c>
+      <c r="N23" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O23" s="8" t="str">
+        <v>55039383</v>
+      </c>
+      <c r="O23" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P23" s="8" t="str">
+        <v>410529.87096774194</v>
+      </c>
+      <c r="P23" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>295791.31578947371</v>
       </c>
       <c r="Q23" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18149,31 +18215,43 @@
       <c r="B24" s="52" t="s">
         <v>441</v>
       </c>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
+      <c r="C24" s="49">
+        <v>37986291</v>
+      </c>
+      <c r="D24" s="49">
+        <v>97</v>
+      </c>
       <c r="E24" s="49"/>
       <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
+      <c r="G24" s="49">
+        <v>9667497</v>
+      </c>
+      <c r="H24" s="49">
+        <v>5098502</v>
+      </c>
+      <c r="I24" s="49">
+        <v>4775499</v>
+      </c>
+      <c r="J24" s="49">
+        <v>67</v>
+      </c>
       <c r="K24" s="49"/>
       <c r="L24" s="50"/>
-      <c r="M24" s="8" t="str">
+      <c r="M24" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N24" s="8" t="str">
+        <v>19541498</v>
+      </c>
+      <c r="N24" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O24" s="8" t="str">
+        <v>57527789</v>
+      </c>
+      <c r="O24" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P24" s="8" t="str">
+        <v>391611.24742268043</v>
+      </c>
+      <c r="P24" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>291664.14925373136</v>
       </c>
       <c r="Q24" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18187,31 +18265,43 @@
       <c r="B25" s="52" t="s">
         <v>442</v>
       </c>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
+      <c r="C25" s="49">
+        <v>23959777</v>
+      </c>
+      <c r="D25" s="49">
+        <v>61</v>
+      </c>
       <c r="E25" s="49"/>
       <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
+      <c r="G25" s="49">
+        <v>6665001</v>
+      </c>
+      <c r="H25" s="49">
+        <v>2439502</v>
+      </c>
+      <c r="I25" s="49">
+        <v>4378877</v>
+      </c>
+      <c r="J25" s="49">
+        <v>49</v>
+      </c>
       <c r="K25" s="49"/>
       <c r="L25" s="50"/>
-      <c r="M25" s="8" t="str">
+      <c r="M25" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N25" s="8" t="str">
+        <v>13483380</v>
+      </c>
+      <c r="N25" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O25" s="8" t="str">
+        <v>37443157</v>
+      </c>
+      <c r="O25" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P25" s="8" t="str">
+        <v>392783.2295081967</v>
+      </c>
+      <c r="P25" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>275171.02040816325</v>
       </c>
       <c r="Q25" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18887,20 +18977,20 @@
         <v>526</v>
       </c>
       <c r="C4" s="124">
-        <v>180181187</v>
+        <v>180639187</v>
       </c>
       <c r="D4" s="125">
         <v>201819517</v>
       </c>
       <c r="E4" s="126">
         <f>IFERROR(IF(D4&gt;0,C4/D4,""),"")</f>
-        <v>0.89278375886708716</v>
+        <v>0.89505311322293968</v>
       </c>
       <c r="F4" s="124">
         <v>433</v>
       </c>
       <c r="G4" s="124">
-        <v>416123</v>
+        <v>417180</v>
       </c>
       <c r="H4" s="127">
         <f>IFERROR(SUM('📅 DAILY T9'!F6:F11),0)</f>
@@ -18921,7 +19011,7 @@
         <v>0.98901425974827706</v>
       </c>
       <c r="M4" s="130">
-        <v>287330983</v>
+        <v>287788983</v>
       </c>
       <c r="N4" s="131"/>
     </row>
@@ -18933,20 +19023,20 @@
         <v>527</v>
       </c>
       <c r="C5" s="124">
-        <v>246869905</v>
+        <v>247909656</v>
       </c>
       <c r="D5" s="125">
         <v>235456103</v>
       </c>
       <c r="E5" s="126">
         <f>IFERROR(IF(D5&gt;0,C5/D5,""),"")</f>
-        <v>1.0484752862829807</v>
+        <v>1.0528911879595664</v>
       </c>
       <c r="F5" s="124">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G5" s="124">
-        <v>442419</v>
+        <v>443487</v>
       </c>
       <c r="H5" s="127">
         <f>IFERROR(SUM('📅 DAILY T9'!F12:F18),0)</f>
@@ -18967,7 +19057,7 @@
         <v>0.83851964534156942</v>
       </c>
       <c r="M5" s="130">
-        <v>352855985</v>
+        <v>353895736</v>
       </c>
       <c r="N5" s="131"/>
     </row>
@@ -18979,20 +19069,20 @@
         <v>528</v>
       </c>
       <c r="C6" s="124">
-        <v>0</v>
+        <v>246932174</v>
       </c>
       <c r="D6" s="125">
         <v>235456103</v>
       </c>
       <c r="E6" s="126">
         <f>IFERROR(IF(D6&gt;0,C6/D6,""),"")</f>
-        <v>0</v>
+        <v>1.0487397474679176</v>
       </c>
       <c r="F6" s="124">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="G6" s="124">
-        <v>0</v>
+        <v>436275</v>
       </c>
       <c r="H6" s="127">
         <f>IFERROR(SUM('📅 DAILY T9'!F19:F25),0)</f>
@@ -19003,17 +19093,17 @@
         <v/>
       </c>
       <c r="J6" s="129">
-        <v>0</v>
+        <v>107761600</v>
       </c>
       <c r="K6" s="125">
         <v>126396657</v>
       </c>
       <c r="L6" s="126">
         <f>IFERROR(IF(K6&gt;0,J6/K6,""),"")</f>
-        <v>0</v>
+        <v>0.85256685230211426</v>
       </c>
       <c r="M6" s="130">
-        <v>0</v>
+        <v>354693774</v>
       </c>
       <c r="N6" s="131"/>
     </row>
@@ -19135,7 +19225,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="159" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="149"/>
@@ -19163,7 +19253,7 @@
       <c r="X1" s="149"/>
     </row>
     <row r="2" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="149"/>
@@ -19265,7 +19355,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="158" t="s">
+      <c r="A4" s="153" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="149"/>
@@ -19293,7 +19383,7 @@
       <c r="X4" s="149"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="150" t="s">
+      <c r="A5" s="158" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="149"/>
@@ -19390,7 +19480,7 @@
       </c>
       <c r="X6" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35),0)</f>
-        <v>427051092</v>
+        <v>675481017</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19463,7 +19553,7 @@
       </c>
       <c r="X7" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!D$6:D$35),0)</f>
-        <v>991</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19536,7 +19626,7 @@
       </c>
       <c r="X8" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)/SUM('📅 DAILY T9'!D$6:D$35),"")</f>
-        <v>430929.45711402624</v>
+        <v>433556.49358151475</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19608,7 +19698,7 @@
         <v>4841</v>
       </c>
       <c r="X9" s="11">
-        <v>2472</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19729,7 +19819,7 @@
       </c>
       <c r="X11" s="12">
         <f t="shared" si="0"/>
-        <v>0.40088996763754048</v>
+        <v>0.45675754910583405</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19761,7 +19851,7 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="150" t="s">
+      <c r="A13" s="158" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="149"/>
@@ -19789,7 +19879,7 @@
       <c r="X13" s="149"/>
     </row>
     <row r="14" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="151" t="s">
+      <c r="A14" s="152" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="149"/>
@@ -19885,7 +19975,7 @@
         <v>747</v>
       </c>
       <c r="X15" s="11">
-        <v>281</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19957,7 +20047,7 @@
         <v>433990</v>
       </c>
       <c r="X16" s="11">
-        <v>385103</v>
+        <v>399217</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20029,7 +20119,7 @@
         <v>115</v>
       </c>
       <c r="X17" s="13">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20101,11 +20191,11 @@
         <v>74</v>
       </c>
       <c r="X18" s="13">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="151" t="s">
+      <c r="A19" s="152" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="149"/>
@@ -20201,7 +20291,7 @@
         <v>1655</v>
       </c>
       <c r="X20" s="11">
-        <v>665</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20273,7 +20363,7 @@
         <v>500556</v>
       </c>
       <c r="X21" s="11">
-        <v>481095</v>
+        <v>491806</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20345,7 +20435,7 @@
         <v>0.68899999999999995</v>
       </c>
       <c r="X22" s="13">
-        <v>0.70299999999999996</v>
+        <v>0.69199999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20417,7 +20507,7 @@
         <v>490</v>
       </c>
       <c r="X23" s="11">
-        <v>179</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20489,7 +20579,7 @@
         <v>473743</v>
       </c>
       <c r="X24" s="11">
-        <v>371329</v>
+        <v>416474</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20561,7 +20651,7 @@
         <v>483</v>
       </c>
       <c r="X25" s="11">
-        <v>213</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20633,7 +20723,7 @@
         <v>524029</v>
       </c>
       <c r="X26" s="11">
-        <v>484623</v>
+        <v>506565</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20705,7 +20795,7 @@
         <v>682</v>
       </c>
       <c r="X27" s="11">
-        <v>273</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20777,11 +20867,11 @@
         <v>503197</v>
       </c>
       <c r="X28" s="11">
-        <v>550314</v>
+        <v>532365</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="151" t="s">
+      <c r="A29" s="152" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="149"/>
@@ -20877,7 +20967,7 @@
         <v>1348</v>
       </c>
       <c r="X30" s="11">
-        <v>538</v>
+        <v>808</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20949,7 +21039,7 @@
         <v>517786</v>
       </c>
       <c r="X31" s="11">
-        <v>506563</v>
+        <v>520091</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21021,11 +21111,11 @@
         <v>1740028</v>
       </c>
       <c r="X32" s="11">
-        <v>1672378</v>
+        <v>1693483</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="155" t="s">
+      <c r="A33" s="157" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="149"/>
@@ -21053,7 +21143,7 @@
       <c r="X33" s="149"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="157" t="s">
+      <c r="A34" s="148" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="149"/>
@@ -21149,7 +21239,7 @@
         <v>478057804</v>
       </c>
       <c r="X35" s="8">
-        <v>213135876</v>
+        <v>320897476</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21221,7 +21311,7 @@
         <v>241642155</v>
       </c>
       <c r="X36" s="8">
-        <v>108298050</v>
+        <v>165755667</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21293,7 +21383,7 @@
         <v>124655638</v>
       </c>
       <c r="X37" s="8">
-        <v>61391263</v>
+        <v>87516027</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21365,7 +21455,7 @@
         <v>111760011</v>
       </c>
       <c r="X38" s="8">
-        <v>43446563</v>
+        <v>67625782</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21437,7 +21527,7 @@
         <v>1536</v>
       </c>
       <c r="X39" s="8">
-        <v>641</v>
+        <v>996</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21510,11 +21600,11 @@
       </c>
       <c r="X40" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!M$6:M$35)/SUM('📅 DAILY T9'!J$6:J$35),"")</f>
-        <v>332505.26677067083</v>
+        <v>322186.22088353412</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="153"/>
+      <c r="A41" s="156"/>
       <c r="B41" s="149"/>
       <c r="C41" s="149"/>
       <c r="D41" s="149"/>
@@ -21537,10 +21627,10 @@
       <c r="U41" s="149"/>
       <c r="V41" s="149"/>
       <c r="W41" s="149"/>
-      <c r="X41" s="154"/>
+      <c r="X41" s="151"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="153"/>
+      <c r="A42" s="156"/>
       <c r="B42" s="149"/>
       <c r="C42" s="149"/>
       <c r="D42" s="149"/>
@@ -21563,7 +21653,7 @@
       <c r="U42" s="149"/>
       <c r="V42" s="149"/>
       <c r="W42" s="149"/>
-      <c r="X42" s="154"/>
+      <c r="X42" s="151"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -21634,7 +21724,7 @@
         <v>527</v>
       </c>
       <c r="X43" s="11">
-        <v>222</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21706,7 +21796,7 @@
         <v>338511</v>
       </c>
       <c r="X44" s="11">
-        <v>384295</v>
+        <v>356240</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21778,7 +21868,7 @@
         <v>60</v>
       </c>
       <c r="X45" s="13">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21850,11 +21940,11 @@
         <v>34</v>
       </c>
       <c r="X46" s="13">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="151" t="s">
+      <c r="A47" s="152" t="s">
         <v>46</v>
       </c>
       <c r="B47" s="149"/>
@@ -21950,7 +22040,7 @@
         <v>791</v>
       </c>
       <c r="X48" s="11">
-        <v>329</v>
+        <v>503</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22022,7 +22112,7 @@
         <v>380772</v>
       </c>
       <c r="X49" s="11">
-        <v>389171</v>
+        <v>389691</v>
       </c>
     </row>
     <row r="50" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22094,7 +22184,7 @@
         <v>0.60019999999999996</v>
       </c>
       <c r="X50" s="13">
-        <v>0.59709999999999996</v>
+        <v>0.58760000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22166,7 +22256,7 @@
         <v>174</v>
       </c>
       <c r="X51" s="11">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22238,7 +22328,7 @@
         <v>500388</v>
       </c>
       <c r="X52" s="11">
-        <v>476202</v>
+        <v>474968</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22310,7 +22400,7 @@
         <v>223</v>
       </c>
       <c r="X53" s="11">
-        <v>93</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22382,7 +22472,7 @@
         <v>369027</v>
       </c>
       <c r="X54" s="11">
-        <v>328995</v>
+        <v>354539</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22454,7 +22544,7 @@
         <v>394</v>
       </c>
       <c r="X55" s="11">
-        <v>168</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22526,11 +22616,11 @@
         <v>334595</v>
       </c>
       <c r="X56" s="11">
-        <v>387257</v>
+        <v>377527</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="151" t="s">
+      <c r="A57" s="152" t="s">
         <v>54</v>
       </c>
       <c r="B57" s="149"/>
@@ -22626,7 +22716,7 @@
         <v>585</v>
       </c>
       <c r="X58" s="11">
-        <v>250</v>
+        <v>384</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22698,7 +22788,7 @@
         <v>406621</v>
       </c>
       <c r="X59" s="11">
-        <v>418496</v>
+        <v>423650</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22770,7 +22860,7 @@
         <v>1389818</v>
       </c>
       <c r="X60" s="11">
-        <v>1420474</v>
+        <v>1529432</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -22852,7 +22942,7 @@
         <v>30530917</v>
       </c>
       <c r="X63" s="8">
-        <v>9650006</v>
+        <v>11981487</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22924,7 +23014,7 @@
         <v>1.8781108525479821E-2</v>
       </c>
       <c r="X64" s="132">
-        <v>1.507373077297631E-2</v>
+        <v>1.2025035751148031E-2</v>
       </c>
     </row>
     <row r="65" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -23054,11 +23144,11 @@
       </c>
       <c r="X68" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)+SUM('📅 DAILY T9'!G$6:I$35),0)</f>
-        <v>640186968</v>
+        <v>996378493</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="156"/>
+      <c r="A69" s="150"/>
       <c r="B69" s="149"/>
       <c r="C69" s="149"/>
       <c r="D69" s="149"/>
@@ -23081,7 +23171,7 @@
       <c r="U69" s="149"/>
       <c r="V69" s="149"/>
       <c r="W69" s="149"/>
-      <c r="X69" s="154"/>
+      <c r="X69" s="151"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="25"/>
@@ -23152,7 +23242,7 @@
         <v>1.135</v>
       </c>
       <c r="X70" s="14">
-        <v>1.109</v>
+        <v>1.121</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23224,7 +23314,7 @@
         <v>20501</v>
       </c>
       <c r="X71" s="11">
-        <v>19907</v>
+        <v>20390</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23296,7 +23386,7 @@
         <v>1449</v>
       </c>
       <c r="X72" s="11">
-        <v>497</v>
+        <v>793</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23436,7 +23526,7 @@
         <v>105</v>
       </c>
       <c r="X74">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23604,7 +23694,7 @@
         <v>1418862</v>
       </c>
       <c r="X77" s="11">
-        <v>1363698</v>
+        <v>1380908</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23676,7 +23766,7 @@
         <v>914424</v>
       </c>
       <c r="X78" s="11">
-        <v>1004940</v>
+        <v>1006283</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23748,7 +23838,7 @@
         <v>1740028</v>
       </c>
       <c r="X79" s="11">
-        <v>1672378</v>
+        <v>1693483</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23820,11 +23910,11 @@
         <v>1389818</v>
       </c>
       <c r="X80" s="11">
-        <v>1420474</v>
+        <v>1529432</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="159" t="s">
+      <c r="A81" s="154" t="s">
         <v>93</v>
       </c>
       <c r="B81" s="149"/>
@@ -24149,22 +24239,22 @@
     <row r="200" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A81:X81"/>
-    <mergeCell ref="A57:X57"/>
-    <mergeCell ref="A47:X47"/>
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A13:X13"/>
+    <mergeCell ref="A14:X14"/>
+    <mergeCell ref="A2:X2"/>
     <mergeCell ref="A42:X42"/>
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
+    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A69:X69"/>
-    <mergeCell ref="A34:X34"/>
     <mergeCell ref="A29:X29"/>
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A5:X5"/>
-    <mergeCell ref="A13:X13"/>
-    <mergeCell ref="A14:X14"/>
-    <mergeCell ref="A2:X2"/>
     <mergeCell ref="A4:X4"/>
+    <mergeCell ref="A81:X81"/>
+    <mergeCell ref="A57:X57"/>
+    <mergeCell ref="A47:X47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -24195,7 +24285,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>531</v>
       </c>
       <c r="B1" s="149"/>
@@ -24216,7 +24306,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -24237,19 +24327,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -24261,11 +24351,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -24327,7 +24417,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -26099,7 +26189,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>538</v>
       </c>
       <c r="B1" s="149"/>
@@ -26120,7 +26210,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -26141,19 +26231,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -26165,11 +26255,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -26231,7 +26321,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -28027,7 +28117,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>546</v>
       </c>
       <c r="B1" s="149"/>
@@ -28048,7 +28138,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -28069,19 +28159,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -28093,11 +28183,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -28159,7 +28249,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -29922,7 +30012,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>553</v>
       </c>
       <c r="B1" s="149"/>
@@ -33414,40 +33504,40 @@
         <v>626</v>
       </c>
       <c r="C83">
-        <v>301</v>
+        <v>508</v>
       </c>
       <c r="D83">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="E83">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F83">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="G83">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H83">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="I83">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J83">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="M83">
         <v>0</v>
       </c>
       <c r="N83">
-        <v>124</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33458,22 +33548,22 @@
         <v>627</v>
       </c>
       <c r="C84">
-        <v>431</v>
+        <v>656</v>
       </c>
       <c r="D84">
-        <v>309</v>
+        <v>477</v>
       </c>
       <c r="E84">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="F84">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G84">
         <v>7</v>
       </c>
       <c r="H84">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I84">
         <v>3</v>
@@ -33485,13 +33575,13 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="M84">
         <v>0</v>
       </c>
       <c r="N84">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33502,40 +33592,40 @@
         <v>628</v>
       </c>
       <c r="C85">
-        <v>215</v>
+        <v>338</v>
       </c>
       <c r="D85">
-        <v>177</v>
+        <v>275</v>
       </c>
       <c r="E85">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G85">
         <v>4</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85">
         <v>0</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85">
         <v>0</v>
       </c>
       <c r="L85">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="M85">
         <v>0</v>
       </c>
       <c r="N85">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -36430,40 +36520,40 @@
         <v>626</v>
       </c>
       <c r="C163">
-        <v>151</v>
+        <v>490</v>
       </c>
       <c r="D163">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="E163">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F163">
+        <v>92</v>
+      </c>
+      <c r="G163">
+        <v>4</v>
+      </c>
+      <c r="H163">
+        <v>35</v>
+      </c>
+      <c r="I163">
+        <v>11</v>
+      </c>
+      <c r="J163">
         <v>1</v>
-      </c>
-      <c r="G163">
-        <v>0</v>
-      </c>
-      <c r="H163">
-        <v>2</v>
-      </c>
-      <c r="I163">
-        <v>1</v>
-      </c>
-      <c r="J163">
-        <v>0</v>
       </c>
       <c r="K163">
         <v>0</v>
       </c>
       <c r="L163">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M163">
         <v>0</v>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>183</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
@@ -36474,25 +36564,25 @@
         <v>627</v>
       </c>
       <c r="C164">
-        <v>22</v>
+        <v>336</v>
       </c>
       <c r="D164">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -36501,13 +36591,13 @@
         <v>0</v>
       </c>
       <c r="L164">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M164">
         <v>0</v>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
@@ -36518,22 +36608,22 @@
         <v>628</v>
       </c>
       <c r="C165" s="147">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="D165" s="147">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E165" s="147">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F165" s="147">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G165" s="147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" s="147">
         <v>0</v>
@@ -36545,13 +36635,13 @@
         <v>0</v>
       </c>
       <c r="L165" s="147">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M165" s="147">
         <v>0</v>
       </c>
       <c r="N165" s="147">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
@@ -36694,40 +36784,40 @@
         <v>626</v>
       </c>
       <c r="C172">
-        <v>151</v>
+        <v>490</v>
       </c>
       <c r="D172">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="E172">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F172">
+        <v>92</v>
+      </c>
+      <c r="G172">
+        <v>4</v>
+      </c>
+      <c r="H172">
+        <v>35</v>
+      </c>
+      <c r="I172">
+        <v>11</v>
+      </c>
+      <c r="J172">
         <v>1</v>
-      </c>
-      <c r="G172">
-        <v>0</v>
-      </c>
-      <c r="H172">
-        <v>2</v>
-      </c>
-      <c r="I172">
-        <v>1</v>
-      </c>
-      <c r="J172">
-        <v>0</v>
       </c>
       <c r="K172">
         <v>0</v>
       </c>
       <c r="L172">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M172">
         <v>0</v>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>183</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
@@ -36738,25 +36828,25 @@
         <v>627</v>
       </c>
       <c r="C173">
-        <v>22</v>
+        <v>336</v>
       </c>
       <c r="D173">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I173">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -36765,13 +36855,13 @@
         <v>0</v>
       </c>
       <c r="L173">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M173">
         <v>0</v>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
@@ -36782,22 +36872,22 @@
         <v>628</v>
       </c>
       <c r="C174">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="D174">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F174">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -36809,13 +36899,13 @@
         <v>0</v>
       </c>
       <c r="L174">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M174">
         <v>0</v>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -36853,7 +36943,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>408</v>
       </c>
       <c r="B1" s="149"/>
@@ -36874,7 +36964,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -36895,19 +36985,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -36919,11 +37009,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -36985,7 +37075,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -38743,7 +38833,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>443</v>
       </c>
       <c r="B1" s="149"/>
@@ -38764,7 +38854,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -38785,19 +38875,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -38809,11 +38899,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -38875,7 +38965,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -40701,7 +40791,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>444</v>
       </c>
       <c r="B1" s="149"/>
@@ -40722,7 +40812,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -40743,19 +40833,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -40767,11 +40857,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -40833,7 +40923,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -42617,7 +42707,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>445</v>
       </c>
       <c r="B1" s="149"/>
@@ -42638,7 +42728,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -42659,19 +42749,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -42683,11 +42773,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -42749,7 +42839,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -44581,7 +44671,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>446</v>
       </c>
       <c r="B1" s="149"/>
@@ -44602,7 +44692,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -44623,19 +44713,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -44647,11 +44737,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -44713,7 +44803,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -46533,7 +46623,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>447</v>
       </c>
       <c r="B1" s="149"/>
@@ -46554,7 +46644,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -46575,19 +46665,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -46599,11 +46689,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -46665,7 +46755,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>
@@ -48321,7 +48411,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="170" t="s">
         <v>448</v>
       </c>
       <c r="B1" s="149"/>
@@ -48342,7 +48432,7 @@
       <c r="Q1" s="149"/>
     </row>
     <row r="2" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="155" t="s">
         <v>409</v>
       </c>
       <c r="B2" s="149"/>
@@ -48363,19 +48453,19 @@
       <c r="Q2" s="149"/>
     </row>
     <row r="3" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="169" t="s">
         <v>410</v>
       </c>
       <c r="B3" s="149"/>
-      <c r="C3" s="170" t="s">
+      <c r="C3" s="168" t="s">
         <v>411</v>
       </c>
       <c r="D3" s="149"/>
-      <c r="E3" s="166" t="s">
+      <c r="E3" s="171" t="s">
         <v>412</v>
       </c>
       <c r="F3" s="149"/>
-      <c r="G3" s="168" t="s">
+      <c r="G3" s="166" t="s">
         <v>413</v>
       </c>
       <c r="H3" s="149"/>
@@ -48387,11 +48477,11 @@
       <c r="L3" s="32" t="s">
         <v>415</v>
       </c>
-      <c r="M3" s="167" t="s">
+      <c r="M3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="N3" s="149"/>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="165" t="s">
         <v>416</v>
       </c>
       <c r="P3" s="149"/>
@@ -48453,7 +48543,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="167" t="s">
         <v>435</v>
       </c>
       <c r="B5" s="149"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos/REPORT FB&amp;STORE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82C3DAC-4D63-DE45-86D7-6DB0BB7231E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57309BE4-C13C-F54E-822A-681B8428F0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="660" windowWidth="29320" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2047" uniqueCount="648">
   <si>
     <t>CARASE FB &amp; STORE  •  BẢNG CHỈ SỐ TỔNG HỢP  •  T1/2025 → T9/2026</t>
   </si>
@@ -3451,12 +3451,12 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3473,11 +3473,11 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="46" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3513,16 +3513,16 @@
     <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11287,7 +11287,7 @@
     </row>
     <row r="22" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>473</v>
       </c>
       <c r="B23" s="149"/>
@@ -11310,7 +11310,7 @@
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="172" t="s">
+      <c r="A25" s="174" t="s">
         <v>474</v>
       </c>
       <c r="B25" s="149"/>
@@ -11327,7 +11327,7 @@
     </row>
     <row r="26" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:20" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="174" t="s">
+      <c r="A27" s="172" t="s">
         <v>475</v>
       </c>
       <c r="B27" s="149"/>
@@ -11340,7 +11340,7 @@
       <c r="I27" s="149"/>
       <c r="J27" s="149"/>
       <c r="K27" s="149"/>
-      <c r="L27" s="175"/>
+      <c r="L27" s="173"/>
       <c r="M27" s="79"/>
       <c r="N27" s="79"/>
       <c r="O27" s="79"/>
@@ -11573,7 +11573,7 @@
       <c r="T34" s="84"/>
     </row>
     <row r="35" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="174" t="s">
+      <c r="A35" s="172" t="s">
         <v>499</v>
       </c>
       <c r="B35" s="149"/>
@@ -11586,7 +11586,7 @@
       <c r="I35" s="149"/>
       <c r="J35" s="149"/>
       <c r="K35" s="149"/>
-      <c r="L35" s="175"/>
+      <c r="L35" s="173"/>
       <c r="M35" s="84"/>
       <c r="N35" s="84"/>
       <c r="O35" s="84"/>
@@ -11862,11 +11862,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A27:L27"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A25:L25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:L27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -14240,7 +14240,7 @@
     </row>
     <row r="22" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="23" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="173" t="s">
+      <c r="A23" s="175" t="s">
         <v>473</v>
       </c>
       <c r="B23" s="149"/>
@@ -14263,7 +14263,7 @@
     </row>
     <row r="24" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="172" t="s">
+      <c r="A25" s="174" t="s">
         <v>474</v>
       </c>
       <c r="B25" s="149"/>
@@ -16867,7 +16867,7 @@
     </row>
     <row r="23" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="173" t="s">
+      <c r="A24" s="175" t="s">
         <v>473</v>
       </c>
       <c r="B24" s="149"/>
@@ -16890,7 +16890,7 @@
     </row>
     <row r="25" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="172" t="s">
+      <c r="A26" s="174" t="s">
         <v>474</v>
       </c>
       <c r="B26" s="149"/>
@@ -18315,31 +18315,45 @@
       <c r="B26" s="48" t="s">
         <v>436</v>
       </c>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
+      <c r="C26" s="49">
+        <v>31744375</v>
+      </c>
+      <c r="D26" s="49">
+        <v>75</v>
+      </c>
       <c r="E26" s="49"/>
       <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
+      <c r="G26" s="49">
+        <v>5214808</v>
+      </c>
+      <c r="H26" s="49">
+        <v>3531997</v>
+      </c>
+      <c r="I26" s="49">
+        <v>3603998</v>
+      </c>
+      <c r="J26" s="49">
+        <v>37</v>
+      </c>
+      <c r="K26" s="49">
+        <v>14700</v>
+      </c>
       <c r="L26" s="50"/>
-      <c r="M26" s="8" t="str">
+      <c r="M26" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N26" s="8" t="str">
+        <v>12350803</v>
+      </c>
+      <c r="N26" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O26" s="8" t="str">
+        <v>44095178</v>
+      </c>
+      <c r="O26" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P26" s="8" t="str">
+        <v>423258.33333333331</v>
+      </c>
+      <c r="P26" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>333805.48648648651</v>
       </c>
       <c r="Q26" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18353,31 +18367,45 @@
       <c r="B27" s="48" t="s">
         <v>437</v>
       </c>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
+      <c r="C27" s="49">
+        <v>36027824</v>
+      </c>
+      <c r="D27" s="49">
+        <v>92</v>
+      </c>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
+      <c r="G27" s="49">
+        <v>3521500</v>
+      </c>
+      <c r="H27" s="49">
+        <v>1125002</v>
+      </c>
+      <c r="I27" s="49">
+        <v>645000</v>
+      </c>
+      <c r="J27" s="49">
+        <v>20</v>
+      </c>
+      <c r="K27" s="49">
+        <v>502400</v>
+      </c>
       <c r="L27" s="50"/>
-      <c r="M27" s="8" t="str">
+      <c r="M27" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N27" s="8" t="str">
+        <v>5291502</v>
+      </c>
+      <c r="N27" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O27" s="8" t="str">
+        <v>41319326</v>
+      </c>
+      <c r="O27" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P27" s="8" t="str">
+        <v>391606.78260869568</v>
+      </c>
+      <c r="P27" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>264575.09999999998</v>
       </c>
       <c r="Q27" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18391,31 +18419,45 @@
       <c r="B28" s="48" t="s">
         <v>438</v>
       </c>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
+      <c r="C28" s="49">
+        <v>33193661</v>
+      </c>
+      <c r="D28" s="49">
+        <v>75</v>
+      </c>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
+      <c r="G28" s="49">
+        <v>4569498</v>
+      </c>
+      <c r="H28" s="49">
+        <v>2523001</v>
+      </c>
+      <c r="I28" s="49">
+        <v>2478502</v>
+      </c>
+      <c r="J28" s="49">
+        <v>33</v>
+      </c>
+      <c r="K28" s="49">
+        <v>2628696</v>
+      </c>
       <c r="L28" s="50"/>
-      <c r="M28" s="8" t="str">
+      <c r="M28" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N28" s="8" t="str">
+        <v>9571001</v>
+      </c>
+      <c r="N28" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O28" s="8" t="str">
+        <v>42764662</v>
+      </c>
+      <c r="O28" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P28" s="8" t="str">
+        <v>442582.14666666667</v>
+      </c>
+      <c r="P28" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>290030.33333333331</v>
       </c>
       <c r="Q28" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18429,31 +18471,45 @@
       <c r="B29" s="48" t="s">
         <v>439</v>
       </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
+      <c r="C29" s="49">
+        <v>28528630</v>
+      </c>
+      <c r="D29" s="49">
+        <v>72</v>
+      </c>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
+      <c r="G29" s="49">
+        <v>9246499</v>
+      </c>
+      <c r="H29" s="49">
+        <v>5211900</v>
+      </c>
+      <c r="I29" s="49">
+        <v>3829999</v>
+      </c>
+      <c r="J29" s="49">
+        <v>49</v>
+      </c>
+      <c r="K29" s="49">
+        <v>719999</v>
+      </c>
       <c r="L29" s="50"/>
-      <c r="M29" s="8" t="str">
+      <c r="M29" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N29" s="8" t="str">
+        <v>18288398</v>
+      </c>
+      <c r="N29" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O29" s="8" t="str">
+        <v>46817028</v>
+      </c>
+      <c r="O29" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P29" s="8" t="str">
+        <v>396230.97222222225</v>
+      </c>
+      <c r="P29" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>373232.61224489799</v>
       </c>
       <c r="Q29" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18467,31 +18523,43 @@
       <c r="B30" s="48" t="s">
         <v>440</v>
       </c>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
+      <c r="C30" s="49">
+        <v>29080521</v>
+      </c>
+      <c r="D30" s="49">
+        <v>74</v>
+      </c>
       <c r="E30" s="49"/>
       <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
+      <c r="G30" s="49">
+        <v>7425502</v>
+      </c>
+      <c r="H30" s="49">
+        <v>4797503</v>
+      </c>
+      <c r="I30" s="49">
+        <v>5179503</v>
+      </c>
+      <c r="J30" s="49">
+        <v>61</v>
+      </c>
       <c r="K30" s="49"/>
       <c r="L30" s="50"/>
-      <c r="M30" s="8" t="str">
+      <c r="M30" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N30" s="8" t="str">
+        <v>17402508</v>
+      </c>
+      <c r="N30" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O30" s="8" t="str">
+        <v>46483029</v>
+      </c>
+      <c r="O30" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P30" s="8" t="str">
+        <v>392980.01351351349</v>
+      </c>
+      <c r="P30" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>285287.01639344264</v>
       </c>
       <c r="Q30" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18505,31 +18573,45 @@
       <c r="B31" s="52" t="s">
         <v>441</v>
       </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
+      <c r="C31" s="49">
+        <v>34696992</v>
+      </c>
+      <c r="D31" s="49">
+        <v>83</v>
+      </c>
       <c r="E31" s="49"/>
       <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
+      <c r="G31" s="49">
+        <v>9942762</v>
+      </c>
+      <c r="H31" s="49">
+        <v>4676300</v>
+      </c>
+      <c r="I31" s="49">
+        <v>3529497</v>
+      </c>
+      <c r="J31" s="49">
+        <v>63</v>
+      </c>
+      <c r="K31" s="49">
+        <v>1104000</v>
+      </c>
       <c r="L31" s="50"/>
-      <c r="M31" s="8" t="str">
+      <c r="M31" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N31" s="8" t="str">
+        <v>18148559</v>
+      </c>
+      <c r="N31" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O31" s="8" t="str">
+        <v>52845551</v>
+      </c>
+      <c r="O31" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P31" s="8" t="str">
+        <v>418036.04819277109</v>
+      </c>
+      <c r="P31" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>288072.36507936509</v>
       </c>
       <c r="Q31" s="21" t="str">
         <f t="shared" si="4"/>
@@ -18543,31 +18625,43 @@
       <c r="B32" s="52" t="s">
         <v>442</v>
       </c>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
+      <c r="C32" s="49">
+        <v>25823132</v>
+      </c>
+      <c r="D32" s="49">
+        <v>67</v>
+      </c>
       <c r="E32" s="49"/>
       <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
+      <c r="G32" s="49">
+        <v>9085999</v>
+      </c>
+      <c r="H32" s="49">
+        <v>3328500</v>
+      </c>
+      <c r="I32" s="49">
+        <v>3209251</v>
+      </c>
+      <c r="J32" s="49">
+        <v>38</v>
+      </c>
       <c r="K32" s="49"/>
       <c r="L32" s="50"/>
-      <c r="M32" s="8" t="str">
+      <c r="M32" s="8">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N32" s="8" t="str">
+        <v>15623750</v>
+      </c>
+      <c r="N32" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O32" s="8" t="str">
+        <v>41446882</v>
+      </c>
+      <c r="O32" s="8">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="P32" s="8" t="str">
+        <v>385419.88059701491</v>
+      </c>
+      <c r="P32" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>411151.31578947371</v>
       </c>
       <c r="Q32" s="21" t="str">
         <f t="shared" si="4"/>
@@ -19115,20 +19209,20 @@
         <v>529</v>
       </c>
       <c r="C7" s="124">
-        <v>0</v>
+        <v>219095135</v>
       </c>
       <c r="D7" s="125">
         <v>235456103</v>
       </c>
       <c r="E7" s="126">
         <f>IFERROR(IF(D7&gt;0,C7/D7,""),"")</f>
-        <v>0</v>
+        <v>0.93051372297621016</v>
       </c>
       <c r="F7" s="124">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="G7" s="124">
-        <v>0</v>
+        <v>407240</v>
       </c>
       <c r="H7" s="127">
         <f>IFERROR(SUM('📅 DAILY T9'!F26:F32),0)</f>
@@ -19139,17 +19233,17 @@
         <v/>
       </c>
       <c r="J7" s="129">
-        <v>0</v>
+        <v>96676521</v>
       </c>
       <c r="K7" s="125">
         <v>126396657</v>
       </c>
       <c r="L7" s="126">
         <f>IFERROR(IF(K7&gt;0,J7/K7,""),"")</f>
-        <v>0</v>
+        <v>0.76486612300197143</v>
       </c>
       <c r="M7" s="130">
-        <v>0</v>
+        <v>315771656</v>
       </c>
       <c r="N7" s="131"/>
     </row>
@@ -19225,7 +19319,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="158" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="149"/>
@@ -19383,7 +19477,7 @@
       <c r="X4" s="149"/>
     </row>
     <row r="5" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="159" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="149"/>
@@ -19480,7 +19574,7 @@
       </c>
       <c r="X6" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35),0)</f>
-        <v>675481017</v>
+        <v>894576152</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19553,7 +19647,7 @@
       </c>
       <c r="X7" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!D$6:D$35),0)</f>
-        <v>1558</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19626,7 +19720,7 @@
       </c>
       <c r="X8" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)/SUM('📅 DAILY T9'!D$6:D$35),"")</f>
-        <v>433556.49358151475</v>
+        <v>426801.5992366412</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19698,7 +19792,7 @@
         <v>4841</v>
       </c>
       <c r="X9" s="11">
-        <v>3411</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19819,7 +19913,7 @@
       </c>
       <c r="X11" s="12">
         <f t="shared" si="0"/>
-        <v>0.45675754910583405</v>
+        <v>0.49845422116527943</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -19851,7 +19945,7 @@
       <c r="X12" s="14"/>
     </row>
     <row r="13" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="158" t="s">
+      <c r="A13" s="159" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="149"/>
@@ -19975,7 +20069,7 @@
         <v>747</v>
       </c>
       <c r="X15" s="11">
-        <v>449</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20047,7 +20141,7 @@
         <v>433990</v>
       </c>
       <c r="X16" s="11">
-        <v>399217</v>
+        <v>399494</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20119,7 +20213,7 @@
         <v>115</v>
       </c>
       <c r="X17" s="13">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20191,7 +20285,7 @@
         <v>74</v>
       </c>
       <c r="X18" s="13">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20291,7 +20385,7 @@
         <v>1655</v>
       </c>
       <c r="X20" s="11">
-        <v>1009</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20363,7 +20457,7 @@
         <v>500556</v>
       </c>
       <c r="X21" s="11">
-        <v>491806</v>
+        <v>495492</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20435,7 +20529,7 @@
         <v>0.68899999999999995</v>
       </c>
       <c r="X22" s="13">
-        <v>0.69199999999999995</v>
+        <v>0.68189999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20507,7 +20601,7 @@
         <v>490</v>
       </c>
       <c r="X23" s="11">
-        <v>285</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20579,7 +20673,7 @@
         <v>473743</v>
       </c>
       <c r="X24" s="11">
-        <v>416474</v>
+        <v>455758</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20651,7 +20745,7 @@
         <v>483</v>
       </c>
       <c r="X25" s="11">
-        <v>306</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20723,7 +20817,7 @@
         <v>524029</v>
       </c>
       <c r="X26" s="11">
-        <v>506565</v>
+        <v>504574</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20795,7 +20889,7 @@
         <v>682</v>
       </c>
       <c r="X27" s="11">
-        <v>418</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20867,7 +20961,7 @@
         <v>503197</v>
       </c>
       <c r="X28" s="11">
-        <v>532365</v>
+        <v>516325</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20967,7 +21061,7 @@
         <v>1348</v>
       </c>
       <c r="X30" s="11">
-        <v>808</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21039,7 +21133,7 @@
         <v>517786</v>
       </c>
       <c r="X31" s="11">
-        <v>520091</v>
+        <v>524133</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21111,7 +21205,7 @@
         <v>1740028</v>
       </c>
       <c r="X32" s="11">
-        <v>1693483</v>
+        <v>1722425</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -21143,7 +21237,7 @@
       <c r="X33" s="149"/>
     </row>
     <row r="34" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="151" t="s">
         <v>60</v>
       </c>
       <c r="B34" s="149"/>
@@ -21239,7 +21333,7 @@
         <v>478057804</v>
       </c>
       <c r="X35" s="8">
-        <v>320897476</v>
+        <v>417573997</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21311,7 +21405,7 @@
         <v>241642155</v>
       </c>
       <c r="X36" s="8">
-        <v>165755667</v>
+        <v>214762235</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21383,7 +21477,7 @@
         <v>124655638</v>
       </c>
       <c r="X37" s="8">
-        <v>87516027</v>
+        <v>112710230</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21455,7 +21549,7 @@
         <v>111760011</v>
       </c>
       <c r="X38" s="8">
-        <v>67625782</v>
+        <v>90101532</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21527,7 +21621,7 @@
         <v>1536</v>
       </c>
       <c r="X39" s="8">
-        <v>996</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21600,7 +21694,7 @@
       </c>
       <c r="X40" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!M$6:M$35)/SUM('📅 DAILY T9'!J$6:J$35),"")</f>
-        <v>322186.22088353412</v>
+        <v>321953.73708558211</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21627,7 +21721,7 @@
       <c r="U41" s="149"/>
       <c r="V41" s="149"/>
       <c r="W41" s="149"/>
-      <c r="X41" s="151"/>
+      <c r="X41" s="150"/>
     </row>
     <row r="42" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="156"/>
@@ -21653,7 +21747,7 @@
       <c r="U42" s="149"/>
       <c r="V42" s="149"/>
       <c r="W42" s="149"/>
-      <c r="X42" s="151"/>
+      <c r="X42" s="150"/>
     </row>
     <row r="43" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="20"/>
@@ -21724,7 +21818,7 @@
         <v>527</v>
       </c>
       <c r="X43" s="11">
-        <v>353</v>
+        <v>453</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21796,7 +21890,7 @@
         <v>338511</v>
       </c>
       <c r="X44" s="11">
-        <v>356240</v>
+        <v>368702</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21867,8 +21961,8 @@
       <c r="W45" s="49">
         <v>60</v>
       </c>
-      <c r="X45" s="13">
-        <v>44</v>
+      <c r="X45" s="144">
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -21939,8 +22033,8 @@
       <c r="W46" s="49">
         <v>34</v>
       </c>
-      <c r="X46" s="13">
-        <v>21</v>
+      <c r="X46" s="144">
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22040,7 +22134,7 @@
         <v>791</v>
       </c>
       <c r="X48" s="11">
-        <v>503</v>
+        <v>631</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22112,7 +22206,7 @@
         <v>380772</v>
       </c>
       <c r="X49" s="11">
-        <v>389691</v>
+        <v>398973</v>
       </c>
     </row>
     <row r="50" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22184,7 +22278,7 @@
         <v>0.60019999999999996</v>
       </c>
       <c r="X50" s="13">
-        <v>0.58760000000000001</v>
+        <v>0.58209999999999995</v>
       </c>
     </row>
     <row r="51" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22256,7 +22350,7 @@
         <v>174</v>
       </c>
       <c r="X51" s="11">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22328,7 +22422,7 @@
         <v>500388</v>
       </c>
       <c r="X52" s="11">
-        <v>474968</v>
+        <v>526821</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22400,7 +22494,7 @@
         <v>223</v>
       </c>
       <c r="X53" s="11">
-        <v>145</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22472,7 +22566,7 @@
         <v>369027</v>
       </c>
       <c r="X54" s="11">
-        <v>354539</v>
+        <v>374974</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22544,7 +22638,7 @@
         <v>394</v>
       </c>
       <c r="X55" s="11">
-        <v>261</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22616,7 +22710,7 @@
         <v>334595</v>
       </c>
       <c r="X56" s="11">
-        <v>377527</v>
+        <v>362945</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22716,7 +22810,7 @@
         <v>585</v>
       </c>
       <c r="X58" s="11">
-        <v>384</v>
+        <v>477</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22788,7 +22882,7 @@
         <v>406621</v>
       </c>
       <c r="X59" s="11">
-        <v>423650</v>
+        <v>433402</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22860,7 +22954,7 @@
         <v>1389818</v>
       </c>
       <c r="X60" s="11">
-        <v>1529432</v>
+        <v>1456251</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -22942,7 +23036,7 @@
         <v>30530917</v>
       </c>
       <c r="X63" s="8">
-        <v>11981487</v>
+        <v>16951282</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23014,7 +23108,7 @@
         <v>1.8781108525479821E-2</v>
       </c>
       <c r="X64" s="132">
-        <v>1.2025035751148031E-2</v>
+        <v>1.2918705997875859E-2</v>
       </c>
     </row>
     <row r="65" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -23144,11 +23238,11 @@
       </c>
       <c r="X68" s="8">
         <f>IFERROR(SUM('📅 DAILY T9'!C$6:C$35)+SUM('📅 DAILY T9'!G$6:I$35),0)</f>
-        <v>996378493</v>
+        <v>1312150149</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="150"/>
+      <c r="A69" s="148"/>
       <c r="B69" s="149"/>
       <c r="C69" s="149"/>
       <c r="D69" s="149"/>
@@ -23171,7 +23265,7 @@
       <c r="U69" s="149"/>
       <c r="V69" s="149"/>
       <c r="W69" s="149"/>
-      <c r="X69" s="151"/>
+      <c r="X69" s="150"/>
     </row>
     <row r="70" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="25"/>
@@ -23242,7 +23336,7 @@
         <v>1.135</v>
       </c>
       <c r="X70" s="14">
-        <v>1.121</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23314,7 +23408,7 @@
         <v>20501</v>
       </c>
       <c r="X71" s="11">
-        <v>20390</v>
+        <v>20893</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23386,7 +23480,7 @@
         <v>1449</v>
       </c>
       <c r="X72" s="11">
-        <v>793</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23694,7 +23788,7 @@
         <v>1418862</v>
       </c>
       <c r="X77" s="11">
-        <v>1380908</v>
+        <v>1404507</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23766,7 +23860,7 @@
         <v>914424</v>
       </c>
       <c r="X78" s="11">
-        <v>1006283</v>
+        <v>958134</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23838,7 +23932,7 @@
         <v>1740028</v>
       </c>
       <c r="X79" s="11">
-        <v>1693483</v>
+        <v>1722425</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -23910,7 +24004,7 @@
         <v>1389818</v>
       </c>
       <c r="X80" s="11">
-        <v>1529432</v>
+        <v>1456251</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24240,6 +24334,7 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A5:X5"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A14:X14"/>
     <mergeCell ref="A2:X2"/>
@@ -24247,9 +24342,8 @@
     <mergeCell ref="A41:X41"/>
     <mergeCell ref="A19:X19"/>
     <mergeCell ref="A33:X33"/>
-    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A69:X69"/>
     <mergeCell ref="A34:X34"/>
-    <mergeCell ref="A69:X69"/>
     <mergeCell ref="A29:X29"/>
     <mergeCell ref="A4:X4"/>
     <mergeCell ref="A81:X81"/>
@@ -30456,7 +30550,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:N174"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -33504,40 +33598,40 @@
         <v>626</v>
       </c>
       <c r="C83">
-        <v>508</v>
+        <v>718</v>
       </c>
       <c r="D83">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="E83">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F83">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="G83">
+        <v>12</v>
+      </c>
+      <c r="H83">
+        <v>75</v>
+      </c>
+      <c r="I83">
+        <v>37</v>
+      </c>
+      <c r="J83">
+        <v>25</v>
+      </c>
+      <c r="K83">
+        <v>18</v>
+      </c>
+      <c r="L83">
+        <v>97</v>
+      </c>
+      <c r="M83">
         <v>11</v>
       </c>
-      <c r="H83">
-        <v>59</v>
-      </c>
-      <c r="I83">
-        <v>29</v>
-      </c>
-      <c r="J83">
-        <v>20</v>
-      </c>
-      <c r="K83">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>79</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
       <c r="N83">
-        <v>211</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33548,22 +33642,22 @@
         <v>627</v>
       </c>
       <c r="C84">
-        <v>656</v>
+        <v>881</v>
       </c>
       <c r="D84">
-        <v>477</v>
+        <v>646</v>
       </c>
       <c r="E84">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="F84">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G84">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H84">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I84">
         <v>3</v>
@@ -33572,16 +33666,16 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="L84">
-        <v>179</v>
+        <v>120</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N84">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33592,19 +33686,19 @@
         <v>628</v>
       </c>
       <c r="C85">
-        <v>338</v>
+        <v>459</v>
       </c>
       <c r="D85">
-        <v>275</v>
+        <v>386</v>
       </c>
       <c r="E85">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F85">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -33616,13 +33710,13 @@
         <v>1</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L85">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="N85">
         <v>61</v>
@@ -36520,40 +36614,40 @@
         <v>626</v>
       </c>
       <c r="C163">
-        <v>490</v>
+        <v>661</v>
       </c>
       <c r="D163">
-        <v>266</v>
+        <v>361</v>
       </c>
       <c r="E163">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="F163">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="G163">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H163">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I163">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L163">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="M163">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N163">
-        <v>183</v>
+        <v>247</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
@@ -36564,16 +36658,16 @@
         <v>627</v>
       </c>
       <c r="C164">
-        <v>336</v>
+        <v>413</v>
       </c>
       <c r="D164">
-        <v>289</v>
+        <v>355</v>
       </c>
       <c r="E164">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F164">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -36588,16 +36682,16 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L164">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="M164">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N164">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
@@ -36608,19 +36702,19 @@
         <v>628</v>
       </c>
       <c r="C165" s="147">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="D165" s="147">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="E165" s="147">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F165" s="147">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G165" s="147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165" s="147">
         <v>1</v>
@@ -36632,280 +36726,16 @@
         <v>0</v>
       </c>
       <c r="K165" s="147">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L165" s="147">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="M165" s="147">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N165" s="147">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
-        <v>646</v>
-      </c>
-      <c r="B166" t="s">
-        <v>626</v>
-      </c>
-      <c r="C166">
-        <v>689</v>
-      </c>
-      <c r="D166">
-        <v>368</v>
-      </c>
-      <c r="E166">
-        <v>91</v>
-      </c>
-      <c r="F166">
-        <v>132</v>
-      </c>
-      <c r="G166">
-        <v>21</v>
-      </c>
-      <c r="H166">
-        <v>61</v>
-      </c>
-      <c r="I166">
-        <v>15</v>
-      </c>
-      <c r="J166">
-        <v>1</v>
-      </c>
-      <c r="K166">
-        <v>23</v>
-      </c>
-      <c r="L166">
-        <v>161</v>
-      </c>
-      <c r="M166">
-        <v>22</v>
-      </c>
-      <c r="N166">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>646</v>
-      </c>
-      <c r="B167" t="s">
-        <v>627</v>
-      </c>
-      <c r="C167">
-        <v>553</v>
-      </c>
-      <c r="D167">
-        <v>480</v>
-      </c>
-      <c r="E167">
-        <v>41</v>
-      </c>
-      <c r="F167">
-        <v>24</v>
-      </c>
-      <c r="G167">
-        <v>5</v>
-      </c>
-      <c r="H167">
-        <v>3</v>
-      </c>
-      <c r="I167">
-        <v>0</v>
-      </c>
-      <c r="J167">
-        <v>0</v>
-      </c>
-      <c r="K167">
-        <v>106</v>
-      </c>
-      <c r="L167">
-        <v>68</v>
-      </c>
-      <c r="M167">
-        <v>114</v>
-      </c>
-      <c r="N167">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>646</v>
-      </c>
-      <c r="B168" t="s">
-        <v>628</v>
-      </c>
-      <c r="C168">
-        <v>272</v>
-      </c>
-      <c r="D168">
-        <v>251</v>
-      </c>
-      <c r="E168">
-        <v>18</v>
-      </c>
-      <c r="F168">
-        <v>3</v>
-      </c>
-      <c r="G168">
-        <v>0</v>
-      </c>
-      <c r="H168">
-        <v>0</v>
-      </c>
-      <c r="I168">
-        <v>0</v>
-      </c>
-      <c r="J168">
-        <v>0</v>
-      </c>
-      <c r="K168">
-        <v>75</v>
-      </c>
-      <c r="L168">
-        <v>21</v>
-      </c>
-      <c r="M168">
-        <v>42</v>
-      </c>
-      <c r="N168">
         <v>47</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
-        <v>647</v>
-      </c>
-      <c r="B172" t="s">
-        <v>626</v>
-      </c>
-      <c r="C172">
-        <v>490</v>
-      </c>
-      <c r="D172">
-        <v>266</v>
-      </c>
-      <c r="E172">
-        <v>81</v>
-      </c>
-      <c r="F172">
-        <v>92</v>
-      </c>
-      <c r="G172">
-        <v>4</v>
-      </c>
-      <c r="H172">
-        <v>35</v>
-      </c>
-      <c r="I172">
-        <v>11</v>
-      </c>
-      <c r="J172">
-        <v>1</v>
-      </c>
-      <c r="K172">
-        <v>0</v>
-      </c>
-      <c r="L172">
-        <v>91</v>
-      </c>
-      <c r="M172">
-        <v>0</v>
-      </c>
-      <c r="N172">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
-        <v>647</v>
-      </c>
-      <c r="B173" t="s">
-        <v>627</v>
-      </c>
-      <c r="C173">
-        <v>336</v>
-      </c>
-      <c r="D173">
-        <v>289</v>
-      </c>
-      <c r="E173">
-        <v>30</v>
-      </c>
-      <c r="F173">
-        <v>8</v>
-      </c>
-      <c r="G173">
-        <v>1</v>
-      </c>
-      <c r="H173">
-        <v>4</v>
-      </c>
-      <c r="I173">
-        <v>4</v>
-      </c>
-      <c r="J173">
-        <v>0</v>
-      </c>
-      <c r="K173">
-        <v>0</v>
-      </c>
-      <c r="L173">
-        <v>81</v>
-      </c>
-      <c r="M173">
-        <v>0</v>
-      </c>
-      <c r="N173">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>647</v>
-      </c>
-      <c r="B174" t="s">
-        <v>628</v>
-      </c>
-      <c r="C174">
-        <v>152</v>
-      </c>
-      <c r="D174">
-        <v>133</v>
-      </c>
-      <c r="E174">
-        <v>11</v>
-      </c>
-      <c r="F174">
-        <v>6</v>
-      </c>
-      <c r="G174">
-        <v>1</v>
-      </c>
-      <c r="H174">
-        <v>1</v>
-      </c>
-      <c r="I174">
-        <v>0</v>
-      </c>
-      <c r="J174">
-        <v>0</v>
-      </c>
-      <c r="K174">
-        <v>0</v>
-      </c>
-      <c r="L174">
-        <v>31</v>
-      </c>
-      <c r="M174">
-        <v>0</v>
-      </c>
-      <c r="N174">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19606,67 +19606,67 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4841</v>
+        <v>4840</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>2994</v>
+        <v>2988</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>3118</v>
+        <v>3107</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>3205</v>
+        <v>3191</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>2797</v>
+        <v>2792</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>3352</v>
+        <v>3333</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>3479</v>
+        <v>3431</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>3548</v>
+        <v>3486</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>3897</v>
+        <v>3818</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>3036</v>
+        <v>2978</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>2810</v>
+        <v>2761</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>2589</v>
+        <v>2540</v>
       </c>
       <c r="T7" s="7" t="n">
-        <v>2512</v>
+        <v>2451</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>2529</v>
+        <v>2470</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>2834</v>
+        <v>2822</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>2644</v>
+        <v>2630</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>2353</v>
+        <v>2338</v>
       </c>
       <c r="Y7" s="153" t="n">
         <v>319</v>
@@ -19687,67 +19687,67 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>535688</v>
+        <v>535799</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>562535</v>
+        <v>562739</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>545387</v>
+        <v>545561</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>519887</v>
+        <v>520219</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>502099</v>
+        <v>502412</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>496028</v>
+        <v>497024</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>486419</v>
+        <v>488141</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>475599</v>
+        <v>477686</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>447916</v>
+        <v>448718</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>419124</v>
+        <v>421514</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>417665</v>
+        <v>423509</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>435292</v>
+        <v>443034</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>445178</v>
+        <v>454389</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>459771</v>
+        <v>468726</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>445962</v>
+        <v>453876</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>448423</v>
+        <v>457074</v>
       </c>
       <c r="T8" s="7" t="n">
-        <v>442222</v>
+        <v>453228</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>438224</v>
+        <v>448691</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>422208</v>
+        <v>424004</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>436078</v>
+        <v>438399</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>423495</v>
+        <v>426212</v>
       </c>
       <c r="Y8" s="153" t="n">
         <v>427027</v>
@@ -19882,67 +19882,67 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.5028565492884596</v>
+        <v>0.5027526748</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.4373117768267554</v>
+        <v>0.4371532731</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0.4823927418114716</v>
+        <v>0.4822389666</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.4607900943396226</v>
+        <v>0.460495283</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.5267300754345687</v>
+        <v>0.526402099</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>0.5207862236910767</v>
+        <v>0.5197425639</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>0.4567159806650066</v>
+        <v>0.4551047312</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>0.5191965008909768</v>
+        <v>0.5169285599</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>0.4934721242060692</v>
+        <v>0.4925899788</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.5269611696274171</v>
+        <v>0.5239742179</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>0.5043490866917947</v>
+        <v>0.497390548</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>0.4876975945017182</v>
+        <v>0.4791752577</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>0.4304174950298211</v>
+        <v>0.4216920698</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>0.4122759369907659</v>
+        <v>0.4043997827</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>0.4853195164075993</v>
+        <v>0.4768566494</v>
       </c>
       <c r="S11" s="12" t="n">
-        <v>0.5179035807161432</v>
+        <v>0.5081016202999999</v>
       </c>
       <c r="T11" s="12" t="n">
-        <v>0.4802141082011088</v>
+        <v>0.468552858</v>
       </c>
       <c r="U11" s="12" t="n">
-        <v>0.4368630160649508</v>
+        <v>0.4266712731</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0.5525443556248781</v>
+        <v>0.5502047183</v>
       </c>
       <c r="W11" s="12" t="n">
-        <v>0.5461681470770502</v>
+        <v>0.5432761826</v>
       </c>
       <c r="X11" s="12" t="n">
-        <v>0.5595719381688466</v>
+        <v>0.5560047562</v>
       </c>
       <c r="Y11" s="12">
         <f>Y7/Y9</f>
@@ -31924,7 +31924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:N165"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="176" min="1" max="1"/>
@@ -32055,40 +32055,40 @@
         </is>
       </c>
       <c r="C5" s="102" t="n">
-        <v>780</v>
+        <v>740</v>
       </c>
       <c r="D5" s="103" t="n">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="E5" s="103" t="n">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="F5" s="103" t="n">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="G5" s="103" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="H5" s="103" t="n">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="I5" s="103" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J5" s="103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" s="104" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L5" s="105" t="n">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="M5" s="104" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N5" s="105" t="n">
-        <v>382</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="176">
@@ -32103,40 +32103,40 @@
         </is>
       </c>
       <c r="C6" s="102" t="n">
-        <v>1082</v>
+        <v>630</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>792</v>
+        <v>544</v>
       </c>
       <c r="E6" s="103" t="n">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="F6" s="103" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="G6" s="103" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H6" s="103" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I6" s="103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="103" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="104" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L6" s="105" t="n">
-        <v>346</v>
+        <v>59</v>
       </c>
       <c r="M6" s="104" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="N6" s="105" t="n">
-        <v>139</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="176">
@@ -32151,22 +32151,22 @@
         </is>
       </c>
       <c r="C7" s="102" t="n">
-        <v>1316</v>
+        <v>1436</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>1181</v>
+        <v>1295</v>
       </c>
       <c r="E7" s="103" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F7" s="103" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G7" s="103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="104" t="n">
         <v>0</v>
@@ -32175,16 +32175,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="104" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="L7" s="105" t="n">
-        <v>439</v>
+        <v>127</v>
       </c>
       <c r="M7" s="104" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="N7" s="105" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" ht="4.5" customHeight="1" s="176">
@@ -32215,40 +32215,40 @@
         </is>
       </c>
       <c r="C9" s="102" t="n">
-        <v>418</v>
+        <v>379</v>
       </c>
       <c r="D9" s="103" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E9" s="103" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F9" s="103" t="n">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="G9" s="103" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" s="103" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="I9" s="103" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J9" s="103" t="n">
         <v>11</v>
       </c>
       <c r="K9" s="104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" s="105" t="n">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="M9" s="104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N9" s="105" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="176">
@@ -32263,22 +32263,22 @@
         </is>
       </c>
       <c r="C10" s="102" t="n">
-        <v>567</v>
+        <v>365</v>
       </c>
       <c r="D10" s="103" t="n">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="E10" s="103" t="n">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="F10" s="103" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="G10" s="103" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H10" s="103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I10" s="103" t="n">
         <v>2</v>
@@ -32287,16 +32287,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="104" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L10" s="105" t="n">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="M10" s="104" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="N10" s="105" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="176">
@@ -32311,22 +32311,22 @@
         </is>
       </c>
       <c r="C11" s="102" t="n">
-        <v>750</v>
+        <v>893</v>
       </c>
       <c r="D11" s="103" t="n">
-        <v>636</v>
+        <v>763</v>
       </c>
       <c r="E11" s="103" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F11" s="103" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G11" s="103" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H11" s="103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="104" t="n">
         <v>0</v>
@@ -32335,16 +32335,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="104" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="L11" s="105" t="n">
-        <v>239</v>
+        <v>84</v>
       </c>
       <c r="M11" s="104" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="N11" s="105" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" ht="4.5" customHeight="1" s="176">
@@ -32378,37 +32378,37 @@
         <v>483</v>
       </c>
       <c r="D13" s="103" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E13" s="103" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="F13" s="103" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="G13" s="103" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H13" s="103" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I13" s="103" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J13" s="103" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K13" s="104" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="105" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="M13" s="104" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N13" s="105" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="176">
@@ -32423,40 +32423,40 @@
         </is>
       </c>
       <c r="C14" s="102" t="n">
-        <v>695</v>
+        <v>384</v>
       </c>
       <c r="D14" s="103" t="n">
-        <v>493</v>
+        <v>317</v>
       </c>
       <c r="E14" s="103" t="n">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="F14" s="103" t="n">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G14" s="103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" s="103" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I14" s="103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="104" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L14" s="105" t="n">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="M14" s="104" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="N14" s="105" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="176">
@@ -32471,22 +32471,22 @@
         </is>
       </c>
       <c r="C15" s="102" t="n">
-        <v>844</v>
+        <v>987</v>
       </c>
       <c r="D15" s="103" t="n">
-        <v>740</v>
+        <v>870</v>
       </c>
       <c r="E15" s="103" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F15" s="103" t="n">
         <v>15</v>
       </c>
       <c r="G15" s="103" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H15" s="103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="104" t="n">
         <v>0</v>
@@ -32495,16 +32495,16 @@
         <v>0</v>
       </c>
       <c r="K15" s="104" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L15" s="105" t="n">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="M15" s="104" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="N15" s="105" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" ht="4.5" customHeight="1" s="176">
@@ -32535,40 +32535,40 @@
         </is>
       </c>
       <c r="C17" s="102" t="n">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="D17" s="103" t="n">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E17" s="103" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="F17" s="103" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G17" s="103" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H17" s="103" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="I17" s="103" t="n">
         <v>21</v>
       </c>
       <c r="J17" s="103" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K17" s="104" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L17" s="105" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M17" s="104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N17" s="105" t="n">
-        <v>232</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="176">
@@ -32583,40 +32583,40 @@
         </is>
       </c>
       <c r="C18" s="102" t="n">
-        <v>611</v>
+        <v>519</v>
       </c>
       <c r="D18" s="103" t="n">
-        <v>429</v>
+        <v>386</v>
       </c>
       <c r="E18" s="103" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="F18" s="103" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="G18" s="103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I18" s="103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="104" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L18" s="105" t="n">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="M18" s="104" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N18" s="105" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="176">
@@ -32631,19 +32631,19 @@
         </is>
       </c>
       <c r="C19" s="102" t="n">
-        <v>782</v>
+        <v>996</v>
       </c>
       <c r="D19" s="103" t="n">
-        <v>696</v>
+        <v>885</v>
       </c>
       <c r="E19" s="103" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="F19" s="103" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G19" s="103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" s="103" t="n">
         <v>6</v>
@@ -32655,16 +32655,16 @@
         <v>0</v>
       </c>
       <c r="K19" s="104" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="L19" s="105" t="n">
-        <v>220</v>
+        <v>106</v>
       </c>
       <c r="M19" s="104" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="N19" s="105" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="4.5" customHeight="1" s="176">
@@ -32695,40 +32695,40 @@
         </is>
       </c>
       <c r="C21" s="102" t="n">
-        <v>522</v>
+        <v>606</v>
       </c>
       <c r="D21" s="103" t="n">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="E21" s="103" t="n">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F21" s="103" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G21" s="103" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" s="103" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I21" s="103" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J21" s="103" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K21" s="104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L21" s="105" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="M21" s="104" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N21" s="105" t="n">
-        <v>246</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="176">
@@ -32743,40 +32743,40 @@
         </is>
       </c>
       <c r="C22" s="102" t="n">
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="D22" s="103" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E22" s="103" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="F22" s="103" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G22" s="103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H22" s="103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I22" s="103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="104" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L22" s="105" t="n">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="M22" s="104" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="N22" s="105" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="176">
@@ -32791,22 +32791,22 @@
         </is>
       </c>
       <c r="C23" s="102" t="n">
-        <v>736</v>
+        <v>908</v>
       </c>
       <c r="D23" s="103" t="n">
-        <v>636</v>
+        <v>793</v>
       </c>
       <c r="E23" s="103" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F23" s="103" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G23" s="103" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="103" t="n">
         <v>5</v>
-      </c>
-      <c r="H23" s="103" t="n">
-        <v>6</v>
       </c>
       <c r="I23" s="104" t="n">
         <v>0</v>
@@ -32815,16 +32815,16 @@
         <v>0</v>
       </c>
       <c r="K23" s="104" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="L23" s="105" t="n">
-        <v>183</v>
+        <v>69</v>
       </c>
       <c r="M23" s="104" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="N23" s="105" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" ht="4.5" customHeight="1" s="176">
@@ -32855,40 +32855,40 @@
         </is>
       </c>
       <c r="C25" s="102" t="n">
-        <v>467</v>
+        <v>568</v>
       </c>
       <c r="D25" s="103" t="n">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="E25" s="103" t="n">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="F25" s="103" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G25" s="103" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H25" s="103" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I25" s="103" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J25" s="103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" s="104" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L25" s="105" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="M25" s="104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N25" s="105" t="n">
-        <v>213</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="176">
@@ -32903,22 +32903,22 @@
         </is>
       </c>
       <c r="C26" s="102" t="n">
-        <v>640</v>
+        <v>686</v>
       </c>
       <c r="D26" s="103" t="n">
-        <v>439</v>
+        <v>502</v>
       </c>
       <c r="E26" s="103" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F26" s="103" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G26" s="103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H26" s="103" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I26" s="103" t="n">
         <v>1</v>
@@ -32927,16 +32927,16 @@
         <v>0</v>
       </c>
       <c r="K26" s="104" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="L26" s="105" t="n">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c r="M26" s="104" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N26" s="105" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="176">
@@ -32951,22 +32951,22 @@
         </is>
       </c>
       <c r="C27" s="102" t="n">
-        <v>665</v>
+        <v>826</v>
       </c>
       <c r="D27" s="103" t="n">
-        <v>567</v>
+        <v>718</v>
       </c>
       <c r="E27" s="103" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="F27" s="103" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G27" s="103" t="n">
         <v>3</v>
       </c>
       <c r="H27" s="103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" s="104" t="n">
         <v>0</v>
@@ -32975,16 +32975,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="104" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="L27" s="105" t="n">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="M27" s="104" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="N27" s="105" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="4.5" customHeight="1" s="176">
@@ -33015,40 +33015,40 @@
         </is>
       </c>
       <c r="C29" s="102" t="n">
-        <v>516</v>
+        <v>575</v>
       </c>
       <c r="D29" s="103" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="E29" s="103" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="F29" s="103" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G29" s="103" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H29" s="103" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I29" s="103" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J29" s="103" t="n">
+        <v>11</v>
+      </c>
+      <c r="K29" s="104" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="104" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" s="105" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="M29" s="104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N29" s="105" t="n">
-        <v>242</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="176">
@@ -33063,40 +33063,40 @@
         </is>
       </c>
       <c r="C30" s="102" t="n">
-        <v>678</v>
+        <v>806</v>
       </c>
       <c r="D30" s="103" t="n">
-        <v>468</v>
+        <v>578</v>
       </c>
       <c r="E30" s="103" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F30" s="103" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G30" s="103" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H30" s="103" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I30" s="104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="104" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L30" s="105" t="n">
-        <v>187</v>
+        <v>81</v>
       </c>
       <c r="M30" s="104" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="N30" s="105" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="176">
@@ -33111,22 +33111,22 @@
         </is>
       </c>
       <c r="C31" s="102" t="n">
-        <v>713</v>
+        <v>898</v>
       </c>
       <c r="D31" s="103" t="n">
-        <v>598</v>
+        <v>763</v>
       </c>
       <c r="E31" s="103" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="F31" s="103" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G31" s="103" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H31" s="103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" s="103" t="n">
         <v>1</v>
@@ -33135,16 +33135,16 @@
         <v>0</v>
       </c>
       <c r="K31" s="104" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="L31" s="105" t="n">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="M31" s="104" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N31" s="105" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" ht="4.5" customHeight="1" s="176">
@@ -33175,40 +33175,40 @@
         </is>
       </c>
       <c r="C33" s="102" t="n">
-        <v>644</v>
+        <v>609</v>
       </c>
       <c r="D33" s="103" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E33" s="103" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F33" s="103" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="G33" s="103" t="n">
+        <v>23</v>
+      </c>
+      <c r="H33" s="103" t="n">
+        <v>66</v>
+      </c>
+      <c r="I33" s="103" t="n">
         <v>30</v>
       </c>
-      <c r="H33" s="103" t="n">
-        <v>79</v>
-      </c>
-      <c r="I33" s="103" t="n">
-        <v>31</v>
-      </c>
       <c r="J33" s="103" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K33" s="104" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33" s="105" t="n">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="M33" s="104" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N33" s="105" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="176">
@@ -33223,40 +33223,40 @@
         </is>
       </c>
       <c r="C34" s="102" t="n">
-        <v>819</v>
+        <v>962</v>
       </c>
       <c r="D34" s="103" t="n">
-        <v>574</v>
+        <v>685</v>
       </c>
       <c r="E34" s="103" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="F34" s="103" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G34" s="103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H34" s="103" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I34" s="103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="104" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L34" s="105" t="n">
-        <v>196</v>
+        <v>99</v>
       </c>
       <c r="M34" s="104" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N34" s="105" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="176">
@@ -33271,37 +33271,37 @@
         </is>
       </c>
       <c r="C35" s="102" t="n">
-        <v>773</v>
+        <v>888</v>
       </c>
       <c r="D35" s="103" t="n">
-        <v>646</v>
+        <v>747</v>
       </c>
       <c r="E35" s="103" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F35" s="103" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G35" s="103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="103" t="n">
         <v>8</v>
       </c>
       <c r="I35" s="103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" s="103" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="104" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="L35" s="105" t="n">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="M35" s="104" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N35" s="105" t="n">
         <v>129</v>
@@ -33335,22 +33335,22 @@
         </is>
       </c>
       <c r="C37" s="102" t="n">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="D37" s="103" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="E37" s="103" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="F37" s="103" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G37" s="103" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H37" s="103" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="I37" s="103" t="n">
         <v>25</v>
@@ -33359,16 +33359,16 @@
         <v>19</v>
       </c>
       <c r="K37" s="104" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L37" s="105" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M37" s="104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N37" s="105" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="176">
@@ -33383,22 +33383,22 @@
         </is>
       </c>
       <c r="C38" s="102" t="n">
-        <v>721</v>
+        <v>932</v>
       </c>
       <c r="D38" s="103" t="n">
-        <v>531</v>
+        <v>699</v>
       </c>
       <c r="E38" s="103" t="n">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="F38" s="103" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G38" s="103" t="n">
         <v>12</v>
       </c>
       <c r="H38" s="103" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I38" s="103" t="n">
         <v>1</v>
@@ -33407,16 +33407,16 @@
         <v>0</v>
       </c>
       <c r="K38" s="104" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L38" s="105" t="n">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="M38" s="104" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="N38" s="105" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="176">
@@ -33431,19 +33431,19 @@
         </is>
       </c>
       <c r="C39" s="102" t="n">
-        <v>667</v>
+        <v>766</v>
       </c>
       <c r="D39" s="103" t="n">
-        <v>534</v>
+        <v>636</v>
       </c>
       <c r="E39" s="103" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F39" s="103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G39" s="103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39" s="103" t="n">
         <v>3</v>
@@ -33455,16 +33455,16 @@
         <v>0</v>
       </c>
       <c r="K39" s="104" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="L39" s="105" t="n">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="M39" s="104" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="N39" s="105" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" ht="4.5" customHeight="1" s="176">
@@ -33495,40 +33495,40 @@
         </is>
       </c>
       <c r="C41" s="102" t="n">
-        <v>797</v>
+        <v>739</v>
       </c>
       <c r="D41" s="103" t="n">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="E41" s="103" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="F41" s="103" t="n">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="G41" s="103" t="n">
         <v>29</v>
       </c>
       <c r="H41" s="103" t="n">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="I41" s="103" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J41" s="103" t="n">
         <v>15</v>
       </c>
       <c r="K41" s="104" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L41" s="105" t="n">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="M41" s="104" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N41" s="105" t="n">
-        <v>361</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="176">
@@ -33543,22 +33543,22 @@
         </is>
       </c>
       <c r="C42" s="102" t="n">
-        <v>1009</v>
+        <v>1213</v>
       </c>
       <c r="D42" s="103" t="n">
-        <v>726</v>
+        <v>891</v>
       </c>
       <c r="E42" s="103" t="n">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="F42" s="103" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G42" s="103" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H42" s="103" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I42" s="103" t="n">
         <v>2</v>
@@ -33567,16 +33567,16 @@
         <v>0</v>
       </c>
       <c r="K42" s="104" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="L42" s="105" t="n">
-        <v>234</v>
+        <v>105</v>
       </c>
       <c r="M42" s="104" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="N42" s="105" t="n">
-        <v>170</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="176">
@@ -33591,19 +33591,19 @@
         </is>
       </c>
       <c r="C43" s="102" t="n">
-        <v>688</v>
+        <v>738</v>
       </c>
       <c r="D43" s="103" t="n">
-        <v>588</v>
+        <v>643</v>
       </c>
       <c r="E43" s="103" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F43" s="103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G43" s="103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" s="103" t="n">
         <v>4</v>
@@ -33615,16 +33615,16 @@
         <v>0</v>
       </c>
       <c r="K43" s="104" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L43" s="105" t="n">
-        <v>167</v>
+        <v>48</v>
       </c>
       <c r="M43" s="104" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="N43" s="105" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" ht="4.5" customHeight="1" s="176">
@@ -33655,40 +33655,40 @@
         </is>
       </c>
       <c r="C45" s="102" t="n">
-        <v>1017</v>
+        <v>772</v>
       </c>
       <c r="D45" s="103" t="n">
-        <v>334</v>
+        <v>297</v>
       </c>
       <c r="E45" s="103" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="F45" s="103" t="n">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="G45" s="103" t="n">
+        <v>20</v>
+      </c>
+      <c r="H45" s="103" t="n">
+        <v>76</v>
+      </c>
+      <c r="I45" s="103" t="n">
         <v>27</v>
       </c>
-      <c r="H45" s="103" t="n">
-        <v>123</v>
-      </c>
-      <c r="I45" s="103" t="n">
-        <v>54</v>
-      </c>
       <c r="J45" s="103" t="n">
+        <v>18</v>
+      </c>
+      <c r="K45" s="104" t="n">
         <v>24</v>
       </c>
-      <c r="K45" s="104" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" s="105" t="n">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="M45" s="104" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N45" s="105" t="n">
-        <v>456</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="176">
@@ -33703,22 +33703,22 @@
         </is>
       </c>
       <c r="C46" s="102" t="n">
-        <v>1189</v>
+        <v>1146</v>
       </c>
       <c r="D46" s="103" t="n">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="E46" s="103" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F46" s="103" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G46" s="103" t="n">
         <v>10</v>
       </c>
       <c r="H46" s="103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I46" s="103" t="n">
         <v>1</v>
@@ -33727,16 +33727,16 @@
         <v>0</v>
       </c>
       <c r="K46" s="104" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="L46" s="105" t="n">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="M46" s="104" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="N46" s="105" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="176">
@@ -33751,40 +33751,40 @@
         </is>
       </c>
       <c r="C47" s="102" t="n">
-        <v>1102</v>
+        <v>983</v>
       </c>
       <c r="D47" s="103" t="n">
-        <v>915</v>
+        <v>828</v>
       </c>
       <c r="E47" s="103" t="n">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="F47" s="103" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G47" s="103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H47" s="103" t="n">
         <v>6</v>
       </c>
       <c r="I47" s="103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="104" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="104" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="L47" s="105" t="n">
-        <v>261</v>
+        <v>71</v>
       </c>
       <c r="M47" s="104" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="N47" s="105" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" ht="4.5" customHeight="1" s="176">
@@ -33815,40 +33815,40 @@
         </is>
       </c>
       <c r="C49" s="102" t="n">
-        <v>1102</v>
+        <v>920</v>
       </c>
       <c r="D49" s="103" t="n">
-        <v>384</v>
+        <v>333</v>
       </c>
       <c r="E49" s="103" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="103" t="n">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="G49" s="103" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H49" s="103" t="n">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="I49" s="103" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="J49" s="103" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K49" s="104" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L49" s="105" t="n">
-        <v>400</v>
+        <v>318</v>
       </c>
       <c r="M49" s="104" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="N49" s="105" t="n">
-        <v>477</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="176">
@@ -33863,19 +33863,19 @@
         </is>
       </c>
       <c r="C50" s="102" t="n">
-        <v>1204</v>
+        <v>1161</v>
       </c>
       <c r="D50" s="103" t="n">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="E50" s="103" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F50" s="103" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G50" s="103" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H50" s="103" t="n">
         <v>19</v>
@@ -33887,16 +33887,16 @@
         <v>0</v>
       </c>
       <c r="K50" s="104" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="L50" s="105" t="n">
-        <v>331</v>
+        <v>115</v>
       </c>
       <c r="M50" s="104" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="N50" s="105" t="n">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="176">
@@ -33911,16 +33911,16 @@
         </is>
       </c>
       <c r="C51" s="102" t="n">
-        <v>1092</v>
+        <v>998</v>
       </c>
       <c r="D51" s="103" t="n">
-        <v>896</v>
+        <v>841</v>
       </c>
       <c r="E51" s="103" t="n">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="F51" s="103" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G51" s="103" t="n">
         <v>11</v>
@@ -33935,16 +33935,16 @@
         <v>0</v>
       </c>
       <c r="K51" s="104" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="L51" s="105" t="n">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="M51" s="104" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="N51" s="105" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" ht="4.5" customHeight="1" s="176">
@@ -33975,40 +33975,40 @@
         </is>
       </c>
       <c r="C53" s="102" t="n">
-        <v>1267</v>
+        <v>1100</v>
       </c>
       <c r="D53" s="103" t="n">
-        <v>454</v>
+        <v>409</v>
       </c>
       <c r="E53" s="103" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F53" s="103" t="n">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="G53" s="103" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" s="103" t="n">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="I53" s="103" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="J53" s="103" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K53" s="104" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L53" s="105" t="n">
-        <v>489</v>
+        <v>394</v>
       </c>
       <c r="M53" s="104" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N53" s="105" t="n">
-        <v>561</v>
+        <v>525</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="176">
@@ -34023,13 +34023,13 @@
         </is>
       </c>
       <c r="C54" s="102" t="n">
-        <v>1273</v>
+        <v>1233</v>
       </c>
       <c r="D54" s="103" t="n">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="E54" s="103" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F54" s="103" t="n">
         <v>76</v>
@@ -34047,16 +34047,16 @@
         <v>0</v>
       </c>
       <c r="K54" s="104" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="L54" s="105" t="n">
-        <v>338</v>
+        <v>97</v>
       </c>
       <c r="M54" s="104" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="N54" s="105" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="176">
@@ -34071,22 +34071,22 @@
         </is>
       </c>
       <c r="C55" s="102" t="n">
-        <v>1246</v>
+        <v>1119</v>
       </c>
       <c r="D55" s="103" t="n">
-        <v>1021</v>
+        <v>955</v>
       </c>
       <c r="E55" s="103" t="n">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="F55" s="103" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G55" s="103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H55" s="103" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I55" s="103" t="n">
         <v>1</v>
@@ -34095,16 +34095,16 @@
         <v>0</v>
       </c>
       <c r="K55" s="104" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="L55" s="105" t="n">
-        <v>309</v>
+        <v>88</v>
       </c>
       <c r="M55" s="104" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="N55" s="105" t="n">
-        <v>215</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" ht="4.5" customHeight="1" s="176">
@@ -34135,40 +34135,40 @@
         </is>
       </c>
       <c r="C57" s="102" t="n">
-        <v>791</v>
+        <v>703</v>
       </c>
       <c r="D57" s="103" t="n">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="E57" s="103" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F57" s="103" t="n">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="G57" s="103" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H57" s="103" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="I57" s="103" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J57" s="103" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K57" s="104" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L57" s="105" t="n">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="M57" s="104" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N57" s="105" t="n">
-        <v>418</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="176">
@@ -34183,22 +34183,22 @@
         </is>
       </c>
       <c r="C58" s="102" t="n">
-        <v>1138</v>
+        <v>1099</v>
       </c>
       <c r="D58" s="103" t="n">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E58" s="103" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F58" s="103" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G58" s="103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H58" s="103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I58" s="103" t="n">
         <v>1</v>
@@ -34207,16 +34207,16 @@
         <v>0</v>
       </c>
       <c r="K58" s="104" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="L58" s="105" t="n">
-        <v>258</v>
+        <v>91</v>
       </c>
       <c r="M58" s="104" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="N58" s="105" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="176">
@@ -34231,22 +34231,22 @@
         </is>
       </c>
       <c r="C59" s="102" t="n">
-        <v>1015</v>
+        <v>903</v>
       </c>
       <c r="D59" s="103" t="n">
-        <v>827</v>
+        <v>756</v>
       </c>
       <c r="E59" s="103" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F59" s="103" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G59" s="103" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H59" s="103" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I59" s="103" t="n">
         <v>2</v>
@@ -34255,16 +34255,16 @@
         <v>0</v>
       </c>
       <c r="K59" s="104" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L59" s="105" t="n">
-        <v>205</v>
+        <v>52</v>
       </c>
       <c r="M59" s="104" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N59" s="105" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" ht="4.5" customHeight="1" s="176">
@@ -34295,40 +34295,40 @@
         </is>
       </c>
       <c r="C61" s="102" t="n">
-        <v>807</v>
+        <v>732</v>
       </c>
       <c r="D61" s="103" t="n">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="E61" s="103" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F61" s="103" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="G61" s="103" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H61" s="103" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="I61" s="103" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J61" s="103" t="n">
         <v>32</v>
       </c>
       <c r="K61" s="105" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L61" s="105" t="n">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="M61" s="105" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N61" s="105" t="n">
-        <v>358</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="176">
@@ -34343,16 +34343,16 @@
         </is>
       </c>
       <c r="C62" s="102" t="n">
-        <v>942</v>
+        <v>914</v>
       </c>
       <c r="D62" s="103" t="n">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="E62" s="103" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F62" s="103" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G62" s="103" t="n">
         <v>9</v>
@@ -34367,16 +34367,16 @@
         <v>0</v>
       </c>
       <c r="K62" s="105" t="n">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="L62" s="105" t="n">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="M62" s="105" t="n">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="N62" s="105" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="176">
@@ -34391,22 +34391,22 @@
         </is>
       </c>
       <c r="C63" s="102" t="n">
-        <v>955</v>
+        <v>866</v>
       </c>
       <c r="D63" s="103" t="n">
-        <v>788</v>
+        <v>734</v>
       </c>
       <c r="E63" s="103" t="n">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F63" s="103" t="n">
         <v>15</v>
       </c>
       <c r="G63" s="103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H63" s="103" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I63" s="104" t="n">
         <v>0</v>
@@ -34415,16 +34415,16 @@
         <v>0</v>
       </c>
       <c r="K63" s="105" t="n">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="L63" s="105" t="n">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="M63" s="105" t="n">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="N63" s="105" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" ht="4.5" customHeight="1" s="176">
@@ -34455,40 +34455,40 @@
         </is>
       </c>
       <c r="C65" s="102" t="n">
-        <v>741</v>
+        <v>675</v>
       </c>
       <c r="D65" s="103" t="n">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="E65" s="103" t="n">
         <v>82</v>
       </c>
       <c r="F65" s="103" t="n">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="G65" s="103" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H65" s="103" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I65" s="103" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J65" s="103" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K65" s="105" t="n">
         <v>17</v>
       </c>
       <c r="L65" s="105" t="n">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="M65" s="105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N65" s="105" t="n">
-        <v>313</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="176">
@@ -34503,16 +34503,16 @@
         </is>
       </c>
       <c r="C66" s="102" t="n">
-        <v>1002</v>
+        <v>967</v>
       </c>
       <c r="D66" s="103" t="n">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E66" s="103" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F66" s="103" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G66" s="103" t="n">
         <v>12</v>
@@ -34527,16 +34527,16 @@
         <v>0</v>
       </c>
       <c r="K66" s="105" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L66" s="105" t="n">
         <v>85</v>
       </c>
       <c r="M66" s="105" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N66" s="105" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="176">
@@ -34551,22 +34551,22 @@
         </is>
       </c>
       <c r="C67" s="102" t="n">
-        <v>755</v>
+        <v>704</v>
       </c>
       <c r="D67" s="103" t="n">
-        <v>603</v>
+        <v>574</v>
       </c>
       <c r="E67" s="103" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F67" s="103" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G67" s="103" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H67" s="103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I67" s="103" t="n">
         <v>2</v>
@@ -34575,16 +34575,16 @@
         <v>0</v>
       </c>
       <c r="K67" s="105" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="L67" s="105" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="M67" s="105" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N67" s="105" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" ht="4.5" customHeight="1" s="176">
@@ -34615,40 +34615,40 @@
         </is>
       </c>
       <c r="C69" s="102" t="n">
-        <v>737</v>
+        <v>670</v>
       </c>
       <c r="D69" s="103" t="n">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="E69" s="103" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F69" s="103" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="G69" s="103" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H69" s="103" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I69" s="103" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J69" s="103" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K69" s="105" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L69" s="105" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="M69" s="105" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N69" s="105" t="n">
-        <v>301</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="176">
@@ -34663,16 +34663,16 @@
         </is>
       </c>
       <c r="C70" s="102" t="n">
-        <v>986</v>
+        <v>946</v>
       </c>
       <c r="D70" s="103" t="n">
         <v>656</v>
       </c>
       <c r="E70" s="103" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F70" s="103" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G70" s="103" t="n">
         <v>14</v>
@@ -34687,7 +34687,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="105" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L70" s="105" t="n">
         <v>72</v>
@@ -34696,7 +34696,7 @@
         <v>116</v>
       </c>
       <c r="N70" s="105" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="176">
@@ -34711,22 +34711,22 @@
         </is>
       </c>
       <c r="C71" s="102" t="n">
-        <v>745</v>
+        <v>683</v>
       </c>
       <c r="D71" s="103" t="n">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="E71" s="103" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F71" s="103" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G71" s="103" t="n">
         <v>8</v>
       </c>
       <c r="H71" s="103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I71" s="104" t="n">
         <v>0</v>
@@ -34735,16 +34735,16 @@
         <v>0</v>
       </c>
       <c r="K71" s="105" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="L71" s="105" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M71" s="105" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N71" s="105" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" ht="4.5" customHeight="1" s="176">
@@ -34775,40 +34775,40 @@
         </is>
       </c>
       <c r="C73" s="102" t="n">
-        <v>717</v>
+        <v>687</v>
       </c>
       <c r="D73" s="103" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E73" s="103" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F73" s="103" t="n">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G73" s="103" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H73" s="103" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I73" s="103" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="J73" s="103" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K73" s="105" t="n">
         <v>12</v>
       </c>
       <c r="L73" s="105" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M73" s="105" t="n">
         <v>11</v>
       </c>
       <c r="N73" s="105" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="176">
@@ -34823,16 +34823,16 @@
         </is>
       </c>
       <c r="C74" s="102" t="n">
-        <v>1052</v>
+        <v>1019</v>
       </c>
       <c r="D74" s="103" t="n">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E74" s="103" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F74" s="103" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G74" s="103" t="n">
         <v>13</v>
@@ -34847,16 +34847,16 @@
         <v>0</v>
       </c>
       <c r="K74" s="105" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L74" s="105" t="n">
         <v>107</v>
       </c>
       <c r="M74" s="105" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N74" s="105" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="176">
@@ -34871,19 +34871,19 @@
         </is>
       </c>
       <c r="C75" s="102" t="n">
-        <v>715</v>
+        <v>646</v>
       </c>
       <c r="D75" s="103" t="n">
-        <v>591</v>
+        <v>545</v>
       </c>
       <c r="E75" s="103" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="F75" s="103" t="n">
         <v>16</v>
       </c>
       <c r="G75" s="103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H75" s="103" t="n">
         <v>7</v>
@@ -34895,16 +34895,16 @@
         <v>0</v>
       </c>
       <c r="K75" s="105" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="L75" s="105" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M75" s="105" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="N75" s="105" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" ht="4.5" customHeight="1" s="176">
@@ -34935,22 +34935,22 @@
         </is>
       </c>
       <c r="C77" s="102" t="n">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="D77" s="103" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="E77" s="103" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F77" s="103" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G77" s="103" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H77" s="103" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I77" s="103" t="n">
         <v>64</v>
@@ -34959,16 +34959,16 @@
         <v>27</v>
       </c>
       <c r="K77" s="105" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L77" s="105" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="M77" s="105" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N77" s="105" t="n">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="78" ht="19.5" customHeight="1" s="176">
@@ -34983,10 +34983,10 @@
         </is>
       </c>
       <c r="C78" s="102" t="n">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="D78" s="103" t="n">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="E78" s="103" t="n">
         <v>189</v>
@@ -35013,10 +35013,10 @@
         <v>190</v>
       </c>
       <c r="M78" s="105" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N78" s="105" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="176">
@@ -35031,16 +35031,16 @@
         </is>
       </c>
       <c r="C79" s="102" t="n">
-        <v>735</v>
+        <v>662</v>
       </c>
       <c r="D79" s="103" t="n">
-        <v>592</v>
+        <v>535</v>
       </c>
       <c r="E79" s="103" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F79" s="103" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G79" s="103" t="n">
         <v>7</v>
@@ -35055,16 +35055,16 @@
         <v>0</v>
       </c>
       <c r="K79" s="105" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="L79" s="105" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="M79" s="105" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N79" s="105" t="n">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="176">
@@ -35079,7 +35079,7 @@
         </is>
       </c>
       <c r="C80" s="108" t="n">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D80" s="108" t="n">
         <v>290</v>
@@ -35103,13 +35103,13 @@
         <v>34</v>
       </c>
       <c r="K80" s="108" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L80" s="108" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="M80" s="108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N80" s="108" t="n">
         <v>391</v>
@@ -35127,7 +35127,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="D81" t="n">
         <v>834</v>
@@ -35151,13 +35151,13 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L81" t="n">
-        <v>317</v>
+        <v>176</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N81" t="n">
         <v>171</v>
@@ -35175,7 +35175,7 @@
         </is>
       </c>
       <c r="C82" s="102" t="n">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="D82" s="103" t="n">
         <v>474</v>
@@ -35199,13 +35199,13 @@
         <v>0</v>
       </c>
       <c r="K82" s="105" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L82" s="105" t="n">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="M82" s="105" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N82" s="105" t="n">
         <v>115</v>
@@ -35223,7 +35223,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D83" t="n">
         <v>313</v>
@@ -35271,7 +35271,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="D84" t="n">
         <v>684</v>
@@ -35319,7 +35319,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D85" t="n">
         <v>427</v>
@@ -35406,145 +35406,113 @@
     <row r="87" ht="15.75" customHeight="1" s="176">
       <c r="A87" s="100" t="inlineStr">
         <is>
-          <t>T10/2026</t>
+          <t>T1/2025</t>
         </is>
       </c>
       <c r="B87" s="107" t="inlineStr">
         <is>
-          <t>Lens 1 Ngày</t>
+          <t>Lens 3 Tháng</t>
         </is>
       </c>
       <c r="C87" s="102" t="n">
-        <v>100</v>
+        <v>920</v>
       </c>
       <c r="D87" s="103" t="n">
+        <v>871</v>
+      </c>
+      <c r="E87" s="103" t="n">
         <v>44</v>
       </c>
-      <c r="E87" s="103" t="n">
-        <v>15</v>
-      </c>
       <c r="F87" s="103" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G87" s="103" t="n">
         <v>2</v>
       </c>
       <c r="H87" s="104" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I87" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="105" t="n">
+        <v>469</v>
+      </c>
+      <c r="L87" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="J87" s="104" t="n">
-        <v>4</v>
-      </c>
-      <c r="K87" s="105" t="n">
-        <v>7</v>
-      </c>
-      <c r="L87" s="105" t="n">
-        <v>14</v>
-      </c>
       <c r="M87" s="105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N87" s="105" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="176">
-      <c r="A88" s="108" t="inlineStr">
-        <is>
-          <t>T10/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="108" t="inlineStr">
-        <is>
-          <t>Lens 1 Tháng</t>
-        </is>
-      </c>
-      <c r="C88" s="108" t="n">
-        <v>135</v>
-      </c>
-      <c r="D88" s="108" t="n">
-        <v>89</v>
-      </c>
-      <c r="E88" s="108" t="n">
-        <v>30</v>
-      </c>
-      <c r="F88" s="108" t="n">
-        <v>14</v>
-      </c>
-      <c r="G88" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="I88" s="108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="108" t="n">
-        <v>35</v>
-      </c>
-      <c r="L88" s="108" t="n">
-        <v>17</v>
-      </c>
-      <c r="M88" s="108" t="n">
-        <v>15</v>
-      </c>
-      <c r="N88" s="108" t="n">
-        <v>10</v>
-      </c>
+      <c r="A88" s="108" t="n"/>
+      <c r="B88" s="108" t="n"/>
+      <c r="C88" s="108" t="n"/>
+      <c r="D88" s="108" t="n"/>
+      <c r="E88" s="108" t="n"/>
+      <c r="F88" s="108" t="n"/>
+      <c r="G88" s="108" t="n"/>
+      <c r="H88" s="108" t="n"/>
+      <c r="I88" s="108" t="n"/>
+      <c r="J88" s="108" t="n"/>
+      <c r="K88" s="108" t="n"/>
+      <c r="L88" s="108" t="n"/>
+      <c r="M88" s="108" t="n"/>
+      <c r="N88" s="108" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="176">
       <c r="A89" s="100" t="inlineStr">
         <is>
-          <t>T10/2026</t>
+          <t>T2/2025</t>
         </is>
       </c>
       <c r="B89" s="101" t="inlineStr">
         <is>
-          <t>Lens 3 Tháng</t>
+          <t>Lens 1 Ngày</t>
         </is>
       </c>
       <c r="C89" s="102" t="n">
-        <v>71</v>
+        <v>563</v>
       </c>
       <c r="D89" s="103" t="n">
-        <v>60</v>
+        <v>273</v>
       </c>
       <c r="E89" s="103" t="n">
+        <v>123</v>
+      </c>
+      <c r="F89" s="103" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" s="103" t="n">
         <v>10</v>
       </c>
-      <c r="F89" s="103" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="103" t="n">
-        <v>0</v>
-      </c>
       <c r="H89" s="103" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="I89" s="103" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J89" s="103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K89" s="105" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L89" s="105" t="n">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="M89" s="105" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N89" s="105" t="n">
-        <v>10</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" ht="4.5" customHeight="1" s="176">
@@ -38519,40 +38487,40 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>703</v>
+        <v>661</v>
       </c>
       <c r="D163" t="n">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="E163" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F163" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="G163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H163" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I163" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J163" t="n">
         <v>3</v>
       </c>
       <c r="K163" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L163" t="n">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="M163" t="n">
         <v>20</v>
       </c>
       <c r="N163" t="n">
-        <v>267</v>
+        <v>247</v>
       </c>
     </row>
     <row r="164">
@@ -38567,13 +38535,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>450</v>
+        <v>413</v>
       </c>
       <c r="D164" t="n">
-        <v>389</v>
+        <v>355</v>
       </c>
       <c r="E164" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F164" t="n">
         <v>12</v>
@@ -38591,16 +38559,16 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="L164" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="M164" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="N164" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="165">
@@ -38615,10 +38583,10 @@
         </is>
       </c>
       <c r="C165" s="147" t="n">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D165" s="147" t="n">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="E165" s="147" t="n">
         <v>13</v>
@@ -38639,160 +38607,16 @@
         <v>0</v>
       </c>
       <c r="K165" s="147" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L165" s="147" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M165" s="147" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N165" s="147" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>T10/2026</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Lens 1 Ngày</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>121</v>
-      </c>
-      <c r="D167" t="n">
-        <v>64</v>
-      </c>
-      <c r="E167" t="n">
-        <v>21</v>
-      </c>
-      <c r="F167" t="n">
-        <v>21</v>
-      </c>
-      <c r="G167" t="n">
-        <v>2</v>
-      </c>
-      <c r="H167" t="n">
-        <v>7</v>
-      </c>
-      <c r="I167" t="n">
-        <v>5</v>
-      </c>
-      <c r="J167" t="n">
-        <v>1</v>
-      </c>
-      <c r="K167" t="n">
-        <v>1</v>
-      </c>
-      <c r="L167" t="n">
-        <v>22</v>
-      </c>
-      <c r="M167" t="n">
-        <v>5</v>
-      </c>
-      <c r="N167" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>T10/2026</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Lens 1 Tháng</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>83</v>
-      </c>
-      <c r="D168" t="n">
-        <v>75</v>
-      </c>
-      <c r="E168" t="n">
-        <v>7</v>
-      </c>
-      <c r="F168" t="n">
-        <v>1</v>
-      </c>
-      <c r="G168" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>22</v>
-      </c>
-      <c r="L168" t="n">
-        <v>6</v>
-      </c>
-      <c r="M168" t="n">
-        <v>13</v>
-      </c>
-      <c r="N168" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>T10/2026</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Lens 3 Tháng</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>34</v>
-      </c>
-      <c r="D169" t="n">
-        <v>31</v>
-      </c>
-      <c r="E169" t="n">
-        <v>3</v>
-      </c>
-      <c r="F169" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" t="n">
-        <v>6</v>
-      </c>
-      <c r="L169" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" t="n">
-        <v>12</v>
-      </c>
-      <c r="N169" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
